--- a/進捗/コスト表_winter_2026.xlsx
+++ b/進捗/コスト表_winter_2026.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\平尾泰稀\Documents\GitHub\2026_winter\進捗\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2026_winter\進捗\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E61ED458-6CC7-429E-9FF6-18293B429AA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1A964AD-9A09-48D9-8740-FC76F77AB85B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3450" yWindow="0" windowWidth="21600" windowHeight="15585" activeTab="1" xr2:uid="{90270874-AD68-4987-AED5-115E189B84F1}"/>
+    <workbookView xWindow="-28920" yWindow="1695" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{90270874-AD68-4987-AED5-115E189B84F1}"/>
   </bookViews>
   <sheets>
     <sheet name="集計" sheetId="1" r:id="rId1"/>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="147">
   <si>
     <t>設定</t>
   </si>
@@ -508,6 +508,128 @@
     </rPh>
     <phoneticPr fontId="6"/>
   </si>
+  <si>
+    <t>必殺技カメラワーク</t>
+    <rPh sb="0" eb="3">
+      <t>ヒッサツワザ</t>
+    </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>空中-&gt;地上のカメラワーク</t>
+    <rPh sb="0" eb="2">
+      <t>クウチュウ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>チジョウ</t>
+    </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>敵のヒット状態を増やす</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ジョウタイ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>フ</t>
+    </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>強攻撃を見てからヒットバック</t>
+    <rPh sb="0" eb="1">
+      <t>キョウ</t>
+    </rPh>
+    <rPh sb="1" eb="3">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ミ</t>
+    </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>エフェクト関連</t>
+    <rPh sb="5" eb="7">
+      <t>カンレン</t>
+    </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>ポストエフェクト(シェーダー</t>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>敵が出現する条件の設定</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>シュツゲン</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ジョウケン</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>セッテイ</t>
+    </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>ステージ設計</t>
+    <rPh sb="4" eb="6">
+      <t>セッケイ</t>
+    </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>ガード弾きのアニメーション、ステート追加</t>
+    <rPh sb="3" eb="4">
+      <t>ハジ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ツイカ</t>
+    </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>もう一体敵追加(遠距離(壁走りとかを使って素早く倒してほしいため</t>
+    <rPh sb="2" eb="4">
+      <t>イッタイ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ツイカ</t>
+    </rPh>
+    <rPh sb="8" eb="11">
+      <t>エンキョリ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>カベバシ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>ツカ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>スバヤ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>タオ</t>
+    </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>ヒットストップ、タイムスケールのすべての調整</t>
+    <rPh sb="20" eb="22">
+      <t>チョウセイ</t>
+    </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
 </sst>
 </file>
 
@@ -945,7 +1067,30 @@
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="33">
+  <dxfs count="36">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFF2CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF808080"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE2EFDA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFA6A6A6"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FFA6A6A6"/>
@@ -1014,29 +1159,6 @@
       </border>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFF2CC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF808080"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFE2EFDA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFA6A6A6"/>
-      </font>
-    </dxf>
-    <dxf>
       <font>
         <color rgb="FF0070C0"/>
       </font>
@@ -1058,6 +1180,29 @@
         <b/>
         <i val="0"/>
         <color rgb="FFC00000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFF2CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF808080"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE2EFDA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFA6A6A6"/>
       </font>
     </dxf>
     <dxf>
@@ -1562,24 +1707,24 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3A2567DA-ED67-436A-BAF7-D8D91E4E00C2}" name="タスク表" displayName="タスク表" ref="B4:L53" totalsRowShown="0" headerRowDxfId="32" dataDxfId="31" tableBorderDxfId="30">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3A2567DA-ED67-436A-BAF7-D8D91E4E00C2}" name="タスク表" displayName="タスク表" ref="B4:L53" totalsRowShown="0" headerRowDxfId="35" dataDxfId="34" tableBorderDxfId="33">
   <autoFilter ref="B4:L53" xr:uid="{3A2567DA-ED67-436A-BAF7-D8D91E4E00C2}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{F383ED7B-CAB4-46F1-AC7C-023467A46D88}" name="No" dataDxfId="29">
+    <tableColumn id="1" xr3:uid="{F383ED7B-CAB4-46F1-AC7C-023467A46D88}" name="No" dataDxfId="32">
       <calculatedColumnFormula>IF(タスク表[[#This Row],[作業内容]]="","",ROW()-ROW(タスク表[#Headers]))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{7EF03FBB-5A01-49E5-9341-0CD4CA09848E}" name="カテゴリ" dataDxfId="28"/>
-    <tableColumn id="3" xr3:uid="{48466042-E58A-4D97-AC9B-D6FED5F46A1F}" name="作業内容" dataDxfId="27"/>
-    <tableColumn id="4" xr3:uid="{65680DBB-31AB-43B9-BFA7-0526EC96D22F}" name="優先度" dataDxfId="26"/>
-    <tableColumn id="5" xr3:uid="{D7E12594-DF8F-4044-8B36-8EAC7E3BB4E5}" name="バージョン" dataDxfId="25"/>
-    <tableColumn id="6" xr3:uid="{BAF69BB2-2D96-4276-B8FA-8A5B618ED05F}" name="見積コスト" dataDxfId="24"/>
-    <tableColumn id="7" xr3:uid="{0A021283-FCFD-447B-98BD-F53EF31318C1}" name="実コスト" dataDxfId="23"/>
-    <tableColumn id="8" xr3:uid="{75B48E43-3BBD-4AF9-A1B3-D350673AB994}" name="差分" dataDxfId="22">
+    <tableColumn id="2" xr3:uid="{7EF03FBB-5A01-49E5-9341-0CD4CA09848E}" name="カテゴリ" dataDxfId="31"/>
+    <tableColumn id="3" xr3:uid="{48466042-E58A-4D97-AC9B-D6FED5F46A1F}" name="作業内容" dataDxfId="30"/>
+    <tableColumn id="4" xr3:uid="{65680DBB-31AB-43B9-BFA7-0526EC96D22F}" name="優先度" dataDxfId="29"/>
+    <tableColumn id="5" xr3:uid="{D7E12594-DF8F-4044-8B36-8EAC7E3BB4E5}" name="バージョン" dataDxfId="28"/>
+    <tableColumn id="6" xr3:uid="{BAF69BB2-2D96-4276-B8FA-8A5B618ED05F}" name="見積コスト" dataDxfId="27"/>
+    <tableColumn id="7" xr3:uid="{0A021283-FCFD-447B-98BD-F53EF31318C1}" name="実コスト" dataDxfId="26"/>
+    <tableColumn id="8" xr3:uid="{75B48E43-3BBD-4AF9-A1B3-D350673AB994}" name="差分" dataDxfId="25">
       <calculatedColumnFormula>IF(OR(タスク表[[#This Row],[見積コスト]]="",タスク表[[#This Row],[実コスト]]=""),"",タスク表[[#This Row],[実コスト]]-タスク表[[#This Row],[見積コスト]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{7B1D7DAB-403C-43FB-B066-5FF4BD411B5A}" name="ステータス" dataDxfId="21"/>
-    <tableColumn id="10" xr3:uid="{D6F46B68-27C3-483A-8CAC-834EC0598F40}" name="完了日" dataDxfId="20"/>
-    <tableColumn id="11" xr3:uid="{40889AD2-F644-4454-99EC-D71EF37CD54A}" name="備考" dataDxfId="19"/>
+    <tableColumn id="9" xr3:uid="{7B1D7DAB-403C-43FB-B066-5FF4BD411B5A}" name="ステータス" dataDxfId="24"/>
+    <tableColumn id="10" xr3:uid="{D6F46B68-27C3-483A-8CAC-834EC0598F40}" name="完了日" dataDxfId="23"/>
+    <tableColumn id="11" xr3:uid="{40889AD2-F644-4454-99EC-D71EF37CD54A}" name="備考" dataDxfId="22"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1935,7 +2080,7 @@
       </c>
       <c r="C5" s="17">
         <f ca="1">TODAY()</f>
-        <v>46304</v>
+        <v>46306</v>
       </c>
       <c r="D5" s="3"/>
     </row>
@@ -2051,7 +2196,7 @@
       </c>
       <c r="C15" s="20">
         <f ca="1">IF(C14="","",MAX(0,NETWORKDAYS.INTL(TODAY(),C14,週末区分,休日一覧)))</f>
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>93</v>
@@ -2075,7 +2220,7 @@
       </c>
       <c r="C17" s="18">
         <f ca="1">IF(C15="","",作業時間*C15-C9)</f>
-        <v>688</v>
+        <v>680</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>97</v>
@@ -2168,7 +2313,7 @@
       </c>
       <c r="J23" s="28">
         <f ca="1">IF(C23="","",MAX(0,NETWORKDAYS.INTL(TODAY(),C23,週末区分,休日一覧)))</f>
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K23" s="24">
         <f t="shared" ref="K23:K30" ca="1" si="2">IF(OR(J23="",N(J23)=0),"",G23/J23)</f>
@@ -2176,7 +2321,7 @@
       </c>
       <c r="L23" s="24">
         <f t="shared" ref="L23:L30" ca="1" si="3">IF(J23="","",作業時間*J23-G23)</f>
-        <v>200</v>
+        <v>192</v>
       </c>
     </row>
     <row r="24" spans="2:12" x14ac:dyDescent="0.4">
@@ -2214,7 +2359,7 @@
       </c>
       <c r="J24" s="28">
         <f ca="1">IF(C24="","",MAX(0,NETWORKDAYS.INTL(TODAY(),C24,週末区分,休日一覧)))</f>
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="K24" s="24">
         <f t="shared" ca="1" si="2"/>
@@ -2222,7 +2367,7 @@
       </c>
       <c r="L24" s="24">
         <f t="shared" ca="1" si="3"/>
-        <v>392</v>
+        <v>384</v>
       </c>
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.4">
@@ -2260,7 +2405,7 @@
       </c>
       <c r="J25" s="28">
         <f ca="1">IF(C25="","",MAX(0,NETWORKDAYS.INTL(TODAY(),C25,週末区分,休日一覧)))</f>
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K25" s="24">
         <f t="shared" ca="1" si="2"/>
@@ -2268,7 +2413,7 @@
       </c>
       <c r="L25" s="24">
         <f t="shared" ca="1" si="3"/>
-        <v>576</v>
+        <v>568</v>
       </c>
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.4">
@@ -2306,7 +2451,7 @@
       </c>
       <c r="J26" s="28">
         <f ca="1">IF(C26="","",MAX(0,NETWORKDAYS.INTL(TODAY(),C26,週末区分,休日一覧)))</f>
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="K26" s="24">
         <f t="shared" ca="1" si="2"/>
@@ -2314,7 +2459,7 @@
       </c>
       <c r="L26" s="24">
         <f t="shared" ca="1" si="3"/>
-        <v>688</v>
+        <v>680</v>
       </c>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.4">
@@ -2643,7 +2788,7 @@
       </c>
       <c r="P36" s="5">
         <f>IF(K36="","",COUNTIFS(タスク表[優先度],K36,タスク表[作業内容],"&lt;&gt;",タスク表[ステータス],"&lt;&gt;"&amp;除外ST))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37" spans="2:16" x14ac:dyDescent="0.4">
@@ -2677,7 +2822,7 @@
       </c>
       <c r="I37" s="5">
         <f>IF(B37="","",COUNTIFS(タスク表[カテゴリ],B37,タスク表[作業内容],"&lt;&gt;",タスク表[ステータス],完了ST))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K37" s="30" t="str">
         <f>IF(設定!$H14="","",設定!$H14)</f>
@@ -2731,7 +2876,7 @@
       </c>
       <c r="H38" s="5">
         <f>IF(B38="","",COUNTIFS(タスク表[カテゴリ],B38,タスク表[作業内容],"&lt;&gt;",タスク表[ステータス],"&lt;&gt;"&amp;除外ST))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I38" s="5">
         <f>IF(B38="","",COUNTIFS(タスク表[カテゴリ],B38,タスク表[作業内容],"&lt;&gt;",タスク表[ステータス],完了ST))</f>
@@ -2847,7 +2992,7 @@
       </c>
       <c r="H40" s="5">
         <f>IF(B40="","",COUNTIFS(タスク表[カテゴリ],B40,タスク表[作業内容],"&lt;&gt;",タスク表[ステータス],"&lt;&gt;"&amp;除外ST))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I40" s="5">
         <f>IF(B40="","",COUNTIFS(タスク表[カテゴリ],B40,タスク表[作業内容],"&lt;&gt;",タスク表[ステータス],完了ST))</f>
@@ -3137,7 +3282,7 @@
       </c>
       <c r="H45" s="5">
         <f>IF(B45="","",COUNTIFS(タスク表[カテゴリ],B45,タスク表[作業内容],"&lt;&gt;",タスク表[ステータス],"&lt;&gt;"&amp;除外ST))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I45" s="5">
         <f>IF(B45="","",COUNTIFS(タスク表[カテゴリ],B45,タスク表[作業内容],"&lt;&gt;",タスク表[ステータス],完了ST))</f>
@@ -3874,7 +4019,7 @@
       </c>
       <c r="H66" s="21">
         <f>IF(FALSE,"",COUNTIFS(タスク表[カテゴリ],"",タスク表[作業内容],"&lt;&gt;",タスク表[ステータス],"&lt;&gt;"&amp;除外ST))</f>
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="I66" s="21">
         <f>IF(FALSE,"",COUNTIFS(タスク表[カテゴリ],"",タスク表[作業内容],"&lt;&gt;",タスク表[ステータス],完了ST))</f>
@@ -3898,7 +4043,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C17">
-    <cfRule type="expression" dxfId="18" priority="2" stopIfTrue="1">
+    <cfRule type="expression" dxfId="21" priority="2" stopIfTrue="1">
       <formula>AND(ISNUMBER(C17),C17&lt;0)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3931,7 +4076,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L23:L30">
-    <cfRule type="expression" dxfId="17" priority="4" stopIfTrue="1">
+    <cfRule type="expression" dxfId="20" priority="4" stopIfTrue="1">
       <formula>AND(ISNUMBER(L23),L23&lt;0)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4149,12 +4294,14 @@
       <c r="L7" s="52"/>
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.4">
-      <c r="B8" s="46" t="str">
+      <c r="B8" s="46">
         <f>IF(タスク表[[#This Row],[作業内容]]="","",ROW()-ROW(タスク表[#Headers]))</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="C8" s="44"/>
-      <c r="D8" s="47"/>
+      <c r="D8" s="47" t="s">
+        <v>144</v>
+      </c>
       <c r="E8" s="48"/>
       <c r="F8" s="48"/>
       <c r="G8" s="49"/>
@@ -4262,7 +4409,9 @@
         <f>IF(OR(タスク表[[#This Row],[見積コスト]]="",タスク表[[#This Row],[実コスト]]=""),"",タスク表[[#This Row],[実コスト]]-タスク表[[#This Row],[見積コスト]])</f>
         <v/>
       </c>
-      <c r="J13" s="48"/>
+      <c r="J13" s="48" t="s">
+        <v>11</v>
+      </c>
       <c r="K13" s="51"/>
       <c r="L13" s="52"/>
     </row>
@@ -4283,17 +4432,21 @@
         <f>IF(OR(タスク表[[#This Row],[見積コスト]]="",タスク表[[#This Row],[実コスト]]=""),"",タスク表[[#This Row],[実コスト]]-タスク表[[#This Row],[見積コスト]])</f>
         <v/>
       </c>
-      <c r="J14" s="48"/>
+      <c r="J14" s="48" t="s">
+        <v>51</v>
+      </c>
       <c r="K14" s="51"/>
       <c r="L14" s="52"/>
     </row>
     <row r="15" spans="2:12" x14ac:dyDescent="0.4">
-      <c r="B15" s="46" t="str">
+      <c r="B15" s="46">
         <f>IF(タスク表[[#This Row],[作業内容]]="","",ROW()-ROW(タスク表[#Headers]))</f>
-        <v/>
+        <v>11</v>
       </c>
       <c r="C15" s="44"/>
-      <c r="D15" s="47"/>
+      <c r="D15" s="47" t="s">
+        <v>138</v>
+      </c>
       <c r="E15" s="48"/>
       <c r="F15" s="48"/>
       <c r="G15" s="49"/>
@@ -4307,12 +4460,14 @@
       <c r="L15" s="52"/>
     </row>
     <row r="16" spans="2:12" x14ac:dyDescent="0.4">
-      <c r="B16" s="46" t="str">
+      <c r="B16" s="46">
         <f>IF(タスク表[[#This Row],[作業内容]]="","",ROW()-ROW(タスク表[#Headers]))</f>
-        <v/>
+        <v>12</v>
       </c>
       <c r="C16" s="44"/>
-      <c r="D16" s="47"/>
+      <c r="D16" s="47" t="s">
+        <v>139</v>
+      </c>
       <c r="E16" s="48"/>
       <c r="F16" s="48"/>
       <c r="G16" s="49"/>
@@ -4325,13 +4480,15 @@
       <c r="K16" s="51"/>
       <c r="L16" s="52"/>
     </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.4">
-      <c r="B17" s="46" t="str">
+    <row r="17" spans="2:12" ht="28.5" x14ac:dyDescent="0.4">
+      <c r="B17" s="46">
         <f>IF(タスク表[[#This Row],[作業内容]]="","",ROW()-ROW(タスク表[#Headers]))</f>
-        <v/>
+        <v>13</v>
       </c>
       <c r="C17" s="44"/>
-      <c r="D17" s="47"/>
+      <c r="D17" s="47" t="s">
+        <v>145</v>
+      </c>
       <c r="E17" s="48"/>
       <c r="F17" s="48"/>
       <c r="G17" s="49"/>
@@ -4364,12 +4521,16 @@
       <c r="L18" s="52"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.4">
-      <c r="B19" s="46" t="str">
+      <c r="B19" s="46">
         <f>IF(タスク表[[#This Row],[作業内容]]="","",ROW()-ROW(タスク表[#Headers]))</f>
-        <v/>
-      </c>
-      <c r="C19" s="44"/>
-      <c r="D19" s="47"/>
+        <v>15</v>
+      </c>
+      <c r="C19" s="44" t="s">
+        <v>29</v>
+      </c>
+      <c r="D19" s="47" t="s">
+        <v>136</v>
+      </c>
       <c r="E19" s="48"/>
       <c r="F19" s="48"/>
       <c r="G19" s="49"/>
@@ -4383,12 +4544,14 @@
       <c r="L19" s="52"/>
     </row>
     <row r="20" spans="2:12" x14ac:dyDescent="0.4">
-      <c r="B20" s="46" t="str">
+      <c r="B20" s="46">
         <f>IF(タスク表[[#This Row],[作業内容]]="","",ROW()-ROW(タスク表[#Headers]))</f>
-        <v/>
+        <v>16</v>
       </c>
       <c r="C20" s="44"/>
-      <c r="D20" s="47"/>
+      <c r="D20" s="47" t="s">
+        <v>137</v>
+      </c>
       <c r="E20" s="48"/>
       <c r="F20" s="48"/>
       <c r="G20" s="49"/>
@@ -4440,12 +4603,16 @@
       <c r="L22" s="52"/>
     </row>
     <row r="23" spans="2:12" x14ac:dyDescent="0.4">
-      <c r="B23" s="46" t="str">
+      <c r="B23" s="46">
         <f>IF(タスク表[[#This Row],[作業内容]]="","",ROW()-ROW(タスク表[#Headers]))</f>
-        <v/>
-      </c>
-      <c r="C23" s="44"/>
-      <c r="D23" s="47"/>
+        <v>19</v>
+      </c>
+      <c r="C23" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="D23" s="47" t="s">
+        <v>140</v>
+      </c>
       <c r="E23" s="48"/>
       <c r="F23" s="48"/>
       <c r="G23" s="49"/>
@@ -4459,12 +4626,16 @@
       <c r="L23" s="52"/>
     </row>
     <row r="24" spans="2:12" x14ac:dyDescent="0.4">
-      <c r="B24" s="46" t="str">
+      <c r="B24" s="46">
         <f>IF(タスク表[[#This Row],[作業内容]]="","",ROW()-ROW(タスク表[#Headers]))</f>
-        <v/>
-      </c>
-      <c r="C24" s="44"/>
-      <c r="D24" s="47"/>
+        <v>20</v>
+      </c>
+      <c r="C24" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="D24" s="47" t="s">
+        <v>141</v>
+      </c>
       <c r="E24" s="48"/>
       <c r="F24" s="48"/>
       <c r="G24" s="49"/>
@@ -4478,12 +4649,14 @@
       <c r="L24" s="52"/>
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.4">
-      <c r="B25" s="46" t="str">
+      <c r="B25" s="46">
         <f>IF(タスク表[[#This Row],[作業内容]]="","",ROW()-ROW(タスク表[#Headers]))</f>
-        <v/>
+        <v>21</v>
       </c>
       <c r="C25" s="44"/>
-      <c r="D25" s="47"/>
+      <c r="D25" s="47" t="s">
+        <v>142</v>
+      </c>
       <c r="E25" s="48"/>
       <c r="F25" s="48"/>
       <c r="G25" s="49"/>
@@ -4497,13 +4670,17 @@
       <c r="L25" s="52"/>
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.4">
-      <c r="B26" s="46" t="str">
+      <c r="B26" s="46">
         <f>IF(タスク表[[#This Row],[作業内容]]="","",ROW()-ROW(タスク表[#Headers]))</f>
-        <v/>
+        <v>22</v>
       </c>
       <c r="C26" s="44"/>
-      <c r="D26" s="47"/>
-      <c r="E26" s="48"/>
+      <c r="D26" s="47" t="s">
+        <v>146</v>
+      </c>
+      <c r="E26" s="48" t="s">
+        <v>41</v>
+      </c>
       <c r="F26" s="48"/>
       <c r="G26" s="49"/>
       <c r="H26" s="49"/>
@@ -4535,12 +4712,16 @@
       <c r="L27" s="52"/>
     </row>
     <row r="28" spans="2:12" x14ac:dyDescent="0.4">
-      <c r="B28" s="46" t="str">
+      <c r="B28" s="46">
         <f>IF(タスク表[[#This Row],[作業内容]]="","",ROW()-ROW(タスク表[#Headers]))</f>
-        <v/>
-      </c>
-      <c r="C28" s="44"/>
-      <c r="D28" s="47"/>
+        <v>24</v>
+      </c>
+      <c r="C28" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="D28" s="47" t="s">
+        <v>143</v>
+      </c>
       <c r="E28" s="48"/>
       <c r="F28" s="48"/>
       <c r="G28" s="49"/>
@@ -16394,15 +16575,26 @@
     </row>
   </sheetData>
   <phoneticPr fontId="6"/>
-  <conditionalFormatting sqref="B5:L7 B11:L1000 E8:L10 B8:B10">
-    <cfRule type="expression" dxfId="16" priority="1" stopIfTrue="1">
+  <conditionalFormatting sqref="B5:L7 B8:B10 E8:L10 B11:L16 B21:L1000 B17:B20 E17:L20">
+    <cfRule type="expression" dxfId="19" priority="1" stopIfTrue="1">
       <formula>AND($J5&lt;&gt;"",$J5=除外ST)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="15" priority="2" stopIfTrue="1">
+    <cfRule type="expression" dxfId="18" priority="2" stopIfTrue="1">
       <formula>AND($J5&lt;&gt;"",$J5=完了ST)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="14" priority="3" stopIfTrue="1">
+    <cfRule type="expression" dxfId="17" priority="3" stopIfTrue="1">
       <formula>$J5="作業中"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C13:D14">
+    <cfRule type="expression" dxfId="16" priority="11" stopIfTrue="1">
+      <formula>AND($J8&lt;&gt;"",$J8=除外ST)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="15" priority="12" stopIfTrue="1">
+      <formula>AND($J8&lt;&gt;"",$J8=完了ST)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="14" priority="13" stopIfTrue="1">
+      <formula>$J8="作業中"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E5:E1000">
@@ -16421,15 +16613,15 @@
       <formula>AND(ISNUMBER(I5),I5&lt;0)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C13:D14">
-    <cfRule type="expression" dxfId="9" priority="11" stopIfTrue="1">
-      <formula>AND($J8&lt;&gt;"",$J8=除外ST)</formula>
+  <conditionalFormatting sqref="C19:D20">
+    <cfRule type="expression" dxfId="2" priority="17" stopIfTrue="1">
+      <formula>AND($J17&lt;&gt;"",$J17=除外ST)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="8" priority="12" stopIfTrue="1">
-      <formula>AND($J8&lt;&gt;"",$J8=完了ST)</formula>
+    <cfRule type="expression" dxfId="1" priority="18" stopIfTrue="1">
+      <formula>AND($J17&lt;&gt;"",$J17=完了ST)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="7" priority="13" stopIfTrue="1">
-      <formula>$J8="作業中"</formula>
+    <cfRule type="expression" dxfId="0" priority="19" stopIfTrue="1">
+      <formula>$J17="作業中"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="5">
@@ -16445,7 +16637,7 @@
     <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="0以上の数値を入力してください" sqref="G5:H1000" xr:uid="{3EFE3393-D09C-4B29-BFD5-14DF7F410677}">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C5:C7 C11:C1000" xr:uid="{E6BBE5BD-7004-4694-85A6-704154467F57}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C5:C7 C11:C16 C19:C1000" xr:uid="{E6BBE5BD-7004-4694-85A6-704154467F57}">
       <formula1>カテゴリ一覧</formula1>
     </dataValidation>
   </dataValidations>
@@ -16713,11 +16905,11 @@
       </c>
       <c r="AB7" s="36">
         <f t="shared" ref="AB7:AB14" ca="1" si="0">IF(AA7="","",AA7-TODAY())</f>
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="AC7" s="36">
         <f ca="1">IF(AA7="","",MAX(0,NETWORKDAYS.INTL(TODAY(),AA7,週末区分,休日一覧)))</f>
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8" spans="2:29" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
@@ -16815,11 +17007,11 @@
       </c>
       <c r="AB8" s="36">
         <f t="shared" ca="1" si="0"/>
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="AC8" s="36">
         <f ca="1">IF(AA8="","",MAX(0,NETWORKDAYS.INTL(TODAY(),AA8,週末区分,休日一覧)))</f>
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9" spans="2:29" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
@@ -16917,11 +17109,11 @@
       </c>
       <c r="AB9" s="36">
         <f t="shared" ca="1" si="0"/>
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="AC9" s="36">
         <f ca="1">IF(AA9="","",MAX(0,NETWORKDAYS.INTL(TODAY(),AA9,週末区分,休日一覧)))</f>
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="10" spans="2:29" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
@@ -17019,11 +17211,11 @@
       </c>
       <c r="AB10" s="36">
         <f t="shared" ca="1" si="0"/>
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="AC10" s="36">
         <f ca="1">IF(AA10="","",MAX(0,NETWORKDAYS.INTL(TODAY(),AA10,週末区分,休日一覧)))</f>
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="11" spans="2:29" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
@@ -17915,27 +18107,27 @@
   </mergeCells>
   <phoneticPr fontId="6"/>
   <conditionalFormatting sqref="B7:H12 J7:P12 R7:X12 B17:H22 J17:P22 R17:X22">
-    <cfRule type="expression" dxfId="6" priority="1" stopIfTrue="1">
+    <cfRule type="expression" dxfId="9" priority="1" stopIfTrue="1">
       <formula>AND(B7&lt;&gt;"",B7=TODAY())</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="5" priority="2" stopIfTrue="1">
+    <cfRule type="expression" dxfId="8" priority="2" stopIfTrue="1">
       <formula>AND(B7&lt;&gt;"",COUNTIF(マイルストーン日付,B7)&gt;0)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="4" priority="3" stopIfTrue="1">
+    <cfRule type="expression" dxfId="7" priority="3" stopIfTrue="1">
       <formula>AND(B7&lt;&gt;"",B7=開始日)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="3" priority="4" stopIfTrue="1">
+    <cfRule type="expression" dxfId="6" priority="4" stopIfTrue="1">
       <formula>AND(B7&lt;&gt;"",COUNTIF(休日一覧,B7)&gt;0)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="5" stopIfTrue="1">
+    <cfRule type="expression" dxfId="5" priority="5" stopIfTrue="1">
       <formula>AND(B7&lt;&gt;"",OR(WEEKDAY(B7)=1,WEEKDAY(B7)=7))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="6" stopIfTrue="1">
+    <cfRule type="expression" dxfId="4" priority="6" stopIfTrue="1">
       <formula>AND(B7&lt;&gt;"",B7&lt;TODAY())</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB7:AB14">
-    <cfRule type="expression" dxfId="0" priority="7" stopIfTrue="1">
+    <cfRule type="expression" dxfId="3" priority="7" stopIfTrue="1">
       <formula>AND(ISNUMBER(AB7),AB7&lt;0)</formula>
     </cfRule>
   </conditionalFormatting>

--- a/進捗/コスト表_winter_2026.xlsx
+++ b/進捗/コスト表_winter_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2026_winter\進捗\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1A964AD-9A09-48D9-8740-FC76F77AB85B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37908A3E-5579-40E1-8280-754BEA258A33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="1695" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{90270874-AD68-4987-AED5-115E189B84F1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{90270874-AD68-4987-AED5-115E189B84F1}"/>
   </bookViews>
   <sheets>
     <sheet name="集計" sheetId="1" r:id="rId1"/>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="149">
   <si>
     <t>設定</t>
   </si>
@@ -630,6 +630,32 @@
     </rPh>
     <phoneticPr fontId="6"/>
   </si>
+  <si>
+    <t>壁キック、壁走りのやめる時間制限をつける</t>
+    <rPh sb="0" eb="1">
+      <t>カベ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>カベバシ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ジカン</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>セイゲン</t>
+    </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>敵の外部化</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="2" eb="5">
+      <t>ガイブカ</t>
+    </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
 </sst>
 </file>
 
@@ -1067,7 +1093,7 @@
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="36">
+  <dxfs count="39">
     <dxf>
       <fill>
         <patternFill>
@@ -1180,6 +1206,29 @@
         <b/>
         <i val="0"/>
         <color rgb="FFC00000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFF2CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF808080"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE2EFDA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFA6A6A6"/>
       </font>
     </dxf>
     <dxf>
@@ -1707,24 +1756,24 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3A2567DA-ED67-436A-BAF7-D8D91E4E00C2}" name="タスク表" displayName="タスク表" ref="B4:L53" totalsRowShown="0" headerRowDxfId="35" dataDxfId="34" tableBorderDxfId="33">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3A2567DA-ED67-436A-BAF7-D8D91E4E00C2}" name="タスク表" displayName="タスク表" ref="B4:L53" totalsRowShown="0" headerRowDxfId="38" dataDxfId="37" tableBorderDxfId="36">
   <autoFilter ref="B4:L53" xr:uid="{3A2567DA-ED67-436A-BAF7-D8D91E4E00C2}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{F383ED7B-CAB4-46F1-AC7C-023467A46D88}" name="No" dataDxfId="32">
+    <tableColumn id="1" xr3:uid="{F383ED7B-CAB4-46F1-AC7C-023467A46D88}" name="No" dataDxfId="35">
       <calculatedColumnFormula>IF(タスク表[[#This Row],[作業内容]]="","",ROW()-ROW(タスク表[#Headers]))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{7EF03FBB-5A01-49E5-9341-0CD4CA09848E}" name="カテゴリ" dataDxfId="31"/>
-    <tableColumn id="3" xr3:uid="{48466042-E58A-4D97-AC9B-D6FED5F46A1F}" name="作業内容" dataDxfId="30"/>
-    <tableColumn id="4" xr3:uid="{65680DBB-31AB-43B9-BFA7-0526EC96D22F}" name="優先度" dataDxfId="29"/>
-    <tableColumn id="5" xr3:uid="{D7E12594-DF8F-4044-8B36-8EAC7E3BB4E5}" name="バージョン" dataDxfId="28"/>
-    <tableColumn id="6" xr3:uid="{BAF69BB2-2D96-4276-B8FA-8A5B618ED05F}" name="見積コスト" dataDxfId="27"/>
-    <tableColumn id="7" xr3:uid="{0A021283-FCFD-447B-98BD-F53EF31318C1}" name="実コスト" dataDxfId="26"/>
-    <tableColumn id="8" xr3:uid="{75B48E43-3BBD-4AF9-A1B3-D350673AB994}" name="差分" dataDxfId="25">
+    <tableColumn id="2" xr3:uid="{7EF03FBB-5A01-49E5-9341-0CD4CA09848E}" name="カテゴリ" dataDxfId="34"/>
+    <tableColumn id="3" xr3:uid="{48466042-E58A-4D97-AC9B-D6FED5F46A1F}" name="作業内容" dataDxfId="33"/>
+    <tableColumn id="4" xr3:uid="{65680DBB-31AB-43B9-BFA7-0526EC96D22F}" name="優先度" dataDxfId="32"/>
+    <tableColumn id="5" xr3:uid="{D7E12594-DF8F-4044-8B36-8EAC7E3BB4E5}" name="バージョン" dataDxfId="31"/>
+    <tableColumn id="6" xr3:uid="{BAF69BB2-2D96-4276-B8FA-8A5B618ED05F}" name="見積コスト" dataDxfId="30"/>
+    <tableColumn id="7" xr3:uid="{0A021283-FCFD-447B-98BD-F53EF31318C1}" name="実コスト" dataDxfId="29"/>
+    <tableColumn id="8" xr3:uid="{75B48E43-3BBD-4AF9-A1B3-D350673AB994}" name="差分" dataDxfId="28">
       <calculatedColumnFormula>IF(OR(タスク表[[#This Row],[見積コスト]]="",タスク表[[#This Row],[実コスト]]=""),"",タスク表[[#This Row],[実コスト]]-タスク表[[#This Row],[見積コスト]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{7B1D7DAB-403C-43FB-B066-5FF4BD411B5A}" name="ステータス" dataDxfId="24"/>
-    <tableColumn id="10" xr3:uid="{D6F46B68-27C3-483A-8CAC-834EC0598F40}" name="完了日" dataDxfId="23"/>
-    <tableColumn id="11" xr3:uid="{40889AD2-F644-4454-99EC-D71EF37CD54A}" name="備考" dataDxfId="22"/>
+    <tableColumn id="9" xr3:uid="{7B1D7DAB-403C-43FB-B066-5FF4BD411B5A}" name="ステータス" dataDxfId="27"/>
+    <tableColumn id="10" xr3:uid="{D6F46B68-27C3-483A-8CAC-834EC0598F40}" name="完了日" dataDxfId="26"/>
+    <tableColumn id="11" xr3:uid="{40889AD2-F644-4454-99EC-D71EF37CD54A}" name="備考" dataDxfId="25"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2080,7 +2129,7 @@
       </c>
       <c r="C5" s="17">
         <f ca="1">TODAY()</f>
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="D5" s="3"/>
     </row>
@@ -2160,7 +2209,7 @@
       </c>
       <c r="C12" s="20">
         <f ca="1">MAX(0,NETWORKDAYS.INTL(開始日,TODAY(),週末区分,休日一覧))</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>87</v>
@@ -4019,11 +4068,11 @@
       </c>
       <c r="H66" s="21">
         <f>IF(FALSE,"",COUNTIFS(タスク表[カテゴリ],"",タスク表[作業内容],"&lt;&gt;",タスク表[ステータス],"&lt;&gt;"&amp;除外ST))</f>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I66" s="21">
         <f>IF(FALSE,"",COUNTIFS(タスク表[カテゴリ],"",タスク表[作業内容],"&lt;&gt;",タスク表[ステータス],完了ST))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -4043,7 +4092,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C17">
-    <cfRule type="expression" dxfId="21" priority="2" stopIfTrue="1">
+    <cfRule type="expression" dxfId="24" priority="2" stopIfTrue="1">
       <formula>AND(ISNUMBER(C17),C17&lt;0)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4076,7 +4125,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L23:L30">
-    <cfRule type="expression" dxfId="20" priority="4" stopIfTrue="1">
+    <cfRule type="expression" dxfId="23" priority="4" stopIfTrue="1">
       <formula>AND(ISNUMBER(L23),L23&lt;0)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4315,12 +4364,14 @@
       <c r="L8" s="52"/>
     </row>
     <row r="9" spans="2:12" x14ac:dyDescent="0.4">
-      <c r="B9" s="46" t="str">
+      <c r="B9" s="46">
         <f>IF(タスク表[[#This Row],[作業内容]]="","",ROW()-ROW(タスク表[#Headers]))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="C9" s="44"/>
-      <c r="D9" s="47"/>
+      <c r="D9" s="47" t="s">
+        <v>147</v>
+      </c>
       <c r="E9" s="48"/>
       <c r="F9" s="48"/>
       <c r="G9" s="49"/>
@@ -4433,7 +4484,7 @@
         <v/>
       </c>
       <c r="J14" s="48" t="s">
-        <v>51</v>
+        <v>11</v>
       </c>
       <c r="K14" s="51"/>
       <c r="L14" s="52"/>
@@ -4455,7 +4506,9 @@
         <f>IF(OR(タスク表[[#This Row],[見積コスト]]="",タスク表[[#This Row],[実コスト]]=""),"",タスク表[[#This Row],[実コスト]]-タスク表[[#This Row],[見積コスト]])</f>
         <v/>
       </c>
-      <c r="J15" s="48"/>
+      <c r="J15" s="48" t="s">
+        <v>51</v>
+      </c>
       <c r="K15" s="51"/>
       <c r="L15" s="52"/>
     </row>
@@ -4502,12 +4555,14 @@
       <c r="L17" s="52"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.4">
-      <c r="B18" s="46" t="str">
+      <c r="B18" s="46">
         <f>IF(タスク表[[#This Row],[作業内容]]="","",ROW()-ROW(タスク表[#Headers]))</f>
-        <v/>
+        <v>14</v>
       </c>
       <c r="C18" s="44"/>
-      <c r="D18" s="47"/>
+      <c r="D18" s="47" t="s">
+        <v>148</v>
+      </c>
       <c r="E18" s="48"/>
       <c r="F18" s="48"/>
       <c r="G18" s="49"/>
@@ -4521,16 +4576,12 @@
       <c r="L18" s="52"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.4">
-      <c r="B19" s="46">
+      <c r="B19" s="46" t="str">
         <f>IF(タスク表[[#This Row],[作業内容]]="","",ROW()-ROW(タスク表[#Headers]))</f>
-        <v>15</v>
-      </c>
-      <c r="C19" s="44" t="s">
-        <v>29</v>
-      </c>
-      <c r="D19" s="47" t="s">
-        <v>136</v>
-      </c>
+        <v/>
+      </c>
+      <c r="C19" s="44"/>
+      <c r="D19" s="47"/>
       <c r="E19" s="48"/>
       <c r="F19" s="48"/>
       <c r="G19" s="49"/>
@@ -4544,14 +4595,12 @@
       <c r="L19" s="52"/>
     </row>
     <row r="20" spans="2:12" x14ac:dyDescent="0.4">
-      <c r="B20" s="46">
+      <c r="B20" s="46" t="str">
         <f>IF(タスク表[[#This Row],[作業内容]]="","",ROW()-ROW(タスク表[#Headers]))</f>
-        <v>16</v>
+        <v/>
       </c>
       <c r="C20" s="44"/>
-      <c r="D20" s="47" t="s">
-        <v>137</v>
-      </c>
+      <c r="D20" s="47"/>
       <c r="E20" s="48"/>
       <c r="F20" s="48"/>
       <c r="G20" s="49"/>
@@ -4603,16 +4652,12 @@
       <c r="L22" s="52"/>
     </row>
     <row r="23" spans="2:12" x14ac:dyDescent="0.4">
-      <c r="B23" s="46">
+      <c r="B23" s="46" t="str">
         <f>IF(タスク表[[#This Row],[作業内容]]="","",ROW()-ROW(タスク表[#Headers]))</f>
-        <v>19</v>
-      </c>
-      <c r="C23" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="D23" s="47" t="s">
-        <v>140</v>
-      </c>
+        <v/>
+      </c>
+      <c r="C23" s="44"/>
+      <c r="D23" s="47"/>
       <c r="E23" s="48"/>
       <c r="F23" s="48"/>
       <c r="G23" s="49"/>
@@ -4626,16 +4671,12 @@
       <c r="L23" s="52"/>
     </row>
     <row r="24" spans="2:12" x14ac:dyDescent="0.4">
-      <c r="B24" s="46">
+      <c r="B24" s="46" t="str">
         <f>IF(タスク表[[#This Row],[作業内容]]="","",ROW()-ROW(タスク表[#Headers]))</f>
-        <v>20</v>
-      </c>
-      <c r="C24" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="D24" s="47" t="s">
-        <v>141</v>
-      </c>
+        <v/>
+      </c>
+      <c r="C24" s="44"/>
+      <c r="D24" s="47"/>
       <c r="E24" s="48"/>
       <c r="F24" s="48"/>
       <c r="G24" s="49"/>
@@ -4649,14 +4690,12 @@
       <c r="L24" s="52"/>
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.4">
-      <c r="B25" s="46">
+      <c r="B25" s="46" t="str">
         <f>IF(タスク表[[#This Row],[作業内容]]="","",ROW()-ROW(タスク表[#Headers]))</f>
-        <v>21</v>
+        <v/>
       </c>
       <c r="C25" s="44"/>
-      <c r="D25" s="47" t="s">
-        <v>142</v>
-      </c>
+      <c r="D25" s="47"/>
       <c r="E25" s="48"/>
       <c r="F25" s="48"/>
       <c r="G25" s="49"/>
@@ -4674,13 +4713,13 @@
         <f>IF(タスク表[[#This Row],[作業内容]]="","",ROW()-ROW(タスク表[#Headers]))</f>
         <v>22</v>
       </c>
-      <c r="C26" s="44"/>
+      <c r="C26" s="44" t="s">
+        <v>29</v>
+      </c>
       <c r="D26" s="47" t="s">
-        <v>146</v>
-      </c>
-      <c r="E26" s="48" t="s">
-        <v>41</v>
-      </c>
+        <v>136</v>
+      </c>
+      <c r="E26" s="48"/>
       <c r="F26" s="48"/>
       <c r="G26" s="49"/>
       <c r="H26" s="49"/>
@@ -4693,12 +4732,14 @@
       <c r="L26" s="52"/>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.4">
-      <c r="B27" s="46" t="str">
+      <c r="B27" s="46">
         <f>IF(タスク表[[#This Row],[作業内容]]="","",ROW()-ROW(タスク表[#Headers]))</f>
-        <v/>
+        <v>23</v>
       </c>
       <c r="C27" s="44"/>
-      <c r="D27" s="47"/>
+      <c r="D27" s="47" t="s">
+        <v>137</v>
+      </c>
       <c r="E27" s="48"/>
       <c r="F27" s="48"/>
       <c r="G27" s="49"/>
@@ -4712,16 +4753,12 @@
       <c r="L27" s="52"/>
     </row>
     <row r="28" spans="2:12" x14ac:dyDescent="0.4">
-      <c r="B28" s="46">
+      <c r="B28" s="46" t="str">
         <f>IF(タスク表[[#This Row],[作業内容]]="","",ROW()-ROW(タスク表[#Headers]))</f>
-        <v>24</v>
-      </c>
-      <c r="C28" s="44" t="s">
-        <v>31</v>
-      </c>
-      <c r="D28" s="47" t="s">
-        <v>143</v>
-      </c>
+        <v/>
+      </c>
+      <c r="C28" s="44"/>
+      <c r="D28" s="47"/>
       <c r="E28" s="48"/>
       <c r="F28" s="48"/>
       <c r="G28" s="49"/>
@@ -4754,12 +4791,16 @@
       <c r="L29" s="52"/>
     </row>
     <row r="30" spans="2:12" x14ac:dyDescent="0.4">
-      <c r="B30" s="46" t="str">
+      <c r="B30" s="46">
         <f>IF(タスク表[[#This Row],[作業内容]]="","",ROW()-ROW(タスク表[#Headers]))</f>
-        <v/>
-      </c>
-      <c r="C30" s="44"/>
-      <c r="D30" s="47"/>
+        <v>26</v>
+      </c>
+      <c r="C30" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="D30" s="47" t="s">
+        <v>140</v>
+      </c>
       <c r="E30" s="48"/>
       <c r="F30" s="48"/>
       <c r="G30" s="49"/>
@@ -4773,12 +4814,16 @@
       <c r="L30" s="52"/>
     </row>
     <row r="31" spans="2:12" x14ac:dyDescent="0.4">
-      <c r="B31" s="46" t="str">
+      <c r="B31" s="46">
         <f>IF(タスク表[[#This Row],[作業内容]]="","",ROW()-ROW(タスク表[#Headers]))</f>
-        <v/>
-      </c>
-      <c r="C31" s="44"/>
-      <c r="D31" s="47"/>
+        <v>27</v>
+      </c>
+      <c r="C31" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="D31" s="47" t="s">
+        <v>141</v>
+      </c>
       <c r="E31" s="48"/>
       <c r="F31" s="48"/>
       <c r="G31" s="49"/>
@@ -4792,12 +4837,14 @@
       <c r="L31" s="52"/>
     </row>
     <row r="32" spans="2:12" x14ac:dyDescent="0.4">
-      <c r="B32" s="46" t="str">
+      <c r="B32" s="46">
         <f>IF(タスク表[[#This Row],[作業内容]]="","",ROW()-ROW(タスク表[#Headers]))</f>
-        <v/>
+        <v>28</v>
       </c>
       <c r="C32" s="44"/>
-      <c r="D32" s="47"/>
+      <c r="D32" s="47" t="s">
+        <v>142</v>
+      </c>
       <c r="E32" s="48"/>
       <c r="F32" s="48"/>
       <c r="G32" s="49"/>
@@ -4811,13 +4858,17 @@
       <c r="L32" s="52"/>
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.4">
-      <c r="B33" s="46" t="str">
+      <c r="B33" s="46">
         <f>IF(タスク表[[#This Row],[作業内容]]="","",ROW()-ROW(タスク表[#Headers]))</f>
-        <v/>
+        <v>29</v>
       </c>
       <c r="C33" s="44"/>
-      <c r="D33" s="47"/>
-      <c r="E33" s="48"/>
+      <c r="D33" s="47" t="s">
+        <v>146</v>
+      </c>
+      <c r="E33" s="48" t="s">
+        <v>41</v>
+      </c>
       <c r="F33" s="48"/>
       <c r="G33" s="49"/>
       <c r="H33" s="49"/>
@@ -4849,12 +4900,16 @@
       <c r="L34" s="52"/>
     </row>
     <row r="35" spans="2:12" x14ac:dyDescent="0.4">
-      <c r="B35" s="46" t="str">
+      <c r="B35" s="46">
         <f>IF(タスク表[[#This Row],[作業内容]]="","",ROW()-ROW(タスク表[#Headers]))</f>
-        <v/>
-      </c>
-      <c r="C35" s="44"/>
-      <c r="D35" s="47"/>
+        <v>31</v>
+      </c>
+      <c r="C35" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="D35" s="47" t="s">
+        <v>143</v>
+      </c>
       <c r="E35" s="48"/>
       <c r="F35" s="48"/>
       <c r="G35" s="49"/>
@@ -16575,29 +16630,40 @@
     </row>
   </sheetData>
   <phoneticPr fontId="6"/>
-  <conditionalFormatting sqref="B5:L7 B8:B10 E8:L10 B11:L16 B21:L1000 B17:B20 E17:L20">
-    <cfRule type="expression" dxfId="19" priority="1" stopIfTrue="1">
+  <conditionalFormatting sqref="B5:L7 B8:B10 E8:L10 B11:L16 E17:L18 B36:L1000 B17:B35 F19:L35">
+    <cfRule type="expression" dxfId="22" priority="1" stopIfTrue="1">
       <formula>AND($J5&lt;&gt;"",$J5=除外ST)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="18" priority="2" stopIfTrue="1">
+    <cfRule type="expression" dxfId="21" priority="2" stopIfTrue="1">
       <formula>AND($J5&lt;&gt;"",$J5=完了ST)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="17" priority="3" stopIfTrue="1">
+    <cfRule type="expression" dxfId="20" priority="3" stopIfTrue="1">
       <formula>$J5="作業中"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C13:D14">
-    <cfRule type="expression" dxfId="16" priority="11" stopIfTrue="1">
+    <cfRule type="expression" dxfId="19" priority="11" stopIfTrue="1">
       <formula>AND($J8&lt;&gt;"",$J8=除外ST)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="15" priority="12" stopIfTrue="1">
+    <cfRule type="expression" dxfId="18" priority="12" stopIfTrue="1">
       <formula>AND($J8&lt;&gt;"",$J8=完了ST)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="14" priority="13" stopIfTrue="1">
+    <cfRule type="expression" dxfId="17" priority="13" stopIfTrue="1">
       <formula>$J8="作業中"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E5:E1000">
+  <conditionalFormatting sqref="C26:D27">
+    <cfRule type="expression" dxfId="16" priority="17" stopIfTrue="1">
+      <formula>AND($J17&lt;&gt;"",$J17=除外ST)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="15" priority="18" stopIfTrue="1">
+      <formula>AND($J17&lt;&gt;"",$J17=完了ST)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="14" priority="19" stopIfTrue="1">
+      <formula>$J17="作業中"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E5:E18 E26:E1000">
     <cfRule type="expression" dxfId="13" priority="4" stopIfTrue="1">
       <formula>E5="S"</formula>
     </cfRule>
@@ -16613,21 +16679,18 @@
       <formula>AND(ISNUMBER(I5),I5&lt;0)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C19:D20">
-    <cfRule type="expression" dxfId="2" priority="17" stopIfTrue="1">
-      <formula>AND($J17&lt;&gt;"",$J17=除外ST)</formula>
+  <conditionalFormatting sqref="E26:E27 C28:E35">
+    <cfRule type="expression" dxfId="2" priority="23" stopIfTrue="1">
+      <formula>AND($J19&lt;&gt;"",$J19=除外ST)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="18" stopIfTrue="1">
-      <formula>AND($J17&lt;&gt;"",$J17=完了ST)</formula>
+    <cfRule type="expression" dxfId="1" priority="24" stopIfTrue="1">
+      <formula>AND($J19&lt;&gt;"",$J19=完了ST)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="19" stopIfTrue="1">
-      <formula>$J17="作業中"</formula>
+    <cfRule type="expression" dxfId="0" priority="25" stopIfTrue="1">
+      <formula>$J19="作業中"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="5">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E5:E1000" xr:uid="{029AB92C-5CA0-4F76-9790-7F4B331300FB}">
-      <formula1>優先度一覧</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F5:F1000" xr:uid="{40647F47-509E-46A8-8187-C0A1ADC86BC3}">
       <formula1>バージョン一覧</formula1>
     </dataValidation>
@@ -16637,8 +16700,11 @@
     <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="0以上の数値を入力してください" sqref="G5:H1000" xr:uid="{3EFE3393-D09C-4B29-BFD5-14DF7F410677}">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C5:C7 C11:C16 C19:C1000" xr:uid="{E6BBE5BD-7004-4694-85A6-704154467F57}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C5:C7 C11:C16 C26:C1000" xr:uid="{E6BBE5BD-7004-4694-85A6-704154467F57}">
       <formula1>カテゴリ一覧</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E5:E18 E26:E1000" xr:uid="{029AB92C-5CA0-4F76-9790-7F4B331300FB}">
+      <formula1>優先度一覧</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -16905,7 +16971,7 @@
       </c>
       <c r="AB7" s="36">
         <f t="shared" ref="AB7:AB14" ca="1" si="0">IF(AA7="","",AA7-TODAY())</f>
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AC7" s="36">
         <f ca="1">IF(AA7="","",MAX(0,NETWORKDAYS.INTL(TODAY(),AA7,週末区分,休日一覧)))</f>
@@ -17007,7 +17073,7 @@
       </c>
       <c r="AB8" s="36">
         <f t="shared" ca="1" si="0"/>
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="AC8" s="36">
         <f ca="1">IF(AA8="","",MAX(0,NETWORKDAYS.INTL(TODAY(),AA8,週末区分,休日一覧)))</f>
@@ -17109,7 +17175,7 @@
       </c>
       <c r="AB9" s="36">
         <f t="shared" ca="1" si="0"/>
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="AC9" s="36">
         <f ca="1">IF(AA9="","",MAX(0,NETWORKDAYS.INTL(TODAY(),AA9,週末区分,休日一覧)))</f>
@@ -17211,7 +17277,7 @@
       </c>
       <c r="AB10" s="36">
         <f t="shared" ca="1" si="0"/>
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AC10" s="36">
         <f ca="1">IF(AA10="","",MAX(0,NETWORKDAYS.INTL(TODAY(),AA10,週末区分,休日一覧)))</f>

--- a/進捗/コスト表_winter_2026.xlsx
+++ b/進捗/コスト表_winter_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2026_winter\進捗\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37908A3E-5579-40E1-8280-754BEA258A33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57543333-1590-4981-BEBB-9A0C503FCFBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{90270874-AD68-4987-AED5-115E189B84F1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{90270874-AD68-4987-AED5-115E189B84F1}"/>
   </bookViews>
   <sheets>
     <sheet name="集計" sheetId="1" r:id="rId1"/>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="164">
   <si>
     <t>設定</t>
   </si>
@@ -516,16 +516,6 @@
     <phoneticPr fontId="6"/>
   </si>
   <si>
-    <t>空中-&gt;地上のカメラワーク</t>
-    <rPh sb="0" eb="2">
-      <t>クウチュウ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>チジョウ</t>
-    </rPh>
-    <phoneticPr fontId="6"/>
-  </si>
-  <si>
     <t>敵のヒット状態を増やす</t>
     <rPh sb="0" eb="1">
       <t>テキ</t>
@@ -579,13 +569,6 @@
     <phoneticPr fontId="6"/>
   </si>
   <si>
-    <t>ステージ設計</t>
-    <rPh sb="4" eb="6">
-      <t>セッケイ</t>
-    </rPh>
-    <phoneticPr fontId="6"/>
-  </si>
-  <si>
     <t>ガード弾きのアニメーション、ステート追加</t>
     <rPh sb="3" eb="4">
       <t>ハジ</t>
@@ -624,13 +607,6 @@
     <phoneticPr fontId="6"/>
   </si>
   <si>
-    <t>ヒットストップ、タイムスケールのすべての調整</t>
-    <rPh sb="20" eb="22">
-      <t>チョウセイ</t>
-    </rPh>
-    <phoneticPr fontId="6"/>
-  </si>
-  <si>
     <t>壁キック、壁走りのやめる時間制限をつける</t>
     <rPh sb="0" eb="1">
       <t>カベ</t>
@@ -653,6 +629,158 @@
     </rPh>
     <rPh sb="2" eb="5">
       <t>ガイブカ</t>
+    </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>ヒットストップ、タイムスケールのすべての調整</t>
+  </si>
+  <si>
+    <t>ガードブレイク時のカメラ</t>
+    <rPh sb="7" eb="8">
+      <t>ジ</t>
+    </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>暗殺空中-&gt;地上のカメラワーク</t>
+    <rPh sb="0" eb="2">
+      <t>アンサツ</t>
+    </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>敵2体目</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>タイメ</t>
+    </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>敵2つ目の攻撃行動</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>メ</t>
+    </rPh>
+    <rPh sb="5" eb="9">
+      <t>コウゲキコウドウ</t>
+    </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>ボス</t>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>ボス実装</t>
+    <rPh sb="2" eb="4">
+      <t>ジッソウ</t>
+    </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>演出</t>
+    <rPh sb="0" eb="2">
+      <t>エンシュツ</t>
+    </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>登場時演出</t>
+    <rPh sb="0" eb="3">
+      <t>トウジョウジ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>エンシュツ</t>
+    </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>ボス撃破時の演出</t>
+    <rPh sb="2" eb="5">
+      <t>ゲキハジ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>エンシュツ</t>
+    </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>ステージ設計(デザイン</t>
+    <rPh sb="4" eb="6">
+      <t>セッケイ</t>
+    </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>ステージ設計(本配置</t>
+    <rPh sb="4" eb="6">
+      <t>セッケイ</t>
+    </rPh>
+    <rPh sb="7" eb="10">
+      <t>ホンハイチ</t>
+    </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>プレイヤーのシェーダー(内藤先生のやつ</t>
+    <rPh sb="12" eb="16">
+      <t>ナイトウセンセイ</t>
+    </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>フック</t>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>ずっと待機中だといろいろアニメーションがでるやつ</t>
+    <rPh sb="3" eb="6">
+      <t>タイキチュウ</t>
+    </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>剣の納刀、抜刀関連</t>
+    <rPh sb="0" eb="1">
+      <t>ケン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ノウトウ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>バットウ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>カンレン</t>
+    </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>必殺技の処理、m_isRavenを消す処理</t>
+    <rPh sb="0" eb="3">
+      <t>ヒッサツワザ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ショリ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>ケ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ショリ</t>
+    </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>playerのガード、パリィ追加もあり</t>
+    <rPh sb="14" eb="16">
+      <t>ツイカ</t>
     </rPh>
     <phoneticPr fontId="6"/>
   </si>
@@ -1093,30 +1221,7 @@
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="39">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFF2CC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF808080"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFE2EFDA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFA6A6A6"/>
-      </font>
-    </dxf>
+  <dxfs count="66">
     <dxf>
       <font>
         <color rgb="FFA6A6A6"/>
@@ -1185,6 +1290,213 @@
       </border>
     </dxf>
     <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFF2CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF808080"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE2EFDA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFA6A6A6"/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFF2CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF808080"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE2EFDA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFA6A6A6"/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFF2CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF808080"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE2EFDA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFA6A6A6"/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFF2CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF808080"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE2EFDA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFA6A6A6"/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFF2CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF808080"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE2EFDA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFA6A6A6"/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFF2CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF808080"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE2EFDA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFA6A6A6"/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFF2CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF808080"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE2EFDA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFA6A6A6"/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFF2CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF808080"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE2EFDA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFA6A6A6"/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFF2CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF808080"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE2EFDA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFA6A6A6"/>
+      </font>
+    </dxf>
+    <dxf>
       <font>
         <color rgb="FF0070C0"/>
       </font>
@@ -1192,6 +1504,29 @@
     <dxf>
       <font>
         <color rgb="FFC00000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFF2CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF808080"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE2EFDA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFA6A6A6"/>
       </font>
     </dxf>
     <dxf>
@@ -1756,24 +2091,24 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3A2567DA-ED67-436A-BAF7-D8D91E4E00C2}" name="タスク表" displayName="タスク表" ref="B4:L53" totalsRowShown="0" headerRowDxfId="38" dataDxfId="37" tableBorderDxfId="36">
-  <autoFilter ref="B4:L53" xr:uid="{3A2567DA-ED67-436A-BAF7-D8D91E4E00C2}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3A2567DA-ED67-436A-BAF7-D8D91E4E00C2}" name="タスク表" displayName="タスク表" ref="B4:L57" totalsRowShown="0" headerRowDxfId="65" dataDxfId="64" tableBorderDxfId="63">
+  <autoFilter ref="B4:L57" xr:uid="{3A2567DA-ED67-436A-BAF7-D8D91E4E00C2}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{F383ED7B-CAB4-46F1-AC7C-023467A46D88}" name="No" dataDxfId="35">
+    <tableColumn id="1" xr3:uid="{F383ED7B-CAB4-46F1-AC7C-023467A46D88}" name="No" dataDxfId="62">
       <calculatedColumnFormula>IF(タスク表[[#This Row],[作業内容]]="","",ROW()-ROW(タスク表[#Headers]))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{7EF03FBB-5A01-49E5-9341-0CD4CA09848E}" name="カテゴリ" dataDxfId="34"/>
-    <tableColumn id="3" xr3:uid="{48466042-E58A-4D97-AC9B-D6FED5F46A1F}" name="作業内容" dataDxfId="33"/>
-    <tableColumn id="4" xr3:uid="{65680DBB-31AB-43B9-BFA7-0526EC96D22F}" name="優先度" dataDxfId="32"/>
-    <tableColumn id="5" xr3:uid="{D7E12594-DF8F-4044-8B36-8EAC7E3BB4E5}" name="バージョン" dataDxfId="31"/>
-    <tableColumn id="6" xr3:uid="{BAF69BB2-2D96-4276-B8FA-8A5B618ED05F}" name="見積コスト" dataDxfId="30"/>
-    <tableColumn id="7" xr3:uid="{0A021283-FCFD-447B-98BD-F53EF31318C1}" name="実コスト" dataDxfId="29"/>
-    <tableColumn id="8" xr3:uid="{75B48E43-3BBD-4AF9-A1B3-D350673AB994}" name="差分" dataDxfId="28">
+    <tableColumn id="2" xr3:uid="{7EF03FBB-5A01-49E5-9341-0CD4CA09848E}" name="カテゴリ" dataDxfId="61"/>
+    <tableColumn id="3" xr3:uid="{48466042-E58A-4D97-AC9B-D6FED5F46A1F}" name="作業内容" dataDxfId="60"/>
+    <tableColumn id="4" xr3:uid="{65680DBB-31AB-43B9-BFA7-0526EC96D22F}" name="優先度" dataDxfId="59"/>
+    <tableColumn id="5" xr3:uid="{D7E12594-DF8F-4044-8B36-8EAC7E3BB4E5}" name="バージョン" dataDxfId="58"/>
+    <tableColumn id="6" xr3:uid="{BAF69BB2-2D96-4276-B8FA-8A5B618ED05F}" name="見積コスト" dataDxfId="57"/>
+    <tableColumn id="7" xr3:uid="{0A021283-FCFD-447B-98BD-F53EF31318C1}" name="実コスト" dataDxfId="56"/>
+    <tableColumn id="8" xr3:uid="{75B48E43-3BBD-4AF9-A1B3-D350673AB994}" name="差分" dataDxfId="55">
       <calculatedColumnFormula>IF(OR(タスク表[[#This Row],[見積コスト]]="",タスク表[[#This Row],[実コスト]]=""),"",タスク表[[#This Row],[実コスト]]-タスク表[[#This Row],[見積コスト]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{7B1D7DAB-403C-43FB-B066-5FF4BD411B5A}" name="ステータス" dataDxfId="27"/>
-    <tableColumn id="10" xr3:uid="{D6F46B68-27C3-483A-8CAC-834EC0598F40}" name="完了日" dataDxfId="26"/>
-    <tableColumn id="11" xr3:uid="{40889AD2-F644-4454-99EC-D71EF37CD54A}" name="備考" dataDxfId="25"/>
+    <tableColumn id="9" xr3:uid="{7B1D7DAB-403C-43FB-B066-5FF4BD411B5A}" name="ステータス" dataDxfId="54"/>
+    <tableColumn id="10" xr3:uid="{D6F46B68-27C3-483A-8CAC-834EC0598F40}" name="完了日" dataDxfId="53"/>
+    <tableColumn id="11" xr3:uid="{40889AD2-F644-4454-99EC-D71EF37CD54A}" name="備考" dataDxfId="52"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2129,7 +2464,7 @@
       </c>
       <c r="C5" s="17">
         <f ca="1">TODAY()</f>
-        <v>46307</v>
+        <v>46313</v>
       </c>
       <c r="D5" s="3"/>
     </row>
@@ -2209,7 +2544,7 @@
       </c>
       <c r="C12" s="20">
         <f ca="1">MAX(0,NETWORKDAYS.INTL(開始日,TODAY(),週末区分,休日一覧))</f>
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>87</v>
@@ -2245,7 +2580,7 @@
       </c>
       <c r="C15" s="20">
         <f ca="1">IF(C14="","",MAX(0,NETWORKDAYS.INTL(TODAY(),C14,週末区分,休日一覧)))</f>
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>93</v>
@@ -2269,7 +2604,7 @@
       </c>
       <c r="C17" s="18">
         <f ca="1">IF(C15="","",作業時間*C15-C9)</f>
-        <v>680</v>
+        <v>640</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>97</v>
@@ -2362,7 +2697,7 @@
       </c>
       <c r="J23" s="28">
         <f ca="1">IF(C23="","",MAX(0,NETWORKDAYS.INTL(TODAY(),C23,週末区分,休日一覧)))</f>
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="K23" s="24">
         <f t="shared" ref="K23:K30" ca="1" si="2">IF(OR(J23="",N(J23)=0),"",G23/J23)</f>
@@ -2370,7 +2705,7 @@
       </c>
       <c r="L23" s="24">
         <f t="shared" ref="L23:L30" ca="1" si="3">IF(J23="","",作業時間*J23-G23)</f>
-        <v>192</v>
+        <v>152</v>
       </c>
     </row>
     <row r="24" spans="2:12" x14ac:dyDescent="0.4">
@@ -2408,7 +2743,7 @@
       </c>
       <c r="J24" s="28">
         <f ca="1">IF(C24="","",MAX(0,NETWORKDAYS.INTL(TODAY(),C24,週末区分,休日一覧)))</f>
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="K24" s="24">
         <f t="shared" ca="1" si="2"/>
@@ -2416,7 +2751,7 @@
       </c>
       <c r="L24" s="24">
         <f t="shared" ca="1" si="3"/>
-        <v>384</v>
+        <v>344</v>
       </c>
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.4">
@@ -2454,7 +2789,7 @@
       </c>
       <c r="J25" s="28">
         <f ca="1">IF(C25="","",MAX(0,NETWORKDAYS.INTL(TODAY(),C25,週末区分,休日一覧)))</f>
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="K25" s="24">
         <f t="shared" ca="1" si="2"/>
@@ -2462,7 +2797,7 @@
       </c>
       <c r="L25" s="24">
         <f t="shared" ca="1" si="3"/>
-        <v>568</v>
+        <v>528</v>
       </c>
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.4">
@@ -2500,7 +2835,7 @@
       </c>
       <c r="J26" s="28">
         <f ca="1">IF(C26="","",MAX(0,NETWORKDAYS.INTL(TODAY(),C26,週末区分,休日一覧)))</f>
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="K26" s="24">
         <f t="shared" ca="1" si="2"/>
@@ -2508,7 +2843,7 @@
       </c>
       <c r="L26" s="24">
         <f t="shared" ca="1" si="3"/>
-        <v>680</v>
+        <v>640</v>
       </c>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.4">
@@ -2837,7 +3172,7 @@
       </c>
       <c r="P36" s="5">
         <f>IF(K36="","",COUNTIFS(タスク表[優先度],K36,タスク表[作業内容],"&lt;&gt;",タスク表[ステータス],"&lt;&gt;"&amp;除外ST))</f>
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="37" spans="2:16" x14ac:dyDescent="0.4">
@@ -2895,7 +3230,7 @@
       </c>
       <c r="P37" s="5">
         <f>IF(K37="","",COUNTIFS(タスク表[優先度],K37,タスク表[作業内容],"&lt;&gt;",タスク表[ステータス],"&lt;&gt;"&amp;除外ST))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="38" spans="2:16" x14ac:dyDescent="0.4">
@@ -2953,7 +3288,7 @@
       </c>
       <c r="P38" s="5">
         <f>IF(K38="","",COUNTIFS(タスク表[優先度],K38,タスク表[作業内容],"&lt;&gt;",タスク表[ステータス],"&lt;&gt;"&amp;除外ST))</f>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="39" spans="2:16" x14ac:dyDescent="0.4">
@@ -4068,11 +4403,11 @@
       </c>
       <c r="H66" s="21">
         <f>IF(FALSE,"",COUNTIFS(タスク表[カテゴリ],"",タスク表[作業内容],"&lt;&gt;",タスク表[ステータス],"&lt;&gt;"&amp;除外ST))</f>
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="I66" s="21">
         <f>IF(FALSE,"",COUNTIFS(タスク表[カテゴリ],"",タスク表[作業内容],"&lt;&gt;",タスク表[ステータス],完了ST))</f>
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -4092,7 +4427,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C17">
-    <cfRule type="expression" dxfId="24" priority="2" stopIfTrue="1">
+    <cfRule type="expression" dxfId="51" priority="2" stopIfTrue="1">
       <formula>AND(ISNUMBER(C17),C17&lt;0)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4125,7 +4460,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L23:L30">
-    <cfRule type="expression" dxfId="23" priority="4" stopIfTrue="1">
+    <cfRule type="expression" dxfId="50" priority="4" stopIfTrue="1">
       <formula>AND(ISNUMBER(L23),L23&lt;0)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4210,7 +4545,7 @@
   <sheetPr>
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="B1:L1000"/>
+  <dimension ref="B1:L1004"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="2.625" style="1" customWidth="1"/>
@@ -4315,7 +4650,9 @@
         <f>IF(OR(タスク表[[#This Row],[見積コスト]]="",タスク表[[#This Row],[実コスト]]=""),"",タスク表[[#This Row],[実コスト]]-タスク表[[#This Row],[見積コスト]])</f>
         <v/>
       </c>
-      <c r="J6" s="48"/>
+      <c r="J6" s="48" t="s">
+        <v>11</v>
+      </c>
       <c r="K6" s="51"/>
       <c r="L6" s="52"/>
     </row>
@@ -4329,7 +4666,7 @@
         <v>135</v>
       </c>
       <c r="E7" s="48" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F7" s="48"/>
       <c r="G7" s="49"/>
@@ -4349,9 +4686,11 @@
       </c>
       <c r="C8" s="44"/>
       <c r="D8" s="47" t="s">
-        <v>144</v>
-      </c>
-      <c r="E8" s="48"/>
+        <v>142</v>
+      </c>
+      <c r="E8" s="48" t="s">
+        <v>41</v>
+      </c>
       <c r="F8" s="48"/>
       <c r="G8" s="49"/>
       <c r="H8" s="49"/>
@@ -4359,7 +4698,9 @@
         <f>IF(OR(タスク表[[#This Row],[見積コスト]]="",タスク表[[#This Row],[実コスト]]=""),"",タスク表[[#This Row],[実コスト]]-タスク表[[#This Row],[見積コスト]])</f>
         <v/>
       </c>
-      <c r="J8" s="48"/>
+      <c r="J8" s="48" t="s">
+        <v>11</v>
+      </c>
       <c r="K8" s="51"/>
       <c r="L8" s="52"/>
     </row>
@@ -4370,9 +4711,11 @@
       </c>
       <c r="C9" s="44"/>
       <c r="D9" s="47" t="s">
-        <v>147</v>
-      </c>
-      <c r="E9" s="48"/>
+        <v>144</v>
+      </c>
+      <c r="E9" s="48" t="s">
+        <v>41</v>
+      </c>
       <c r="F9" s="48"/>
       <c r="G9" s="49"/>
       <c r="H9" s="49"/>
@@ -4385,13 +4728,17 @@
       <c r="L9" s="52"/>
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.4">
-      <c r="B10" s="46" t="str">
+      <c r="B10" s="46">
         <f>IF(タスク表[[#This Row],[作業内容]]="","",ROW()-ROW(タスク表[#Headers]))</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="C10" s="44"/>
-      <c r="D10" s="47"/>
-      <c r="E10" s="48"/>
+      <c r="D10" s="47" t="s">
+        <v>158</v>
+      </c>
+      <c r="E10" s="48" t="s">
+        <v>41</v>
+      </c>
       <c r="F10" s="48"/>
       <c r="G10" s="49"/>
       <c r="H10" s="49"/>
@@ -4404,13 +4751,17 @@
       <c r="L10" s="52"/>
     </row>
     <row r="11" spans="2:12" x14ac:dyDescent="0.4">
-      <c r="B11" s="46" t="str">
+      <c r="B11" s="46">
         <f>IF(タスク表[[#This Row],[作業内容]]="","",ROW()-ROW(タスク表[#Headers]))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="C11" s="44"/>
-      <c r="D11" s="47"/>
-      <c r="E11" s="48"/>
+      <c r="D11" s="47" t="s">
+        <v>159</v>
+      </c>
+      <c r="E11" s="48" t="s">
+        <v>45</v>
+      </c>
       <c r="F11" s="48"/>
       <c r="G11" s="49"/>
       <c r="H11" s="49"/>
@@ -4423,12 +4774,14 @@
       <c r="L11" s="52"/>
     </row>
     <row r="12" spans="2:12" x14ac:dyDescent="0.4">
-      <c r="B12" s="46" t="str">
+      <c r="B12" s="46">
         <f>IF(タスク表[[#This Row],[作業内容]]="","",ROW()-ROW(タスク表[#Headers]))</f>
-        <v/>
+        <v>8</v>
       </c>
       <c r="C12" s="44"/>
-      <c r="D12" s="47"/>
+      <c r="D12" s="47" t="s">
+        <v>160</v>
+      </c>
       <c r="E12" s="48"/>
       <c r="F12" s="48"/>
       <c r="G12" s="49"/>
@@ -4446,11 +4799,9 @@
         <f>IF(タスク表[[#This Row],[作業内容]]="","",ROW()-ROW(タスク表[#Headers]))</f>
         <v>9</v>
       </c>
-      <c r="C13" s="44" t="s">
-        <v>28</v>
-      </c>
+      <c r="C13" s="44"/>
       <c r="D13" s="47" t="s">
-        <v>133</v>
+        <v>161</v>
       </c>
       <c r="E13" s="48"/>
       <c r="F13" s="48"/>
@@ -4460,9 +4811,7 @@
         <f>IF(OR(タスク表[[#This Row],[見積コスト]]="",タスク表[[#This Row],[実コスト]]=""),"",タスク表[[#This Row],[実コスト]]-タスク表[[#This Row],[見積コスト]])</f>
         <v/>
       </c>
-      <c r="J13" s="48" t="s">
-        <v>11</v>
-      </c>
+      <c r="J13" s="48"/>
       <c r="K13" s="51"/>
       <c r="L13" s="52"/>
     </row>
@@ -4473,7 +4822,7 @@
       </c>
       <c r="C14" s="44"/>
       <c r="D14" s="47" t="s">
-        <v>134</v>
+        <v>163</v>
       </c>
       <c r="E14" s="48"/>
       <c r="F14" s="48"/>
@@ -4483,21 +4832,17 @@
         <f>IF(OR(タスク表[[#This Row],[見積コスト]]="",タスク表[[#This Row],[実コスト]]=""),"",タスク表[[#This Row],[実コスト]]-タスク表[[#This Row],[見積コスト]])</f>
         <v/>
       </c>
-      <c r="J14" s="48" t="s">
-        <v>11</v>
-      </c>
+      <c r="J14" s="48"/>
       <c r="K14" s="51"/>
       <c r="L14" s="52"/>
     </row>
     <row r="15" spans="2:12" x14ac:dyDescent="0.4">
-      <c r="B15" s="46">
+      <c r="B15" s="46" t="str">
         <f>IF(タスク表[[#This Row],[作業内容]]="","",ROW()-ROW(タスク表[#Headers]))</f>
-        <v>11</v>
+        <v/>
       </c>
       <c r="C15" s="44"/>
-      <c r="D15" s="47" t="s">
-        <v>138</v>
-      </c>
+      <c r="D15" s="47"/>
       <c r="E15" s="48"/>
       <c r="F15" s="48"/>
       <c r="G15" s="49"/>
@@ -4506,9 +4851,7 @@
         <f>IF(OR(タスク表[[#This Row],[見積コスト]]="",タスク表[[#This Row],[実コスト]]=""),"",タスク表[[#This Row],[実コスト]]-タスク表[[#This Row],[見積コスト]])</f>
         <v/>
       </c>
-      <c r="J15" s="48" t="s">
-        <v>51</v>
-      </c>
+      <c r="J15" s="48"/>
       <c r="K15" s="51"/>
       <c r="L15" s="52"/>
     </row>
@@ -4519,7 +4862,7 @@
       </c>
       <c r="C16" s="44"/>
       <c r="D16" s="47" t="s">
-        <v>139</v>
+        <v>162</v>
       </c>
       <c r="E16" s="48"/>
       <c r="F16" s="48"/>
@@ -4533,14 +4876,16 @@
       <c r="K16" s="51"/>
       <c r="L16" s="52"/>
     </row>
-    <row r="17" spans="2:12" ht="28.5" x14ac:dyDescent="0.4">
+    <row r="17" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B17" s="46">
         <f>IF(タスク表[[#This Row],[作業内容]]="","",ROW()-ROW(タスク表[#Headers]))</f>
         <v>13</v>
       </c>
-      <c r="C17" s="44"/>
+      <c r="C17" s="44" t="s">
+        <v>28</v>
+      </c>
       <c r="D17" s="47" t="s">
-        <v>145</v>
+        <v>133</v>
       </c>
       <c r="E17" s="48"/>
       <c r="F17" s="48"/>
@@ -4550,7 +4895,9 @@
         <f>IF(OR(タスク表[[#This Row],[見積コスト]]="",タスク表[[#This Row],[実コスト]]=""),"",タスク表[[#This Row],[実コスト]]-タスク表[[#This Row],[見積コスト]])</f>
         <v/>
       </c>
-      <c r="J17" s="48"/>
+      <c r="J17" s="48" t="s">
+        <v>11</v>
+      </c>
       <c r="K17" s="51"/>
       <c r="L17" s="52"/>
     </row>
@@ -4561,7 +4908,7 @@
       </c>
       <c r="C18" s="44"/>
       <c r="D18" s="47" t="s">
-        <v>148</v>
+        <v>134</v>
       </c>
       <c r="E18" s="48"/>
       <c r="F18" s="48"/>
@@ -4571,18 +4918,24 @@
         <f>IF(OR(タスク表[[#This Row],[見積コスト]]="",タスク表[[#This Row],[実コスト]]=""),"",タスク表[[#This Row],[実コスト]]-タスク表[[#This Row],[見積コスト]])</f>
         <v/>
       </c>
-      <c r="J18" s="48"/>
+      <c r="J18" s="48" t="s">
+        <v>11</v>
+      </c>
       <c r="K18" s="51"/>
       <c r="L18" s="52"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.4">
-      <c r="B19" s="46" t="str">
+      <c r="B19" s="46">
         <f>IF(タスク表[[#This Row],[作業内容]]="","",ROW()-ROW(タスク表[#Headers]))</f>
-        <v/>
+        <v>15</v>
       </c>
       <c r="C19" s="44"/>
-      <c r="D19" s="47"/>
-      <c r="E19" s="48"/>
+      <c r="D19" s="47" t="s">
+        <v>137</v>
+      </c>
+      <c r="E19" s="48" t="s">
+        <v>41</v>
+      </c>
       <c r="F19" s="48"/>
       <c r="G19" s="49"/>
       <c r="H19" s="49"/>
@@ -4590,18 +4943,24 @@
         <f>IF(OR(タスク表[[#This Row],[見積コスト]]="",タスク表[[#This Row],[実コスト]]=""),"",タスク表[[#This Row],[実コスト]]-タスク表[[#This Row],[見積コスト]])</f>
         <v/>
       </c>
-      <c r="J19" s="48"/>
+      <c r="J19" s="48" t="s">
+        <v>51</v>
+      </c>
       <c r="K19" s="51"/>
       <c r="L19" s="52"/>
     </row>
     <row r="20" spans="2:12" x14ac:dyDescent="0.4">
-      <c r="B20" s="46" t="str">
+      <c r="B20" s="46">
         <f>IF(タスク表[[#This Row],[作業内容]]="","",ROW()-ROW(タスク表[#Headers]))</f>
-        <v/>
+        <v>16</v>
       </c>
       <c r="C20" s="44"/>
-      <c r="D20" s="47"/>
-      <c r="E20" s="48"/>
+      <c r="D20" s="47" t="s">
+        <v>138</v>
+      </c>
+      <c r="E20" s="48" t="s">
+        <v>43</v>
+      </c>
       <c r="F20" s="48"/>
       <c r="G20" s="49"/>
       <c r="H20" s="49"/>
@@ -4613,14 +4972,18 @@
       <c r="K20" s="51"/>
       <c r="L20" s="52"/>
     </row>
-    <row r="21" spans="2:12" x14ac:dyDescent="0.4">
-      <c r="B21" s="46" t="str">
+    <row r="21" spans="2:12" ht="28.5" x14ac:dyDescent="0.4">
+      <c r="B21" s="46">
         <f>IF(タスク表[[#This Row],[作業内容]]="","",ROW()-ROW(タスク表[#Headers]))</f>
-        <v/>
+        <v>17</v>
       </c>
       <c r="C21" s="44"/>
-      <c r="D21" s="47"/>
-      <c r="E21" s="48"/>
+      <c r="D21" s="47" t="s">
+        <v>143</v>
+      </c>
+      <c r="E21" s="48" t="s">
+        <v>41</v>
+      </c>
       <c r="F21" s="48"/>
       <c r="G21" s="49"/>
       <c r="H21" s="49"/>
@@ -4633,12 +4996,14 @@
       <c r="L21" s="52"/>
     </row>
     <row r="22" spans="2:12" x14ac:dyDescent="0.4">
-      <c r="B22" s="46" t="str">
+      <c r="B22" s="46">
         <f>IF(タスク表[[#This Row],[作業内容]]="","",ROW()-ROW(タスク表[#Headers]))</f>
-        <v/>
+        <v>18</v>
       </c>
       <c r="C22" s="44"/>
-      <c r="D22" s="47"/>
+      <c r="D22" s="47" t="s">
+        <v>145</v>
+      </c>
       <c r="E22" s="48"/>
       <c r="F22" s="48"/>
       <c r="G22" s="49"/>
@@ -4647,18 +5012,24 @@
         <f>IF(OR(タスク表[[#This Row],[見積コスト]]="",タスク表[[#This Row],[実コスト]]=""),"",タスク表[[#This Row],[実コスト]]-タスク表[[#This Row],[見積コスト]])</f>
         <v/>
       </c>
-      <c r="J22" s="48"/>
+      <c r="J22" s="48" t="s">
+        <v>11</v>
+      </c>
       <c r="K22" s="51"/>
       <c r="L22" s="52"/>
     </row>
     <row r="23" spans="2:12" x14ac:dyDescent="0.4">
-      <c r="B23" s="46" t="str">
+      <c r="B23" s="46">
         <f>IF(タスク表[[#This Row],[作業内容]]="","",ROW()-ROW(タスク表[#Headers]))</f>
-        <v/>
+        <v>19</v>
       </c>
       <c r="C23" s="44"/>
-      <c r="D23" s="47"/>
-      <c r="E23" s="48"/>
+      <c r="D23" s="47" t="s">
+        <v>149</v>
+      </c>
+      <c r="E23" s="48" t="s">
+        <v>41</v>
+      </c>
       <c r="F23" s="48"/>
       <c r="G23" s="49"/>
       <c r="H23" s="49"/>
@@ -4671,13 +5042,17 @@
       <c r="L23" s="52"/>
     </row>
     <row r="24" spans="2:12" x14ac:dyDescent="0.4">
-      <c r="B24" s="46" t="str">
+      <c r="B24" s="46">
         <f>IF(タスク表[[#This Row],[作業内容]]="","",ROW()-ROW(タスク表[#Headers]))</f>
-        <v/>
+        <v>20</v>
       </c>
       <c r="C24" s="44"/>
-      <c r="D24" s="47"/>
-      <c r="E24" s="48"/>
+      <c r="D24" s="47" t="s">
+        <v>150</v>
+      </c>
+      <c r="E24" s="48" t="s">
+        <v>41</v>
+      </c>
       <c r="F24" s="48"/>
       <c r="G24" s="49"/>
       <c r="H24" s="49"/>
@@ -4690,13 +5065,19 @@
       <c r="L24" s="52"/>
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.4">
-      <c r="B25" s="46" t="str">
+      <c r="B25" s="46">
         <f>IF(タスク表[[#This Row],[作業内容]]="","",ROW()-ROW(タスク表[#Headers]))</f>
-        <v/>
-      </c>
-      <c r="C25" s="44"/>
-      <c r="D25" s="47"/>
-      <c r="E25" s="48"/>
+        <v>21</v>
+      </c>
+      <c r="C25" s="44" t="s">
+        <v>151</v>
+      </c>
+      <c r="D25" s="47" t="s">
+        <v>152</v>
+      </c>
+      <c r="E25" s="48" t="s">
+        <v>41</v>
+      </c>
       <c r="F25" s="48"/>
       <c r="G25" s="49"/>
       <c r="H25" s="49"/>
@@ -4709,16 +5090,12 @@
       <c r="L25" s="52"/>
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.4">
-      <c r="B26" s="46">
+      <c r="B26" s="46" t="str">
         <f>IF(タスク表[[#This Row],[作業内容]]="","",ROW()-ROW(タスク表[#Headers]))</f>
-        <v>22</v>
-      </c>
-      <c r="C26" s="44" t="s">
-        <v>29</v>
-      </c>
-      <c r="D26" s="47" t="s">
-        <v>136</v>
-      </c>
+        <v/>
+      </c>
+      <c r="C26" s="44"/>
+      <c r="D26" s="47"/>
       <c r="E26" s="48"/>
       <c r="F26" s="48"/>
       <c r="G26" s="49"/>
@@ -4736,11 +5113,15 @@
         <f>IF(タスク表[[#This Row],[作業内容]]="","",ROW()-ROW(タスク表[#Headers]))</f>
         <v>23</v>
       </c>
-      <c r="C27" s="44"/>
+      <c r="C27" s="44" t="s">
+        <v>29</v>
+      </c>
       <c r="D27" s="47" t="s">
-        <v>137</v>
-      </c>
-      <c r="E27" s="48"/>
+        <v>136</v>
+      </c>
+      <c r="E27" s="48" t="s">
+        <v>41</v>
+      </c>
       <c r="F27" s="48"/>
       <c r="G27" s="49"/>
       <c r="H27" s="49"/>
@@ -4748,18 +5129,24 @@
         <f>IF(OR(タスク表[[#This Row],[見積コスト]]="",タスク表[[#This Row],[実コスト]]=""),"",タスク表[[#This Row],[実コスト]]-タスク表[[#This Row],[見積コスト]])</f>
         <v/>
       </c>
-      <c r="J27" s="48"/>
+      <c r="J27" s="48" t="s">
+        <v>50</v>
+      </c>
       <c r="K27" s="51"/>
       <c r="L27" s="52"/>
     </row>
     <row r="28" spans="2:12" x14ac:dyDescent="0.4">
-      <c r="B28" s="46" t="str">
+      <c r="B28" s="46">
         <f>IF(タスク表[[#This Row],[作業内容]]="","",ROW()-ROW(タスク表[#Headers]))</f>
-        <v/>
+        <v>24</v>
       </c>
       <c r="C28" s="44"/>
-      <c r="D28" s="47"/>
-      <c r="E28" s="48"/>
+      <c r="D28" s="47" t="s">
+        <v>148</v>
+      </c>
+      <c r="E28" s="48" t="s">
+        <v>45</v>
+      </c>
       <c r="F28" s="48"/>
       <c r="G28" s="49"/>
       <c r="H28" s="49"/>
@@ -4767,18 +5154,24 @@
         <f>IF(OR(タスク表[[#This Row],[見積コスト]]="",タスク表[[#This Row],[実コスト]]=""),"",タスク表[[#This Row],[実コスト]]-タスク表[[#This Row],[見積コスト]])</f>
         <v/>
       </c>
-      <c r="J28" s="48"/>
+      <c r="J28" s="48" t="s">
+        <v>50</v>
+      </c>
       <c r="K28" s="51"/>
       <c r="L28" s="52"/>
     </row>
     <row r="29" spans="2:12" x14ac:dyDescent="0.4">
-      <c r="B29" s="46" t="str">
+      <c r="B29" s="46">
         <f>IF(タスク表[[#This Row],[作業内容]]="","",ROW()-ROW(タスク表[#Headers]))</f>
-        <v/>
+        <v>25</v>
       </c>
       <c r="C29" s="44"/>
-      <c r="D29" s="47"/>
-      <c r="E29" s="48"/>
+      <c r="D29" s="47" t="s">
+        <v>147</v>
+      </c>
+      <c r="E29" s="48" t="s">
+        <v>41</v>
+      </c>
       <c r="F29" s="48"/>
       <c r="G29" s="49"/>
       <c r="H29" s="49"/>
@@ -4791,16 +5184,12 @@
       <c r="L29" s="52"/>
     </row>
     <row r="30" spans="2:12" x14ac:dyDescent="0.4">
-      <c r="B30" s="46">
+      <c r="B30" s="46" t="str">
         <f>IF(タスク表[[#This Row],[作業内容]]="","",ROW()-ROW(タスク表[#Headers]))</f>
-        <v>26</v>
-      </c>
-      <c r="C30" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="D30" s="47" t="s">
-        <v>140</v>
-      </c>
+        <v/>
+      </c>
+      <c r="C30" s="44"/>
+      <c r="D30" s="47"/>
       <c r="E30" s="48"/>
       <c r="F30" s="48"/>
       <c r="G30" s="49"/>
@@ -4819,12 +5208,14 @@
         <v>27</v>
       </c>
       <c r="C31" s="44" t="s">
-        <v>36</v>
+        <v>153</v>
       </c>
       <c r="D31" s="47" t="s">
-        <v>141</v>
-      </c>
-      <c r="E31" s="48"/>
+        <v>154</v>
+      </c>
+      <c r="E31" s="48" t="s">
+        <v>43</v>
+      </c>
       <c r="F31" s="48"/>
       <c r="G31" s="49"/>
       <c r="H31" s="49"/>
@@ -4843,9 +5234,11 @@
       </c>
       <c r="C32" s="44"/>
       <c r="D32" s="47" t="s">
-        <v>142</v>
-      </c>
-      <c r="E32" s="48"/>
+        <v>155</v>
+      </c>
+      <c r="E32" s="48" t="s">
+        <v>43</v>
+      </c>
       <c r="F32" s="48"/>
       <c r="G32" s="49"/>
       <c r="H32" s="49"/>
@@ -4858,17 +5251,13 @@
       <c r="L32" s="52"/>
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.4">
-      <c r="B33" s="46">
+      <c r="B33" s="46" t="str">
         <f>IF(タスク表[[#This Row],[作業内容]]="","",ROW()-ROW(タスク表[#Headers]))</f>
-        <v>29</v>
+        <v/>
       </c>
       <c r="C33" s="44"/>
-      <c r="D33" s="47" t="s">
-        <v>146</v>
-      </c>
-      <c r="E33" s="48" t="s">
-        <v>41</v>
-      </c>
+      <c r="D33" s="47"/>
+      <c r="E33" s="48"/>
       <c r="F33" s="48"/>
       <c r="G33" s="49"/>
       <c r="H33" s="49"/>
@@ -4900,16 +5289,12 @@
       <c r="L34" s="52"/>
     </row>
     <row r="35" spans="2:12" x14ac:dyDescent="0.4">
-      <c r="B35" s="46">
+      <c r="B35" s="46" t="str">
         <f>IF(タスク表[[#This Row],[作業内容]]="","",ROW()-ROW(タスク表[#Headers]))</f>
-        <v>31</v>
-      </c>
-      <c r="C35" s="44" t="s">
-        <v>31</v>
-      </c>
-      <c r="D35" s="47" t="s">
-        <v>143</v>
-      </c>
+        <v/>
+      </c>
+      <c r="C35" s="44"/>
+      <c r="D35" s="47"/>
       <c r="E35" s="48"/>
       <c r="F35" s="48"/>
       <c r="G35" s="49"/>
@@ -4980,12 +5365,16 @@
       <c r="L38" s="52"/>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.4">
-      <c r="B39" s="46" t="str">
+      <c r="B39" s="46">
         <f>IF(タスク表[[#This Row],[作業内容]]="","",ROW()-ROW(タスク表[#Headers]))</f>
-        <v/>
-      </c>
-      <c r="C39" s="44"/>
-      <c r="D39" s="47"/>
+        <v>35</v>
+      </c>
+      <c r="C39" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="D39" s="47" t="s">
+        <v>139</v>
+      </c>
       <c r="E39" s="48"/>
       <c r="F39" s="48"/>
       <c r="G39" s="49"/>
@@ -4999,12 +5388,16 @@
       <c r="L39" s="52"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.4">
-      <c r="B40" s="46" t="str">
+      <c r="B40" s="46">
         <f>IF(タスク表[[#This Row],[作業内容]]="","",ROW()-ROW(タスク表[#Headers]))</f>
-        <v/>
-      </c>
-      <c r="C40" s="44"/>
-      <c r="D40" s="47"/>
+        <v>36</v>
+      </c>
+      <c r="C40" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="D40" s="47" t="s">
+        <v>140</v>
+      </c>
       <c r="E40" s="48"/>
       <c r="F40" s="48"/>
       <c r="G40" s="49"/>
@@ -5018,12 +5411,14 @@
       <c r="L40" s="52"/>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.4">
-      <c r="B41" s="46" t="str">
+      <c r="B41" s="46">
         <f>IF(タスク表[[#This Row],[作業内容]]="","",ROW()-ROW(タスク表[#Headers]))</f>
-        <v/>
+        <v>37</v>
       </c>
       <c r="C41" s="44"/>
-      <c r="D41" s="47"/>
+      <c r="D41" s="47" t="s">
+        <v>141</v>
+      </c>
       <c r="E41" s="48"/>
       <c r="F41" s="48"/>
       <c r="G41" s="49"/>
@@ -5056,12 +5451,14 @@
       <c r="L42" s="52"/>
     </row>
     <row r="43" spans="2:12" x14ac:dyDescent="0.4">
-      <c r="B43" s="46" t="str">
+      <c r="B43" s="46">
         <f>IF(タスク表[[#This Row],[作業内容]]="","",ROW()-ROW(タスク表[#Headers]))</f>
-        <v/>
+        <v>39</v>
       </c>
       <c r="C43" s="44"/>
-      <c r="D43" s="47"/>
+      <c r="D43" s="47" t="s">
+        <v>146</v>
+      </c>
       <c r="E43" s="48"/>
       <c r="F43" s="48"/>
       <c r="G43" s="49"/>
@@ -5075,13 +5472,19 @@
       <c r="L43" s="52"/>
     </row>
     <row r="44" spans="2:12" x14ac:dyDescent="0.4">
-      <c r="B44" s="46" t="str">
+      <c r="B44" s="46">
         <f>IF(タスク表[[#This Row],[作業内容]]="","",ROW()-ROW(タスク表[#Headers]))</f>
-        <v/>
-      </c>
-      <c r="C44" s="44"/>
-      <c r="D44" s="47"/>
-      <c r="E44" s="48"/>
+        <v>40</v>
+      </c>
+      <c r="C44" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="D44" s="47" t="s">
+        <v>156</v>
+      </c>
+      <c r="E44" s="48" t="s">
+        <v>41</v>
+      </c>
       <c r="F44" s="48"/>
       <c r="G44" s="49"/>
       <c r="H44" s="49"/>
@@ -5094,13 +5497,17 @@
       <c r="L44" s="52"/>
     </row>
     <row r="45" spans="2:12" x14ac:dyDescent="0.4">
-      <c r="B45" s="46" t="str">
+      <c r="B45" s="46">
         <f>IF(タスク表[[#This Row],[作業内容]]="","",ROW()-ROW(タスク表[#Headers]))</f>
-        <v/>
+        <v>41</v>
       </c>
       <c r="C45" s="44"/>
-      <c r="D45" s="47"/>
-      <c r="E45" s="48"/>
+      <c r="D45" s="47" t="s">
+        <v>157</v>
+      </c>
+      <c r="E45" s="48" t="s">
+        <v>41</v>
+      </c>
       <c r="F45" s="48"/>
       <c r="G45" s="49"/>
       <c r="H45" s="49"/>
@@ -5265,52 +5672,80 @@
       <c r="L53" s="52"/>
     </row>
     <row r="54" spans="2:12" x14ac:dyDescent="0.4">
-      <c r="B54" s="11"/>
-      <c r="D54" s="15"/>
-      <c r="E54" s="11"/>
-      <c r="F54" s="11"/>
-      <c r="G54" s="12"/>
-      <c r="H54" s="12"/>
-      <c r="I54" s="13"/>
-      <c r="J54" s="11"/>
-      <c r="K54" s="14"/>
-      <c r="L54" s="15"/>
+      <c r="B54" s="46" t="str">
+        <f>IF(タスク表[[#This Row],[作業内容]]="","",ROW()-ROW(タスク表[#Headers]))</f>
+        <v/>
+      </c>
+      <c r="C54" s="44"/>
+      <c r="D54" s="47"/>
+      <c r="E54" s="48"/>
+      <c r="F54" s="48"/>
+      <c r="G54" s="49"/>
+      <c r="H54" s="49"/>
+      <c r="I54" s="50" t="str">
+        <f>IF(OR(タスク表[[#This Row],[見積コスト]]="",タスク表[[#This Row],[実コスト]]=""),"",タスク表[[#This Row],[実コスト]]-タスク表[[#This Row],[見積コスト]])</f>
+        <v/>
+      </c>
+      <c r="J54" s="48"/>
+      <c r="K54" s="51"/>
+      <c r="L54" s="52"/>
     </row>
     <row r="55" spans="2:12" x14ac:dyDescent="0.4">
-      <c r="B55" s="11"/>
-      <c r="D55" s="15"/>
-      <c r="E55" s="11"/>
-      <c r="F55" s="11"/>
-      <c r="G55" s="12"/>
-      <c r="H55" s="12"/>
-      <c r="I55" s="13"/>
-      <c r="J55" s="11"/>
-      <c r="K55" s="14"/>
-      <c r="L55" s="15"/>
+      <c r="B55" s="46" t="str">
+        <f>IF(タスク表[[#This Row],[作業内容]]="","",ROW()-ROW(タスク表[#Headers]))</f>
+        <v/>
+      </c>
+      <c r="C55" s="44"/>
+      <c r="D55" s="47"/>
+      <c r="E55" s="48"/>
+      <c r="F55" s="48"/>
+      <c r="G55" s="49"/>
+      <c r="H55" s="49"/>
+      <c r="I55" s="50" t="str">
+        <f>IF(OR(タスク表[[#This Row],[見積コスト]]="",タスク表[[#This Row],[実コスト]]=""),"",タスク表[[#This Row],[実コスト]]-タスク表[[#This Row],[見積コスト]])</f>
+        <v/>
+      </c>
+      <c r="J55" s="48"/>
+      <c r="K55" s="51"/>
+      <c r="L55" s="52"/>
     </row>
     <row r="56" spans="2:12" x14ac:dyDescent="0.4">
-      <c r="B56" s="11"/>
-      <c r="D56" s="15"/>
-      <c r="E56" s="11"/>
-      <c r="F56" s="11"/>
-      <c r="G56" s="12"/>
-      <c r="H56" s="12"/>
-      <c r="I56" s="13"/>
-      <c r="J56" s="11"/>
-      <c r="K56" s="14"/>
-      <c r="L56" s="15"/>
+      <c r="B56" s="46" t="str">
+        <f>IF(タスク表[[#This Row],[作業内容]]="","",ROW()-ROW(タスク表[#Headers]))</f>
+        <v/>
+      </c>
+      <c r="C56" s="44"/>
+      <c r="D56" s="47"/>
+      <c r="E56" s="48"/>
+      <c r="F56" s="48"/>
+      <c r="G56" s="49"/>
+      <c r="H56" s="49"/>
+      <c r="I56" s="50" t="str">
+        <f>IF(OR(タスク表[[#This Row],[見積コスト]]="",タスク表[[#This Row],[実コスト]]=""),"",タスク表[[#This Row],[実コスト]]-タスク表[[#This Row],[見積コスト]])</f>
+        <v/>
+      </c>
+      <c r="J56" s="48"/>
+      <c r="K56" s="51"/>
+      <c r="L56" s="52"/>
     </row>
     <row r="57" spans="2:12" x14ac:dyDescent="0.4">
-      <c r="B57" s="11"/>
-      <c r="D57" s="15"/>
-      <c r="E57" s="11"/>
-      <c r="F57" s="11"/>
-      <c r="G57" s="12"/>
-      <c r="H57" s="12"/>
-      <c r="I57" s="13"/>
-      <c r="J57" s="11"/>
-      <c r="K57" s="14"/>
-      <c r="L57" s="15"/>
+      <c r="B57" s="46" t="str">
+        <f>IF(タスク表[[#This Row],[作業内容]]="","",ROW()-ROW(タスク表[#Headers]))</f>
+        <v/>
+      </c>
+      <c r="C57" s="44"/>
+      <c r="D57" s="47"/>
+      <c r="E57" s="48"/>
+      <c r="F57" s="48"/>
+      <c r="G57" s="49"/>
+      <c r="H57" s="49"/>
+      <c r="I57" s="50" t="str">
+        <f>IF(OR(タスク表[[#This Row],[見積コスト]]="",タスク表[[#This Row],[実コスト]]=""),"",タスク表[[#This Row],[実コスト]]-タスク表[[#This Row],[見積コスト]])</f>
+        <v/>
+      </c>
+      <c r="J57" s="48"/>
+      <c r="K57" s="51"/>
+      <c r="L57" s="52"/>
     </row>
     <row r="58" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B58" s="11"/>
@@ -16628,83 +17063,230 @@
       <c r="K1000" s="14"/>
       <c r="L1000" s="15"/>
     </row>
+    <row r="1001" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B1001" s="11"/>
+      <c r="D1001" s="15"/>
+      <c r="E1001" s="11"/>
+      <c r="F1001" s="11"/>
+      <c r="G1001" s="12"/>
+      <c r="H1001" s="12"/>
+      <c r="I1001" s="13"/>
+      <c r="J1001" s="11"/>
+      <c r="K1001" s="14"/>
+      <c r="L1001" s="15"/>
+    </row>
+    <row r="1002" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B1002" s="11"/>
+      <c r="D1002" s="15"/>
+      <c r="E1002" s="11"/>
+      <c r="F1002" s="11"/>
+      <c r="G1002" s="12"/>
+      <c r="H1002" s="12"/>
+      <c r="I1002" s="13"/>
+      <c r="J1002" s="11"/>
+      <c r="K1002" s="14"/>
+      <c r="L1002" s="15"/>
+    </row>
+    <row r="1003" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B1003" s="11"/>
+      <c r="D1003" s="15"/>
+      <c r="E1003" s="11"/>
+      <c r="F1003" s="11"/>
+      <c r="G1003" s="12"/>
+      <c r="H1003" s="12"/>
+      <c r="I1003" s="13"/>
+      <c r="J1003" s="11"/>
+      <c r="K1003" s="14"/>
+      <c r="L1003" s="15"/>
+    </row>
+    <row r="1004" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B1004" s="11"/>
+      <c r="D1004" s="15"/>
+      <c r="E1004" s="11"/>
+      <c r="F1004" s="11"/>
+      <c r="G1004" s="12"/>
+      <c r="H1004" s="12"/>
+      <c r="I1004" s="13"/>
+      <c r="J1004" s="11"/>
+      <c r="K1004" s="14"/>
+      <c r="L1004" s="15"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="6"/>
-  <conditionalFormatting sqref="B5:L7 B8:B10 E8:L10 B11:L16 E17:L18 B36:L1000 B17:B35 F19:L35">
-    <cfRule type="expression" dxfId="22" priority="1" stopIfTrue="1">
+  <conditionalFormatting sqref="B5:L7 B8:B10 E8:L10 B11:L20 E21:L22 C22:D22 C27:E28 B21:B33 F23:L33 B39:B44 F39:L44 B34:L38 B45:L1004 E29">
+    <cfRule type="expression" dxfId="49" priority="13" stopIfTrue="1">
       <formula>AND($J5&lt;&gt;"",$J5=除外ST)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="21" priority="2" stopIfTrue="1">
+    <cfRule type="expression" dxfId="48" priority="14" stopIfTrue="1">
       <formula>AND($J5&lt;&gt;"",$J5=完了ST)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="20" priority="3" stopIfTrue="1">
+    <cfRule type="expression" dxfId="47" priority="15" stopIfTrue="1">
       <formula>$J5="作業中"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C13:D14">
-    <cfRule type="expression" dxfId="19" priority="11" stopIfTrue="1">
+  <conditionalFormatting sqref="C17:D18">
+    <cfRule type="expression" dxfId="46" priority="23" stopIfTrue="1">
       <formula>AND($J8&lt;&gt;"",$J8=除外ST)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="18" priority="12" stopIfTrue="1">
+    <cfRule type="expression" dxfId="45" priority="24" stopIfTrue="1">
       <formula>AND($J8&lt;&gt;"",$J8=完了ST)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="17" priority="13" stopIfTrue="1">
+    <cfRule type="expression" dxfId="44" priority="25" stopIfTrue="1">
       <formula>$J8="作業中"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C26:D27">
-    <cfRule type="expression" dxfId="16" priority="17" stopIfTrue="1">
-      <formula>AND($J17&lt;&gt;"",$J17=除外ST)</formula>
+  <conditionalFormatting sqref="C27:D27">
+    <cfRule type="expression" dxfId="43" priority="29" stopIfTrue="1">
+      <formula>AND($J21&lt;&gt;"",$J21=除外ST)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="15" priority="18" stopIfTrue="1">
-      <formula>AND($J17&lt;&gt;"",$J17=完了ST)</formula>
+    <cfRule type="expression" dxfId="42" priority="30" stopIfTrue="1">
+      <formula>AND($J21&lt;&gt;"",$J21=完了ST)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="14" priority="19" stopIfTrue="1">
-      <formula>$J17="作業中"</formula>
+    <cfRule type="expression" dxfId="41" priority="31" stopIfTrue="1">
+      <formula>$J21="作業中"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E5:E18 E26:E1000">
-    <cfRule type="expression" dxfId="13" priority="4" stopIfTrue="1">
+  <conditionalFormatting sqref="E44:E1004 E5:E29 E31:E41">
+    <cfRule type="expression" dxfId="40" priority="16" stopIfTrue="1">
       <formula>E5="S"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="12" priority="5" stopIfTrue="1">
+    <cfRule type="expression" dxfId="39" priority="17" stopIfTrue="1">
       <formula>E5="A"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I5:I1000">
-    <cfRule type="expression" dxfId="11" priority="6" stopIfTrue="1">
+  <conditionalFormatting sqref="C44:E44">
+    <cfRule type="expression" dxfId="38" priority="35" stopIfTrue="1">
+      <formula>AND($J32&lt;&gt;"",$J32=除外ST)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="37" priority="36" stopIfTrue="1">
+      <formula>AND($J32&lt;&gt;"",$J32=完了ST)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="36" priority="37" stopIfTrue="1">
+      <formula>$J32="作業中"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I5:I1004">
+    <cfRule type="expression" dxfId="35" priority="18" stopIfTrue="1">
       <formula>AND(ISNUMBER(I5),I5&gt;0)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="10" priority="7" stopIfTrue="1">
+    <cfRule type="expression" dxfId="34" priority="19" stopIfTrue="1">
       <formula>AND(ISNUMBER(I5),I5&lt;0)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E26:E27 C28:E35">
-    <cfRule type="expression" dxfId="2" priority="23" stopIfTrue="1">
-      <formula>AND($J19&lt;&gt;"",$J19=除外ST)</formula>
+  <conditionalFormatting sqref="E27:E29">
+    <cfRule type="expression" dxfId="33" priority="50" stopIfTrue="1">
+      <formula>AND($J23&lt;&gt;"",$J23=除外ST)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="24" stopIfTrue="1">
-      <formula>AND($J19&lt;&gt;"",$J19=完了ST)</formula>
+    <cfRule type="expression" dxfId="32" priority="51" stopIfTrue="1">
+      <formula>AND($J23&lt;&gt;"",$J23=完了ST)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="25" stopIfTrue="1">
-      <formula>$J19="作業中"</formula>
+    <cfRule type="expression" dxfId="31" priority="52" stopIfTrue="1">
+      <formula>$J23="作業中"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C39:E39">
+    <cfRule type="expression" dxfId="30" priority="111" stopIfTrue="1">
+      <formula>AND($J26&lt;&gt;"",$J26=除外ST)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="29" priority="112" stopIfTrue="1">
+      <formula>AND($J26&lt;&gt;"",$J26=完了ST)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="28" priority="113" stopIfTrue="1">
+      <formula>$J26="作業中"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C32:E32">
+    <cfRule type="expression" dxfId="27" priority="117" stopIfTrue="1">
+      <formula>AND($J25&lt;&gt;"",$J25=除外ST)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="26" priority="118" stopIfTrue="1">
+      <formula>AND($J25&lt;&gt;"",$J25=完了ST)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="25" priority="119" stopIfTrue="1">
+      <formula>$J25="作業中"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C33:E33">
+    <cfRule type="expression" dxfId="24" priority="153" stopIfTrue="1">
+      <formula>AND($J29&lt;&gt;"",$J29=除外ST)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="23" priority="154" stopIfTrue="1">
+      <formula>AND($J29&lt;&gt;"",$J29=完了ST)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="22" priority="155" stopIfTrue="1">
+      <formula>$J29="作業中"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C40:E41">
+    <cfRule type="expression" dxfId="21" priority="171" stopIfTrue="1">
+      <formula>AND($J30&lt;&gt;"",$J30=除外ST)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="20" priority="172" stopIfTrue="1">
+      <formula>AND($J30&lt;&gt;"",$J30=完了ST)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="19" priority="173" stopIfTrue="1">
+      <formula>$J30="作業中"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E23:E26">
+    <cfRule type="expression" dxfId="18" priority="10" stopIfTrue="1">
+      <formula>AND($J23&lt;&gt;"",$J23=除外ST)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="17" priority="11" stopIfTrue="1">
+      <formula>AND($J23&lt;&gt;"",$J23=完了ST)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="16" priority="12" stopIfTrue="1">
+      <formula>$J23="作業中"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E23:E26">
+    <cfRule type="expression" dxfId="15" priority="7" stopIfTrue="1">
+      <formula>AND($J23&lt;&gt;"",$J23=除外ST)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="14" priority="8" stopIfTrue="1">
+      <formula>AND($J23&lt;&gt;"",$J23=完了ST)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="13" priority="9" stopIfTrue="1">
+      <formula>$J23="作業中"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E31:E32">
+    <cfRule type="expression" dxfId="12" priority="1" stopIfTrue="1">
+      <formula>AND($J31&lt;&gt;"",$J31=除外ST)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="11" priority="2" stopIfTrue="1">
+      <formula>AND($J31&lt;&gt;"",$J31=完了ST)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="10" priority="3" stopIfTrue="1">
+      <formula>$J31="作業中"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E31:E32">
+    <cfRule type="expression" dxfId="9" priority="4" stopIfTrue="1">
+      <formula>AND($J27&lt;&gt;"",$J27=除外ST)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="8" priority="5" stopIfTrue="1">
+      <formula>AND($J27&lt;&gt;"",$J27=完了ST)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="7" priority="6" stopIfTrue="1">
+      <formula>$J27="作業中"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="5">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F5:F1000" xr:uid="{40647F47-509E-46A8-8187-C0A1ADC86BC3}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C5:C7 C11:C20 C22 C27:C28 C44:C1004 C32:C41" xr:uid="{E6BBE5BD-7004-4694-85A6-704154467F57}">
+      <formula1>カテゴリ一覧</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E5:E29 E44:E1004 E31:E41" xr:uid="{029AB92C-5CA0-4F76-9790-7F4B331300FB}">
+      <formula1>優先度一覧</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F5:F1004" xr:uid="{40647F47-509E-46A8-8187-C0A1ADC86BC3}">
       <formula1>バージョン一覧</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J5:J1000" xr:uid="{FD5F72C4-282D-476B-B239-E9C4C9E28E99}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J5:J1004" xr:uid="{FD5F72C4-282D-476B-B239-E9C4C9E28E99}">
       <formula1>ステータス一覧</formula1>
     </dataValidation>
-    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="0以上の数値を入力してください" sqref="G5:H1000" xr:uid="{3EFE3393-D09C-4B29-BFD5-14DF7F410677}">
+    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="0以上の数値を入力してください" sqref="G5:H1004" xr:uid="{3EFE3393-D09C-4B29-BFD5-14DF7F410677}">
       <formula1>0</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C5:C7 C11:C16 C26:C1000" xr:uid="{E6BBE5BD-7004-4694-85A6-704154467F57}">
-      <formula1>カテゴリ一覧</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E5:E18 E26:E1000" xr:uid="{029AB92C-5CA0-4F76-9790-7F4B331300FB}">
-      <formula1>優先度一覧</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -16971,11 +17553,11 @@
       </c>
       <c r="AB7" s="36">
         <f t="shared" ref="AB7:AB14" ca="1" si="0">IF(AA7="","",AA7-TODAY())</f>
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="AC7" s="36">
         <f ca="1">IF(AA7="","",MAX(0,NETWORKDAYS.INTL(TODAY(),AA7,週末区分,休日一覧)))</f>
-        <v>24</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="2:29" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
@@ -17073,11 +17655,11 @@
       </c>
       <c r="AB8" s="36">
         <f t="shared" ca="1" si="0"/>
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="AC8" s="36">
         <f ca="1">IF(AA8="","",MAX(0,NETWORKDAYS.INTL(TODAY(),AA8,週末区分,休日一覧)))</f>
-        <v>48</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9" spans="2:29" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
@@ -17175,11 +17757,11 @@
       </c>
       <c r="AB9" s="36">
         <f t="shared" ca="1" si="0"/>
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="AC9" s="36">
         <f ca="1">IF(AA9="","",MAX(0,NETWORKDAYS.INTL(TODAY(),AA9,週末区分,休日一覧)))</f>
-        <v>71</v>
+        <v>66</v>
       </c>
     </row>
     <row r="10" spans="2:29" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
@@ -17277,11 +17859,11 @@
       </c>
       <c r="AB10" s="36">
         <f t="shared" ca="1" si="0"/>
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="AC10" s="36">
         <f ca="1">IF(AA10="","",MAX(0,NETWORKDAYS.INTL(TODAY(),AA10,週末区分,休日一覧)))</f>
-        <v>85</v>
+        <v>80</v>
       </c>
     </row>
     <row r="11" spans="2:29" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
@@ -18173,27 +18755,27 @@
   </mergeCells>
   <phoneticPr fontId="6"/>
   <conditionalFormatting sqref="B7:H12 J7:P12 R7:X12 B17:H22 J17:P22 R17:X22">
-    <cfRule type="expression" dxfId="9" priority="1" stopIfTrue="1">
+    <cfRule type="expression" dxfId="6" priority="1" stopIfTrue="1">
       <formula>AND(B7&lt;&gt;"",B7=TODAY())</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="8" priority="2" stopIfTrue="1">
+    <cfRule type="expression" dxfId="5" priority="2" stopIfTrue="1">
       <formula>AND(B7&lt;&gt;"",COUNTIF(マイルストーン日付,B7)&gt;0)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="7" priority="3" stopIfTrue="1">
+    <cfRule type="expression" dxfId="4" priority="3" stopIfTrue="1">
       <formula>AND(B7&lt;&gt;"",B7=開始日)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="6" priority="4" stopIfTrue="1">
+    <cfRule type="expression" dxfId="3" priority="4" stopIfTrue="1">
       <formula>AND(B7&lt;&gt;"",COUNTIF(休日一覧,B7)&gt;0)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="5" priority="5" stopIfTrue="1">
+    <cfRule type="expression" dxfId="2" priority="5" stopIfTrue="1">
       <formula>AND(B7&lt;&gt;"",OR(WEEKDAY(B7)=1,WEEKDAY(B7)=7))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="4" priority="6" stopIfTrue="1">
+    <cfRule type="expression" dxfId="1" priority="6" stopIfTrue="1">
       <formula>AND(B7&lt;&gt;"",B7&lt;TODAY())</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB7:AB14">
-    <cfRule type="expression" dxfId="3" priority="7" stopIfTrue="1">
+    <cfRule type="expression" dxfId="0" priority="7" stopIfTrue="1">
       <formula>AND(ISNUMBER(AB7),AB7&lt;0)</formula>
     </cfRule>
   </conditionalFormatting>

--- a/進捗/コスト表_winter_2026.xlsx
+++ b/進捗/コスト表_winter_2026.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsyts\GitHub\2026_winter\進捗\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\平尾泰稀\Documents\GitHub\2026_winter\進捗\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57543333-1590-4981-BEBB-9A0C503FCFBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F014D85-C218-4C35-846F-8012B54A4AFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{90270874-AD68-4987-AED5-115E189B84F1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{90270874-AD68-4987-AED5-115E189B84F1}"/>
   </bookViews>
   <sheets>
     <sheet name="集計" sheetId="1" r:id="rId1"/>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="165">
   <si>
     <t>設定</t>
   </si>
@@ -118,9 +118,6 @@
   </si>
   <si>
     <t>プロト</t>
-  </si>
-  <si>
-    <t>仮の日付</t>
   </si>
   <si>
     <t>アルファ</t>
@@ -509,13 +506,6 @@
     <phoneticPr fontId="6"/>
   </si>
   <si>
-    <t>必殺技カメラワーク</t>
-    <rPh sb="0" eb="3">
-      <t>ヒッサツワザ</t>
-    </rPh>
-    <phoneticPr fontId="6"/>
-  </si>
-  <si>
     <t>敵のヒット状態を増やす</t>
     <rPh sb="0" eb="1">
       <t>テキ</t>
@@ -525,19 +515,6 @@
     </rPh>
     <rPh sb="8" eb="9">
       <t>フ</t>
-    </rPh>
-    <phoneticPr fontId="6"/>
-  </si>
-  <si>
-    <t>強攻撃を見てからヒットバック</t>
-    <rPh sb="0" eb="1">
-      <t>キョウ</t>
-    </rPh>
-    <rPh sb="1" eb="3">
-      <t>コウゲキ</t>
-    </rPh>
-    <rPh sb="4" eb="5">
-      <t>ミ</t>
     </rPh>
     <phoneticPr fontId="6"/>
   </si>
@@ -575,34 +552,6 @@
     </rPh>
     <rPh sb="18" eb="20">
       <t>ツイカ</t>
-    </rPh>
-    <phoneticPr fontId="6"/>
-  </si>
-  <si>
-    <t>もう一体敵追加(遠距離(壁走りとかを使って素早く倒してほしいため</t>
-    <rPh sb="2" eb="4">
-      <t>イッタイ</t>
-    </rPh>
-    <rPh sb="4" eb="5">
-      <t>テキ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>ツイカ</t>
-    </rPh>
-    <rPh sb="8" eb="11">
-      <t>エンキョリ</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>カベバシ</t>
-    </rPh>
-    <rPh sb="18" eb="19">
-      <t>ツカ</t>
-    </rPh>
-    <rPh sb="21" eb="23">
-      <t>スバヤ</t>
-    </rPh>
-    <rPh sb="24" eb="25">
-      <t>タオ</t>
     </rPh>
     <phoneticPr fontId="6"/>
   </si>
@@ -778,11 +727,62 @@
     <phoneticPr fontId="6"/>
   </si>
   <si>
-    <t>playerのガード、パリィ追加もあり</t>
+    <t>中・遠距離たちの</t>
+    <rPh sb="0" eb="1">
+      <t>チュウ</t>
+    </rPh>
+    <rPh sb="2" eb="5">
+      <t>エンキョリ</t>
+    </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>playerのガード、パリィ追加もあり←なし</t>
     <rPh sb="14" eb="16">
       <t>ツイカ</t>
     </rPh>
     <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>走りアニメーション修正(もういっそ同じでエフェクト足す感じでいい気がしてきた、それかブレンドする</t>
+    <rPh sb="0" eb="1">
+      <t>ハシ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>シュウセイ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>オナ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>タ</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>カン</t>
+    </rPh>
+    <rPh sb="32" eb="33">
+      <t>キ</t>
+    </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>強攻撃を見てからバックステップ</t>
+    <rPh sb="0" eb="1">
+      <t>キョウ</t>
+    </rPh>
+    <rPh sb="1" eb="3">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ミ</t>
+    </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>もう一体敵追加(遠距離(壁走りとかを使って素早く倒してほしいため</t>
+  </si>
+  <si>
+    <t>必殺技カメラワーク</t>
   </si>
 </sst>
 </file>
@@ -1221,7 +1221,7 @@
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="66">
+  <dxfs count="69">
     <dxf>
       <font>
         <color rgb="FFA6A6A6"/>
@@ -1310,6 +1310,145 @@
       <font>
         <strike/>
         <color rgb="FFA6A6A6"/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFF2CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF808080"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE2EFDA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFA6A6A6"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF0070C0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFF2CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF808080"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE2EFDA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFA6A6A6"/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFF2CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF808080"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE2EFDA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFA6A6A6"/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFF2CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF808080"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE2EFDA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFA6A6A6"/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFF2CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF808080"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE2EFDA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFA6A6A6"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFED7D31"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFC00000"/>
       </font>
     </dxf>
     <dxf>
@@ -1425,122 +1564,6 @@
       <font>
         <strike/>
         <color rgb="FFA6A6A6"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFF2CC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF808080"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFE2EFDA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFA6A6A6"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFF2CC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF808080"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFE2EFDA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFA6A6A6"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFF2CC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF808080"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFE2EFDA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFA6A6A6"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF0070C0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC00000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFF2CC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF808080"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFE2EFDA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFA6A6A6"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFED7D31"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFC00000"/>
       </font>
     </dxf>
     <dxf>
@@ -2091,24 +2114,24 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3A2567DA-ED67-436A-BAF7-D8D91E4E00C2}" name="タスク表" displayName="タスク表" ref="B4:L57" totalsRowShown="0" headerRowDxfId="65" dataDxfId="64" tableBorderDxfId="63">
-  <autoFilter ref="B4:L57" xr:uid="{3A2567DA-ED67-436A-BAF7-D8D91E4E00C2}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3A2567DA-ED67-436A-BAF7-D8D91E4E00C2}" name="タスク表" displayName="タスク表" ref="B4:L63" totalsRowShown="0" headerRowDxfId="68" dataDxfId="67" tableBorderDxfId="66">
+  <autoFilter ref="B4:L63" xr:uid="{3A2567DA-ED67-436A-BAF7-D8D91E4E00C2}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{F383ED7B-CAB4-46F1-AC7C-023467A46D88}" name="No" dataDxfId="62">
+    <tableColumn id="1" xr3:uid="{F383ED7B-CAB4-46F1-AC7C-023467A46D88}" name="No" dataDxfId="65">
       <calculatedColumnFormula>IF(タスク表[[#This Row],[作業内容]]="","",ROW()-ROW(タスク表[#Headers]))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{7EF03FBB-5A01-49E5-9341-0CD4CA09848E}" name="カテゴリ" dataDxfId="61"/>
-    <tableColumn id="3" xr3:uid="{48466042-E58A-4D97-AC9B-D6FED5F46A1F}" name="作業内容" dataDxfId="60"/>
-    <tableColumn id="4" xr3:uid="{65680DBB-31AB-43B9-BFA7-0526EC96D22F}" name="優先度" dataDxfId="59"/>
-    <tableColumn id="5" xr3:uid="{D7E12594-DF8F-4044-8B36-8EAC7E3BB4E5}" name="バージョン" dataDxfId="58"/>
-    <tableColumn id="6" xr3:uid="{BAF69BB2-2D96-4276-B8FA-8A5B618ED05F}" name="見積コスト" dataDxfId="57"/>
-    <tableColumn id="7" xr3:uid="{0A021283-FCFD-447B-98BD-F53EF31318C1}" name="実コスト" dataDxfId="56"/>
-    <tableColumn id="8" xr3:uid="{75B48E43-3BBD-4AF9-A1B3-D350673AB994}" name="差分" dataDxfId="55">
+    <tableColumn id="2" xr3:uid="{7EF03FBB-5A01-49E5-9341-0CD4CA09848E}" name="カテゴリ" dataDxfId="64"/>
+    <tableColumn id="3" xr3:uid="{48466042-E58A-4D97-AC9B-D6FED5F46A1F}" name="作業内容" dataDxfId="63"/>
+    <tableColumn id="4" xr3:uid="{65680DBB-31AB-43B9-BFA7-0526EC96D22F}" name="優先度" dataDxfId="62"/>
+    <tableColumn id="5" xr3:uid="{D7E12594-DF8F-4044-8B36-8EAC7E3BB4E5}" name="バージョン" dataDxfId="61"/>
+    <tableColumn id="6" xr3:uid="{BAF69BB2-2D96-4276-B8FA-8A5B618ED05F}" name="見積コスト" dataDxfId="60"/>
+    <tableColumn id="7" xr3:uid="{0A021283-FCFD-447B-98BD-F53EF31318C1}" name="実コスト" dataDxfId="59"/>
+    <tableColumn id="8" xr3:uid="{75B48E43-3BBD-4AF9-A1B3-D350673AB994}" name="差分" dataDxfId="58">
       <calculatedColumnFormula>IF(OR(タスク表[[#This Row],[見積コスト]]="",タスク表[[#This Row],[実コスト]]=""),"",タスク表[[#This Row],[実コスト]]-タスク表[[#This Row],[見積コスト]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{7B1D7DAB-403C-43FB-B066-5FF4BD411B5A}" name="ステータス" dataDxfId="54"/>
-    <tableColumn id="10" xr3:uid="{D6F46B68-27C3-483A-8CAC-834EC0598F40}" name="完了日" dataDxfId="53"/>
-    <tableColumn id="11" xr3:uid="{40889AD2-F644-4454-99EC-D71EF37CD54A}" name="備考" dataDxfId="52"/>
+    <tableColumn id="9" xr3:uid="{7B1D7DAB-403C-43FB-B066-5FF4BD411B5A}" name="ステータス" dataDxfId="57"/>
+    <tableColumn id="10" xr3:uid="{D6F46B68-27C3-483A-8CAC-834EC0598F40}" name="完了日" dataDxfId="56"/>
+    <tableColumn id="11" xr3:uid="{40889AD2-F644-4454-99EC-D71EF37CD54A}" name="備考" dataDxfId="55"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2445,26 +2468,26 @@
   <sheetData>
     <row r="1" spans="2:4" ht="21" x14ac:dyDescent="0.4">
       <c r="B1" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="2" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B2" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="4" spans="2:4" ht="16.5" x14ac:dyDescent="0.4">
       <c r="B4" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="5" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B5" s="16" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C5" s="17">
         <f ca="1">TODAY()</f>
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="D5" s="3"/>
     </row>
@@ -2477,36 +2500,36 @@
         <v>46296</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="7" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B7" s="16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C7" s="18">
         <f>SUMIFS(タスク表[見積コスト],タスク表[ステータス],"&lt;&gt;"&amp;除外ST)</f>
         <v>0</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="8" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B8" s="16" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C8" s="18">
         <f>SUMIFS(タスク表[見積コスト],タスク表[ステータス],完了ST)</f>
         <v>0</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="9" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B9" s="16" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C9" s="18">
         <f>C7-C8</f>
@@ -2516,150 +2539,150 @@
     </row>
     <row r="10" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B10" s="16" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C10" s="19">
         <f>IF(C7=0,0,C8/C7)</f>
         <v>0</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="11" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B11" s="16" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C11" s="18">
         <f>SUMIFS(タスク表[実コスト],タスク表[ステータス],"&lt;&gt;"&amp;除外ST)</f>
         <v>0</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="12" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B12" s="16" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C12" s="20">
         <f ca="1">MAX(0,NETWORKDAYS.INTL(開始日,TODAY(),週末区分,休日一覧))</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="13" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B13" s="16" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C13" s="18">
         <f ca="1">IF(C12&lt;=0,"",C8/C12)</f>
         <v>0</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="14" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B14" s="16" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C14" s="17">
         <f>IF(COUNT(マイルストーン日付)=0,"",MAX(マイルストーン日付))</f>
-        <v>46430</v>
+        <v>46387</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="15" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B15" s="16" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C15" s="20">
         <f ca="1">IF(C14="","",MAX(0,NETWORKDAYS.INTL(TODAY(),C14,週末区分,休日一覧)))</f>
-        <v>80</v>
+        <v>52</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="16" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B16" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C16" s="18">
         <f ca="1">IF(OR(C15="",C15=0),"",C9/C15)</f>
         <v>0</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="17" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B17" s="16" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C17" s="18">
         <f ca="1">IF(C15="","",作業時間*C15-C9)</f>
-        <v>640</v>
+        <v>416</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B18" s="16" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C18" s="17" t="str">
         <f ca="1">IF(OR(C13="",C13=0),"",WORKDAY.INTL(TODAY(),ROUNDUP(C9/C13,0),週末区分,休日一覧))</f>
         <v/>
       </c>
       <c r="D18" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="21" spans="2:12" ht="16.5" x14ac:dyDescent="0.4">
       <c r="B21" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="22" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B22" s="10" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C22" s="10" t="s">
         <v>18</v>
       </c>
       <c r="D22" s="10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E22" s="10" t="s">
         <v>11</v>
       </c>
       <c r="F22" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="G22" s="10" t="s">
         <v>102</v>
       </c>
-      <c r="G22" s="10" t="s">
-        <v>103</v>
-      </c>
       <c r="H22" s="10" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I22" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J22" s="10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K22" s="10" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="L22" s="10" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="23" spans="2:12" x14ac:dyDescent="0.4">
@@ -2669,7 +2692,7 @@
       </c>
       <c r="C23" s="22">
         <f>IF(OR(B23="",設定!$C13=""),"",設定!$C13)</f>
-        <v>46339</v>
+        <v>46326</v>
       </c>
       <c r="D23" s="24">
         <f>IF(B23="","",SUMIFS(タスク表[見積コスト],タスク表[バージョン],B23,タスク表[ステータス],"&lt;&gt;"&amp;除外ST))</f>
@@ -2697,7 +2720,7 @@
       </c>
       <c r="J23" s="28">
         <f ca="1">IF(C23="","",MAX(0,NETWORKDAYS.INTL(TODAY(),C23,週末区分,休日一覧)))</f>
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="K23" s="24">
         <f t="shared" ref="K23:K30" ca="1" si="2">IF(OR(J23="",N(J23)=0),"",G23/J23)</f>
@@ -2705,7 +2728,7 @@
       </c>
       <c r="L23" s="24">
         <f t="shared" ref="L23:L30" ca="1" si="3">IF(J23="","",作業時間*J23-G23)</f>
-        <v>152</v>
+        <v>80</v>
       </c>
     </row>
     <row r="24" spans="2:12" x14ac:dyDescent="0.4">
@@ -2715,7 +2738,7 @@
       </c>
       <c r="C24" s="22">
         <f>IF(OR(B24="",設定!$C14=""),"",設定!$C14)</f>
-        <v>46374</v>
+        <v>46356</v>
       </c>
       <c r="D24" s="24">
         <f>IF(B24="","",SUMIFS(タスク表[見積コスト],タスク表[バージョン],B24,タスク表[ステータス],"&lt;&gt;"&amp;除外ST))</f>
@@ -2743,7 +2766,7 @@
       </c>
       <c r="J24" s="28">
         <f ca="1">IF(C24="","",MAX(0,NETWORKDAYS.INTL(TODAY(),C24,週末区分,休日一覧)))</f>
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="K24" s="24">
         <f t="shared" ca="1" si="2"/>
@@ -2751,7 +2774,7 @@
       </c>
       <c r="L24" s="24">
         <f t="shared" ca="1" si="3"/>
-        <v>344</v>
+        <v>232</v>
       </c>
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.4">
@@ -2761,7 +2784,7 @@
       </c>
       <c r="C25" s="22">
         <f>IF(OR(B25="",設定!$C15=""),"",設定!$C15)</f>
-        <v>46409</v>
+        <v>46372</v>
       </c>
       <c r="D25" s="24">
         <f>IF(B25="","",SUMIFS(タスク表[見積コスト],タスク表[バージョン],B25,タスク表[ステータス],"&lt;&gt;"&amp;除外ST))</f>
@@ -2789,7 +2812,7 @@
       </c>
       <c r="J25" s="28">
         <f ca="1">IF(C25="","",MAX(0,NETWORKDAYS.INTL(TODAY(),C25,週末区分,休日一覧)))</f>
-        <v>66</v>
+        <v>41</v>
       </c>
       <c r="K25" s="24">
         <f t="shared" ca="1" si="2"/>
@@ -2797,7 +2820,7 @@
       </c>
       <c r="L25" s="24">
         <f t="shared" ca="1" si="3"/>
-        <v>528</v>
+        <v>328</v>
       </c>
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.4">
@@ -2807,7 +2830,7 @@
       </c>
       <c r="C26" s="22">
         <f>IF(OR(B26="",設定!$C16=""),"",設定!$C16)</f>
-        <v>46430</v>
+        <v>46387</v>
       </c>
       <c r="D26" s="24">
         <f>IF(B26="","",SUMIFS(タスク表[見積コスト],タスク表[バージョン],B26,タスク表[ステータス],"&lt;&gt;"&amp;除外ST))</f>
@@ -2835,7 +2858,7 @@
       </c>
       <c r="J26" s="28">
         <f ca="1">IF(C26="","",MAX(0,NETWORKDAYS.INTL(TODAY(),C26,週末区分,休日一覧)))</f>
-        <v>80</v>
+        <v>52</v>
       </c>
       <c r="K26" s="24">
         <f t="shared" ca="1" si="2"/>
@@ -2843,7 +2866,7 @@
       </c>
       <c r="L26" s="24">
         <f t="shared" ca="1" si="3"/>
-        <v>640</v>
+        <v>416</v>
       </c>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.4">
@@ -3032,7 +3055,7 @@
     </row>
     <row r="31" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B31" s="21" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C31" s="23"/>
       <c r="D31" s="25">
@@ -3062,59 +3085,59 @@
     </row>
     <row r="32" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B32" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="16.5" x14ac:dyDescent="0.4">
       <c r="B34" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="K34" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="35" spans="2:16" x14ac:dyDescent="0.4">
       <c r="B35" s="10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C35" s="10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D35" s="10" t="s">
         <v>11</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F35" s="10" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G35" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H35" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="I35" s="10" t="s">
         <v>107</v>
       </c>
-      <c r="I35" s="10" t="s">
-        <v>108</v>
-      </c>
       <c r="K35" s="10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L35" s="10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="M35" s="10" t="s">
         <v>11</v>
       </c>
       <c r="N35" s="10" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="O35" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="P35" s="10" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="36" spans="2:16" x14ac:dyDescent="0.4">
@@ -3172,7 +3195,7 @@
       </c>
       <c r="P36" s="5">
         <f>IF(K36="","",COUNTIFS(タスク表[優先度],K36,タスク表[作業内容],"&lt;&gt;",タスク表[ステータス],"&lt;&gt;"&amp;除外ST))</f>
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="37" spans="2:16" x14ac:dyDescent="0.4">
@@ -3202,11 +3225,11 @@
       </c>
       <c r="H37" s="5">
         <f>IF(B37="","",COUNTIFS(タスク表[カテゴリ],B37,タスク表[作業内容],"&lt;&gt;",タスク表[ステータス],"&lt;&gt;"&amp;除外ST))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I37" s="5">
         <f>IF(B37="","",COUNTIFS(タスク表[カテゴリ],B37,タスク表[作業内容],"&lt;&gt;",タスク表[ステータス],完了ST))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K37" s="30" t="str">
         <f>IF(設定!$H14="","",設定!$H14)</f>
@@ -3288,7 +3311,7 @@
       </c>
       <c r="P38" s="5">
         <f>IF(K38="","",COUNTIFS(タスク表[優先度],K38,タスク表[作業内容],"&lt;&gt;",タスク表[ステータス],"&lt;&gt;"&amp;除外ST))</f>
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39" spans="2:16" x14ac:dyDescent="0.4">
@@ -4379,7 +4402,7 @@
     </row>
     <row r="66" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B66" s="21" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C66" s="25">
         <f>IF(FALSE,"",SUMIFS(タスク表[見積コスト],タスク表[カテゴリ],"",タスク表[ステータス],"&lt;&gt;"&amp;除外ST))</f>
@@ -4403,11 +4426,11 @@
       </c>
       <c r="H66" s="21">
         <f>IF(FALSE,"",COUNTIFS(タスク表[カテゴリ],"",タスク表[作業内容],"&lt;&gt;",タスク表[ステータス],"&lt;&gt;"&amp;除外ST))</f>
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I66" s="21">
         <f>IF(FALSE,"",COUNTIFS(タスク表[カテゴリ],"",タスク表[作業内容],"&lt;&gt;",タスク表[ステータス],完了ST))</f>
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -4427,7 +4450,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C17">
-    <cfRule type="expression" dxfId="51" priority="2" stopIfTrue="1">
+    <cfRule type="expression" dxfId="54" priority="2" stopIfTrue="1">
       <formula>AND(ISNUMBER(C17),C17&lt;0)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4460,7 +4483,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L23:L30">
-    <cfRule type="expression" dxfId="50" priority="4" stopIfTrue="1">
+    <cfRule type="expression" dxfId="53" priority="4" stopIfTrue="1">
       <formula>AND(ISNUMBER(L23),L23&lt;0)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4545,7 +4568,7 @@
   <sheetPr>
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="B1:L1004"/>
+  <dimension ref="B1:L1010"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="2.625" style="1" customWidth="1"/>
@@ -4563,47 +4586,47 @@
   <sheetData>
     <row r="1" spans="2:12" ht="21" x14ac:dyDescent="0.4">
       <c r="B1" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="2" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B2" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="4" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B4" s="43" t="s">
+        <v>63</v>
+      </c>
+      <c r="C4" s="44" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" s="44" t="s">
         <v>64</v>
       </c>
-      <c r="C4" s="44" t="s">
-        <v>26</v>
-      </c>
-      <c r="D4" s="44" t="s">
+      <c r="E4" s="44" t="s">
+        <v>37</v>
+      </c>
+      <c r="F4" s="44" t="s">
         <v>65</v>
       </c>
-      <c r="E4" s="44" t="s">
-        <v>38</v>
-      </c>
-      <c r="F4" s="44" t="s">
+      <c r="G4" s="44" t="s">
         <v>66</v>
       </c>
-      <c r="G4" s="44" t="s">
+      <c r="H4" s="44" t="s">
         <v>67</v>
       </c>
-      <c r="H4" s="44" t="s">
+      <c r="I4" s="44" t="s">
         <v>68</v>
       </c>
-      <c r="I4" s="44" t="s">
+      <c r="J4" s="44" t="s">
+        <v>48</v>
+      </c>
+      <c r="K4" s="44" t="s">
         <v>69</v>
       </c>
-      <c r="J4" s="44" t="s">
-        <v>49</v>
-      </c>
-      <c r="K4" s="44" t="s">
+      <c r="L4" s="45" t="s">
         <v>70</v>
-      </c>
-      <c r="L4" s="45" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="5" spans="2:12" x14ac:dyDescent="0.4">
@@ -4612,13 +4635,13 @@
         <v>1</v>
       </c>
       <c r="C5" s="44" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D5" s="47" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E5" s="48" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F5" s="48"/>
       <c r="G5" s="49"/>
@@ -4638,10 +4661,10 @@
       </c>
       <c r="C6" s="44"/>
       <c r="D6" s="47" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E6" s="48" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F6" s="48"/>
       <c r="G6" s="49"/>
@@ -4651,7 +4674,7 @@
         <v/>
       </c>
       <c r="J6" s="48" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K6" s="51"/>
       <c r="L6" s="52"/>
@@ -4663,10 +4686,10 @@
       </c>
       <c r="C7" s="44"/>
       <c r="D7" s="47" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E7" s="48" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F7" s="48"/>
       <c r="G7" s="49"/>
@@ -4686,10 +4709,10 @@
       </c>
       <c r="C8" s="44"/>
       <c r="D8" s="47" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="E8" s="48" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F8" s="48"/>
       <c r="G8" s="49"/>
@@ -4699,7 +4722,7 @@
         <v/>
       </c>
       <c r="J8" s="48" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K8" s="51"/>
       <c r="L8" s="52"/>
@@ -4711,10 +4734,10 @@
       </c>
       <c r="C9" s="44"/>
       <c r="D9" s="47" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="E9" s="48" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F9" s="48"/>
       <c r="G9" s="49"/>
@@ -4723,7 +4746,9 @@
         <f>IF(OR(タスク表[[#This Row],[見積コスト]]="",タスク表[[#This Row],[実コスト]]=""),"",タスク表[[#This Row],[実コスト]]-タスク表[[#This Row],[見積コスト]])</f>
         <v/>
       </c>
-      <c r="J9" s="48"/>
+      <c r="J9" s="48" t="s">
+        <v>51</v>
+      </c>
       <c r="K9" s="51"/>
       <c r="L9" s="52"/>
     </row>
@@ -4734,10 +4759,10 @@
       </c>
       <c r="C10" s="44"/>
       <c r="D10" s="47" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="E10" s="48" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F10" s="48"/>
       <c r="G10" s="49"/>
@@ -4746,7 +4771,9 @@
         <f>IF(OR(タスク表[[#This Row],[見積コスト]]="",タスク表[[#This Row],[実コスト]]=""),"",タスク表[[#This Row],[実コスト]]-タスク表[[#This Row],[見積コスト]])</f>
         <v/>
       </c>
-      <c r="J10" s="48"/>
+      <c r="J10" s="48" t="s">
+        <v>51</v>
+      </c>
       <c r="K10" s="51"/>
       <c r="L10" s="52"/>
     </row>
@@ -4757,10 +4784,10 @@
       </c>
       <c r="C11" s="44"/>
       <c r="D11" s="47" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="E11" s="48" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F11" s="48"/>
       <c r="G11" s="49"/>
@@ -4769,7 +4796,9 @@
         <f>IF(OR(タスク表[[#This Row],[見積コスト]]="",タスク表[[#This Row],[実コスト]]=""),"",タスク表[[#This Row],[実コスト]]-タスク表[[#This Row],[見積コスト]])</f>
         <v/>
       </c>
-      <c r="J11" s="48"/>
+      <c r="J11" s="48" t="s">
+        <v>14</v>
+      </c>
       <c r="K11" s="51"/>
       <c r="L11" s="52"/>
     </row>
@@ -4780,7 +4809,7 @@
       </c>
       <c r="C12" s="44"/>
       <c r="D12" s="47" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="E12" s="48"/>
       <c r="F12" s="48"/>
@@ -4790,7 +4819,9 @@
         <f>IF(OR(タスク表[[#This Row],[見積コスト]]="",タスク表[[#This Row],[実コスト]]=""),"",タスク表[[#This Row],[実コスト]]-タスク表[[#This Row],[見積コスト]])</f>
         <v/>
       </c>
-      <c r="J12" s="48"/>
+      <c r="J12" s="48" t="s">
+        <v>49</v>
+      </c>
       <c r="K12" s="51"/>
       <c r="L12" s="52"/>
     </row>
@@ -4801,7 +4832,7 @@
       </c>
       <c r="C13" s="44"/>
       <c r="D13" s="47" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="E13" s="48"/>
       <c r="F13" s="48"/>
@@ -4811,7 +4842,9 @@
         <f>IF(OR(タスク表[[#This Row],[見積コスト]]="",タスク表[[#This Row],[実コスト]]=""),"",タスク表[[#This Row],[実コスト]]-タスク表[[#This Row],[見積コスト]])</f>
         <v/>
       </c>
-      <c r="J13" s="48"/>
+      <c r="J13" s="48" t="s">
+        <v>49</v>
+      </c>
       <c r="K13" s="51"/>
       <c r="L13" s="52"/>
     </row>
@@ -4822,7 +4855,7 @@
       </c>
       <c r="C14" s="44"/>
       <c r="D14" s="47" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="E14" s="48"/>
       <c r="F14" s="48"/>
@@ -4832,17 +4865,21 @@
         <f>IF(OR(タスク表[[#This Row],[見積コスト]]="",タスク表[[#This Row],[実コスト]]=""),"",タスク表[[#This Row],[実コスト]]-タスク表[[#This Row],[見積コスト]])</f>
         <v/>
       </c>
-      <c r="J14" s="48"/>
+      <c r="J14" s="48" t="s">
+        <v>14</v>
+      </c>
       <c r="K14" s="51"/>
       <c r="L14" s="52"/>
     </row>
     <row r="15" spans="2:12" x14ac:dyDescent="0.4">
-      <c r="B15" s="46" t="str">
+      <c r="B15" s="46">
         <f>IF(タスク表[[#This Row],[作業内容]]="","",ROW()-ROW(タスク表[#Headers]))</f>
-        <v/>
+        <v>11</v>
       </c>
       <c r="C15" s="44"/>
-      <c r="D15" s="47"/>
+      <c r="D15" s="47" t="s">
+        <v>143</v>
+      </c>
       <c r="E15" s="48"/>
       <c r="F15" s="48"/>
       <c r="G15" s="49"/>
@@ -4851,7 +4888,9 @@
         <f>IF(OR(タスク表[[#This Row],[見積コスト]]="",タスク表[[#This Row],[実コスト]]=""),"",タスク表[[#This Row],[実コスト]]-タスク表[[#This Row],[見積コスト]])</f>
         <v/>
       </c>
-      <c r="J15" s="48"/>
+      <c r="J15" s="48" t="s">
+        <v>50</v>
+      </c>
       <c r="K15" s="51"/>
       <c r="L15" s="52"/>
     </row>
@@ -4862,7 +4901,7 @@
       </c>
       <c r="C16" s="44"/>
       <c r="D16" s="47" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="E16" s="48"/>
       <c r="F16" s="48"/>
@@ -4872,20 +4911,20 @@
         <f>IF(OR(タスク表[[#This Row],[見積コスト]]="",タスク表[[#This Row],[実コスト]]=""),"",タスク表[[#This Row],[実コスト]]-タスク表[[#This Row],[見積コスト]])</f>
         <v/>
       </c>
-      <c r="J16" s="48"/>
+      <c r="J16" s="48" t="s">
+        <v>51</v>
+      </c>
       <c r="K16" s="51"/>
       <c r="L16" s="52"/>
     </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.4">
+    <row r="17" spans="2:12" ht="28.5" x14ac:dyDescent="0.4">
       <c r="B17" s="46">
         <f>IF(タスク表[[#This Row],[作業内容]]="","",ROW()-ROW(タスク表[#Headers]))</f>
         <v>13</v>
       </c>
-      <c r="C17" s="44" t="s">
-        <v>28</v>
-      </c>
+      <c r="C17" s="44"/>
       <c r="D17" s="47" t="s">
-        <v>133</v>
+        <v>161</v>
       </c>
       <c r="E17" s="48"/>
       <c r="F17" s="48"/>
@@ -4896,20 +4935,18 @@
         <v/>
       </c>
       <c r="J17" s="48" t="s">
-        <v>11</v>
+        <v>51</v>
       </c>
       <c r="K17" s="51"/>
       <c r="L17" s="52"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.4">
-      <c r="B18" s="46">
+      <c r="B18" s="46" t="str">
         <f>IF(タスク表[[#This Row],[作業内容]]="","",ROW()-ROW(タスク表[#Headers]))</f>
-        <v>14</v>
+        <v/>
       </c>
       <c r="C18" s="44"/>
-      <c r="D18" s="47" t="s">
-        <v>134</v>
-      </c>
+      <c r="D18" s="47"/>
       <c r="E18" s="48"/>
       <c r="F18" s="48"/>
       <c r="G18" s="49"/>
@@ -4918,24 +4955,18 @@
         <f>IF(OR(タスク表[[#This Row],[見積コスト]]="",タスク表[[#This Row],[実コスト]]=""),"",タスク表[[#This Row],[実コスト]]-タスク表[[#This Row],[見積コスト]])</f>
         <v/>
       </c>
-      <c r="J18" s="48" t="s">
-        <v>11</v>
-      </c>
+      <c r="J18" s="48"/>
       <c r="K18" s="51"/>
       <c r="L18" s="52"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.4">
-      <c r="B19" s="46">
+      <c r="B19" s="46" t="str">
         <f>IF(タスク表[[#This Row],[作業内容]]="","",ROW()-ROW(タスク表[#Headers]))</f>
-        <v>15</v>
+        <v/>
       </c>
       <c r="C19" s="44"/>
-      <c r="D19" s="47" t="s">
-        <v>137</v>
-      </c>
-      <c r="E19" s="48" t="s">
-        <v>41</v>
-      </c>
+      <c r="D19" s="47"/>
+      <c r="E19" s="48"/>
       <c r="F19" s="48"/>
       <c r="G19" s="49"/>
       <c r="H19" s="49"/>
@@ -4943,9 +4974,7 @@
         <f>IF(OR(タスク表[[#This Row],[見積コスト]]="",タスク表[[#This Row],[実コスト]]=""),"",タスク表[[#This Row],[実コスト]]-タスク表[[#This Row],[見積コスト]])</f>
         <v/>
       </c>
-      <c r="J19" s="48" t="s">
-        <v>51</v>
-      </c>
+      <c r="J19" s="48"/>
       <c r="K19" s="51"/>
       <c r="L19" s="52"/>
     </row>
@@ -4954,13 +4983,13 @@
         <f>IF(タスク表[[#This Row],[作業内容]]="","",ROW()-ROW(タスク表[#Headers]))</f>
         <v>16</v>
       </c>
-      <c r="C20" s="44"/>
+      <c r="C20" s="44" t="s">
+        <v>27</v>
+      </c>
       <c r="D20" s="47" t="s">
-        <v>138</v>
-      </c>
-      <c r="E20" s="48" t="s">
-        <v>43</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="E20" s="48"/>
       <c r="F20" s="48"/>
       <c r="G20" s="49"/>
       <c r="H20" s="49"/>
@@ -4968,22 +4997,22 @@
         <f>IF(OR(タスク表[[#This Row],[見積コスト]]="",タスク表[[#This Row],[実コスト]]=""),"",タスク表[[#This Row],[実コスト]]-タスク表[[#This Row],[見積コスト]])</f>
         <v/>
       </c>
-      <c r="J20" s="48"/>
+      <c r="J20" s="48" t="s">
+        <v>14</v>
+      </c>
       <c r="K20" s="51"/>
       <c r="L20" s="52"/>
     </row>
-    <row r="21" spans="2:12" ht="28.5" x14ac:dyDescent="0.4">
+    <row r="21" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B21" s="46">
         <f>IF(タスク表[[#This Row],[作業内容]]="","",ROW()-ROW(タスク表[#Headers]))</f>
         <v>17</v>
       </c>
       <c r="C21" s="44"/>
       <c r="D21" s="47" t="s">
-        <v>143</v>
-      </c>
-      <c r="E21" s="48" t="s">
-        <v>41</v>
-      </c>
+        <v>133</v>
+      </c>
+      <c r="E21" s="48"/>
       <c r="F21" s="48"/>
       <c r="G21" s="49"/>
       <c r="H21" s="49"/>
@@ -4991,7 +5020,9 @@
         <f>IF(OR(タスク表[[#This Row],[見積コスト]]="",タスク表[[#This Row],[実コスト]]=""),"",タスク表[[#This Row],[実コスト]]-タスク表[[#This Row],[見積コスト]])</f>
         <v/>
       </c>
-      <c r="J21" s="48"/>
+      <c r="J21" s="48" t="s">
+        <v>14</v>
+      </c>
       <c r="K21" s="51"/>
       <c r="L21" s="52"/>
     </row>
@@ -5002,9 +5033,11 @@
       </c>
       <c r="C22" s="44"/>
       <c r="D22" s="47" t="s">
-        <v>145</v>
-      </c>
-      <c r="E22" s="48"/>
+        <v>135</v>
+      </c>
+      <c r="E22" s="48" t="s">
+        <v>40</v>
+      </c>
       <c r="F22" s="48"/>
       <c r="G22" s="49"/>
       <c r="H22" s="49"/>
@@ -5013,7 +5046,7 @@
         <v/>
       </c>
       <c r="J22" s="48" t="s">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="K22" s="51"/>
       <c r="L22" s="52"/>
@@ -5025,10 +5058,10 @@
       </c>
       <c r="C23" s="44"/>
       <c r="D23" s="47" t="s">
-        <v>149</v>
+        <v>162</v>
       </c>
       <c r="E23" s="48" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F23" s="48"/>
       <c r="G23" s="49"/>
@@ -5037,21 +5070,23 @@
         <f>IF(OR(タスク表[[#This Row],[見積コスト]]="",タスク表[[#This Row],[実コスト]]=""),"",タスク表[[#This Row],[実コスト]]-タスク表[[#This Row],[見積コスト]])</f>
         <v/>
       </c>
-      <c r="J23" s="48"/>
+      <c r="J23" s="48" t="s">
+        <v>51</v>
+      </c>
       <c r="K23" s="51"/>
       <c r="L23" s="52"/>
     </row>
-    <row r="24" spans="2:12" x14ac:dyDescent="0.4">
+    <row r="24" spans="2:12" ht="28.5" x14ac:dyDescent="0.4">
       <c r="B24" s="46">
         <f>IF(タスク表[[#This Row],[作業内容]]="","",ROW()-ROW(タスク表[#Headers]))</f>
         <v>20</v>
       </c>
       <c r="C24" s="44"/>
       <c r="D24" s="47" t="s">
-        <v>150</v>
+        <v>163</v>
       </c>
       <c r="E24" s="48" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F24" s="48"/>
       <c r="G24" s="49"/>
@@ -5060,24 +5095,20 @@
         <f>IF(OR(タスク表[[#This Row],[見積コスト]]="",タスク表[[#This Row],[実コスト]]=""),"",タスク表[[#This Row],[実コスト]]-タスク表[[#This Row],[見積コスト]])</f>
         <v/>
       </c>
-      <c r="J24" s="48"/>
+      <c r="J24" s="48" t="s">
+        <v>50</v>
+      </c>
       <c r="K24" s="51"/>
       <c r="L24" s="52"/>
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.4">
-      <c r="B25" s="46">
+      <c r="B25" s="46" t="str">
         <f>IF(タスク表[[#This Row],[作業内容]]="","",ROW()-ROW(タスク表[#Headers]))</f>
-        <v>21</v>
-      </c>
-      <c r="C25" s="44" t="s">
-        <v>151</v>
-      </c>
-      <c r="D25" s="47" t="s">
-        <v>152</v>
-      </c>
-      <c r="E25" s="48" t="s">
-        <v>41</v>
-      </c>
+        <v/>
+      </c>
+      <c r="C25" s="44"/>
+      <c r="D25" s="47"/>
+      <c r="E25" s="48"/>
       <c r="F25" s="48"/>
       <c r="G25" s="49"/>
       <c r="H25" s="49"/>
@@ -5090,12 +5121,14 @@
       <c r="L25" s="52"/>
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.4">
-      <c r="B26" s="46" t="str">
+      <c r="B26" s="46">
         <f>IF(タスク表[[#This Row],[作業内容]]="","",ROW()-ROW(タスク表[#Headers]))</f>
-        <v/>
+        <v>22</v>
       </c>
       <c r="C26" s="44"/>
-      <c r="D26" s="47"/>
+      <c r="D26" s="47" t="s">
+        <v>141</v>
+      </c>
       <c r="E26" s="48"/>
       <c r="F26" s="48"/>
       <c r="G26" s="49"/>
@@ -5104,7 +5137,9 @@
         <f>IF(OR(タスク表[[#This Row],[見積コスト]]="",タスク表[[#This Row],[実コスト]]=""),"",タスク表[[#This Row],[実コスト]]-タスク表[[#This Row],[見積コスト]])</f>
         <v/>
       </c>
-      <c r="J26" s="48"/>
+      <c r="J26" s="48" t="s">
+        <v>11</v>
+      </c>
       <c r="K26" s="51"/>
       <c r="L26" s="52"/>
     </row>
@@ -5113,14 +5148,12 @@
         <f>IF(タスク表[[#This Row],[作業内容]]="","",ROW()-ROW(タスク表[#Headers]))</f>
         <v>23</v>
       </c>
-      <c r="C27" s="44" t="s">
-        <v>29</v>
-      </c>
+      <c r="C27" s="44"/>
       <c r="D27" s="47" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="E27" s="48" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F27" s="48"/>
       <c r="G27" s="49"/>
@@ -5129,9 +5162,7 @@
         <f>IF(OR(タスク表[[#This Row],[見積コスト]]="",タスク表[[#This Row],[実コスト]]=""),"",タスク表[[#This Row],[実コスト]]-タスク表[[#This Row],[見積コスト]])</f>
         <v/>
       </c>
-      <c r="J27" s="48" t="s">
-        <v>50</v>
-      </c>
+      <c r="J27" s="48"/>
       <c r="K27" s="51"/>
       <c r="L27" s="52"/>
     </row>
@@ -5142,10 +5173,10 @@
       </c>
       <c r="C28" s="44"/>
       <c r="D28" s="47" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="E28" s="48" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="F28" s="48"/>
       <c r="G28" s="49"/>
@@ -5154,9 +5185,7 @@
         <f>IF(OR(タスク表[[#This Row],[見積コスト]]="",タスク表[[#This Row],[実コスト]]=""),"",タスク表[[#This Row],[実コスト]]-タスク表[[#This Row],[見積コスト]])</f>
         <v/>
       </c>
-      <c r="J28" s="48" t="s">
-        <v>50</v>
-      </c>
+      <c r="J28" s="48"/>
       <c r="K28" s="51"/>
       <c r="L28" s="52"/>
     </row>
@@ -5167,11 +5196,9 @@
       </c>
       <c r="C29" s="44"/>
       <c r="D29" s="47" t="s">
-        <v>147</v>
-      </c>
-      <c r="E29" s="48" t="s">
-        <v>41</v>
-      </c>
+        <v>159</v>
+      </c>
+      <c r="E29" s="48"/>
       <c r="F29" s="48"/>
       <c r="G29" s="49"/>
       <c r="H29" s="49"/>
@@ -5208,13 +5235,13 @@
         <v>27</v>
       </c>
       <c r="C31" s="44" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="D31" s="47" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="E31" s="48" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F31" s="48"/>
       <c r="G31" s="49"/>
@@ -5232,13 +5259,13 @@
         <f>IF(タスク表[[#This Row],[作業内容]]="","",ROW()-ROW(タスク表[#Headers]))</f>
         <v>28</v>
       </c>
-      <c r="C32" s="44"/>
+      <c r="C32" s="44" t="s">
+        <v>28</v>
+      </c>
       <c r="D32" s="47" t="s">
-        <v>155</v>
-      </c>
-      <c r="E32" s="48" t="s">
-        <v>43</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="E32" s="48"/>
       <c r="F32" s="48"/>
       <c r="G32" s="49"/>
       <c r="H32" s="49"/>
@@ -5257,7 +5284,9 @@
       </c>
       <c r="C33" s="44"/>
       <c r="D33" s="47"/>
-      <c r="E33" s="48"/>
+      <c r="E33" s="48" t="s">
+        <v>40</v>
+      </c>
       <c r="F33" s="48"/>
       <c r="G33" s="49"/>
       <c r="H33" s="49"/>
@@ -5265,18 +5294,24 @@
         <f>IF(OR(タスク表[[#This Row],[見積コスト]]="",タスク表[[#This Row],[実コスト]]=""),"",タスク表[[#This Row],[実コスト]]-タスク表[[#This Row],[見積コスト]])</f>
         <v/>
       </c>
-      <c r="J33" s="48"/>
+      <c r="J33" s="48" t="s">
+        <v>49</v>
+      </c>
       <c r="K33" s="51"/>
       <c r="L33" s="52"/>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.4">
-      <c r="B34" s="46" t="str">
+      <c r="B34" s="46">
         <f>IF(タスク表[[#This Row],[作業内容]]="","",ROW()-ROW(タスク表[#Headers]))</f>
-        <v/>
+        <v>30</v>
       </c>
       <c r="C34" s="44"/>
-      <c r="D34" s="47"/>
-      <c r="E34" s="48"/>
+      <c r="D34" s="47" t="s">
+        <v>144</v>
+      </c>
+      <c r="E34" s="48" t="s">
+        <v>44</v>
+      </c>
       <c r="F34" s="48"/>
       <c r="G34" s="49"/>
       <c r="H34" s="49"/>
@@ -5284,18 +5319,24 @@
         <f>IF(OR(タスク表[[#This Row],[見積コスト]]="",タスク表[[#This Row],[実コスト]]=""),"",タスク表[[#This Row],[実コスト]]-タスク表[[#This Row],[見積コスト]])</f>
         <v/>
       </c>
-      <c r="J34" s="48"/>
+      <c r="J34" s="48" t="s">
+        <v>49</v>
+      </c>
       <c r="K34" s="51"/>
       <c r="L34" s="52"/>
     </row>
     <row r="35" spans="2:12" x14ac:dyDescent="0.4">
-      <c r="B35" s="46" t="str">
+      <c r="B35" s="46">
         <f>IF(タスク表[[#This Row],[作業内容]]="","",ROW()-ROW(タスク表[#Headers]))</f>
-        <v/>
+        <v>31</v>
       </c>
       <c r="C35" s="44"/>
-      <c r="D35" s="47"/>
-      <c r="E35" s="48"/>
+      <c r="D35" s="47" t="s">
+        <v>143</v>
+      </c>
+      <c r="E35" s="48" t="s">
+        <v>40</v>
+      </c>
       <c r="F35" s="48"/>
       <c r="G35" s="49"/>
       <c r="H35" s="49"/>
@@ -5327,13 +5368,19 @@
       <c r="L36" s="52"/>
     </row>
     <row r="37" spans="2:12" x14ac:dyDescent="0.4">
-      <c r="B37" s="46" t="str">
+      <c r="B37" s="46">
         <f>IF(タスク表[[#This Row],[作業内容]]="","",ROW()-ROW(タスク表[#Headers]))</f>
-        <v/>
-      </c>
-      <c r="C37" s="44"/>
-      <c r="D37" s="47"/>
-      <c r="E37" s="48"/>
+        <v>33</v>
+      </c>
+      <c r="C37" s="44" t="s">
+        <v>149</v>
+      </c>
+      <c r="D37" s="47" t="s">
+        <v>150</v>
+      </c>
+      <c r="E37" s="48" t="s">
+        <v>42</v>
+      </c>
       <c r="F37" s="48"/>
       <c r="G37" s="49"/>
       <c r="H37" s="49"/>
@@ -5346,13 +5393,17 @@
       <c r="L37" s="52"/>
     </row>
     <row r="38" spans="2:12" x14ac:dyDescent="0.4">
-      <c r="B38" s="46" t="str">
+      <c r="B38" s="46">
         <f>IF(タスク表[[#This Row],[作業内容]]="","",ROW()-ROW(タスク表[#Headers]))</f>
-        <v/>
+        <v>34</v>
       </c>
       <c r="C38" s="44"/>
-      <c r="D38" s="47"/>
-      <c r="E38" s="48"/>
+      <c r="D38" s="47" t="s">
+        <v>151</v>
+      </c>
+      <c r="E38" s="48" t="s">
+        <v>42</v>
+      </c>
       <c r="F38" s="48"/>
       <c r="G38" s="49"/>
       <c r="H38" s="49"/>
@@ -5365,16 +5416,12 @@
       <c r="L38" s="52"/>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.4">
-      <c r="B39" s="46">
+      <c r="B39" s="46" t="str">
         <f>IF(タスク表[[#This Row],[作業内容]]="","",ROW()-ROW(タスク表[#Headers]))</f>
-        <v>35</v>
-      </c>
-      <c r="C39" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="D39" s="47" t="s">
-        <v>139</v>
-      </c>
+        <v/>
+      </c>
+      <c r="C39" s="44"/>
+      <c r="D39" s="47"/>
       <c r="E39" s="48"/>
       <c r="F39" s="48"/>
       <c r="G39" s="49"/>
@@ -5388,16 +5435,12 @@
       <c r="L39" s="52"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.4">
-      <c r="B40" s="46">
+      <c r="B40" s="46" t="str">
         <f>IF(タスク表[[#This Row],[作業内容]]="","",ROW()-ROW(タスク表[#Headers]))</f>
-        <v>36</v>
-      </c>
-      <c r="C40" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="D40" s="47" t="s">
-        <v>140</v>
-      </c>
+        <v/>
+      </c>
+      <c r="C40" s="44"/>
+      <c r="D40" s="47"/>
       <c r="E40" s="48"/>
       <c r="F40" s="48"/>
       <c r="G40" s="49"/>
@@ -5411,14 +5454,12 @@
       <c r="L40" s="52"/>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.4">
-      <c r="B41" s="46">
+      <c r="B41" s="46" t="str">
         <f>IF(タスク表[[#This Row],[作業内容]]="","",ROW()-ROW(タスク表[#Headers]))</f>
-        <v>37</v>
+        <v/>
       </c>
       <c r="C41" s="44"/>
-      <c r="D41" s="47" t="s">
-        <v>141</v>
-      </c>
+      <c r="D41" s="47"/>
       <c r="E41" s="48"/>
       <c r="F41" s="48"/>
       <c r="G41" s="49"/>
@@ -5451,14 +5492,12 @@
       <c r="L42" s="52"/>
     </row>
     <row r="43" spans="2:12" x14ac:dyDescent="0.4">
-      <c r="B43" s="46">
+      <c r="B43" s="46" t="str">
         <f>IF(タスク表[[#This Row],[作業内容]]="","",ROW()-ROW(タスク表[#Headers]))</f>
-        <v>39</v>
+        <v/>
       </c>
       <c r="C43" s="44"/>
-      <c r="D43" s="47" t="s">
-        <v>146</v>
-      </c>
+      <c r="D43" s="47"/>
       <c r="E43" s="48"/>
       <c r="F43" s="48"/>
       <c r="G43" s="49"/>
@@ -5472,19 +5511,13 @@
       <c r="L43" s="52"/>
     </row>
     <row r="44" spans="2:12" x14ac:dyDescent="0.4">
-      <c r="B44" s="46">
+      <c r="B44" s="46" t="str">
         <f>IF(タスク表[[#This Row],[作業内容]]="","",ROW()-ROW(タスク表[#Headers]))</f>
-        <v>40</v>
-      </c>
-      <c r="C44" s="44" t="s">
-        <v>31</v>
-      </c>
-      <c r="D44" s="47" t="s">
-        <v>156</v>
-      </c>
-      <c r="E44" s="48" t="s">
-        <v>41</v>
-      </c>
+        <v/>
+      </c>
+      <c r="C44" s="44"/>
+      <c r="D44" s="47"/>
+      <c r="E44" s="48"/>
       <c r="F44" s="48"/>
       <c r="G44" s="49"/>
       <c r="H44" s="49"/>
@@ -5501,13 +5534,13 @@
         <f>IF(タスク表[[#This Row],[作業内容]]="","",ROW()-ROW(タスク表[#Headers]))</f>
         <v>41</v>
       </c>
-      <c r="C45" s="44"/>
+      <c r="C45" s="44" t="s">
+        <v>35</v>
+      </c>
       <c r="D45" s="47" t="s">
-        <v>157</v>
-      </c>
-      <c r="E45" s="48" t="s">
-        <v>41</v>
-      </c>
+        <v>136</v>
+      </c>
+      <c r="E45" s="48"/>
       <c r="F45" s="48"/>
       <c r="G45" s="49"/>
       <c r="H45" s="49"/>
@@ -5520,12 +5553,16 @@
       <c r="L45" s="52"/>
     </row>
     <row r="46" spans="2:12" x14ac:dyDescent="0.4">
-      <c r="B46" s="46" t="str">
+      <c r="B46" s="46">
         <f>IF(タスク表[[#This Row],[作業内容]]="","",ROW()-ROW(タスク表[#Headers]))</f>
-        <v/>
-      </c>
-      <c r="C46" s="44"/>
-      <c r="D46" s="47"/>
+        <v>42</v>
+      </c>
+      <c r="C46" s="44" t="s">
+        <v>35</v>
+      </c>
+      <c r="D46" s="47" t="s">
+        <v>137</v>
+      </c>
       <c r="E46" s="48"/>
       <c r="F46" s="48"/>
       <c r="G46" s="49"/>
@@ -5539,12 +5576,14 @@
       <c r="L46" s="52"/>
     </row>
     <row r="47" spans="2:12" x14ac:dyDescent="0.4">
-      <c r="B47" s="46" t="str">
+      <c r="B47" s="46">
         <f>IF(タスク表[[#This Row],[作業内容]]="","",ROW()-ROW(タスク表[#Headers]))</f>
-        <v/>
+        <v>43</v>
       </c>
       <c r="C47" s="44"/>
-      <c r="D47" s="47"/>
+      <c r="D47" s="47" t="s">
+        <v>138</v>
+      </c>
       <c r="E47" s="48"/>
       <c r="F47" s="48"/>
       <c r="G47" s="49"/>
@@ -5577,12 +5616,14 @@
       <c r="L48" s="52"/>
     </row>
     <row r="49" spans="2:12" x14ac:dyDescent="0.4">
-      <c r="B49" s="46" t="str">
+      <c r="B49" s="46">
         <f>IF(タスク表[[#This Row],[作業内容]]="","",ROW()-ROW(タスク表[#Headers]))</f>
-        <v/>
+        <v>45</v>
       </c>
       <c r="C49" s="44"/>
-      <c r="D49" s="47"/>
+      <c r="D49" s="47" t="s">
+        <v>142</v>
+      </c>
       <c r="E49" s="48"/>
       <c r="F49" s="48"/>
       <c r="G49" s="49"/>
@@ -5596,13 +5637,19 @@
       <c r="L49" s="52"/>
     </row>
     <row r="50" spans="2:12" x14ac:dyDescent="0.4">
-      <c r="B50" s="46" t="str">
+      <c r="B50" s="46">
         <f>IF(タスク表[[#This Row],[作業内容]]="","",ROW()-ROW(タスク表[#Headers]))</f>
-        <v/>
-      </c>
-      <c r="C50" s="44"/>
-      <c r="D50" s="47"/>
-      <c r="E50" s="48"/>
+        <v>46</v>
+      </c>
+      <c r="C50" s="44" t="s">
+        <v>30</v>
+      </c>
+      <c r="D50" s="47" t="s">
+        <v>152</v>
+      </c>
+      <c r="E50" s="48" t="s">
+        <v>40</v>
+      </c>
       <c r="F50" s="48"/>
       <c r="G50" s="49"/>
       <c r="H50" s="49"/>
@@ -5615,13 +5662,17 @@
       <c r="L50" s="52"/>
     </row>
     <row r="51" spans="2:12" x14ac:dyDescent="0.4">
-      <c r="B51" s="46" t="str">
+      <c r="B51" s="46">
         <f>IF(タスク表[[#This Row],[作業内容]]="","",ROW()-ROW(タスク表[#Headers]))</f>
-        <v/>
+        <v>47</v>
       </c>
       <c r="C51" s="44"/>
-      <c r="D51" s="47"/>
-      <c r="E51" s="48"/>
+      <c r="D51" s="47" t="s">
+        <v>153</v>
+      </c>
+      <c r="E51" s="48" t="s">
+        <v>40</v>
+      </c>
       <c r="F51" s="48"/>
       <c r="G51" s="49"/>
       <c r="H51" s="49"/>
@@ -5748,76 +5799,118 @@
       <c r="L57" s="52"/>
     </row>
     <row r="58" spans="2:12" x14ac:dyDescent="0.4">
-      <c r="B58" s="11"/>
-      <c r="D58" s="15"/>
-      <c r="E58" s="11"/>
-      <c r="F58" s="11"/>
-      <c r="G58" s="12"/>
-      <c r="H58" s="12"/>
-      <c r="I58" s="13"/>
-      <c r="J58" s="11"/>
-      <c r="K58" s="14"/>
-      <c r="L58" s="15"/>
+      <c r="B58" s="46" t="str">
+        <f>IF(タスク表[[#This Row],[作業内容]]="","",ROW()-ROW(タスク表[#Headers]))</f>
+        <v/>
+      </c>
+      <c r="C58" s="44"/>
+      <c r="D58" s="47"/>
+      <c r="E58" s="48"/>
+      <c r="F58" s="48"/>
+      <c r="G58" s="49"/>
+      <c r="H58" s="49"/>
+      <c r="I58" s="50" t="str">
+        <f>IF(OR(タスク表[[#This Row],[見積コスト]]="",タスク表[[#This Row],[実コスト]]=""),"",タスク表[[#This Row],[実コスト]]-タスク表[[#This Row],[見積コスト]])</f>
+        <v/>
+      </c>
+      <c r="J58" s="48"/>
+      <c r="K58" s="51"/>
+      <c r="L58" s="52"/>
     </row>
     <row r="59" spans="2:12" x14ac:dyDescent="0.4">
-      <c r="B59" s="11"/>
-      <c r="D59" s="15"/>
-      <c r="E59" s="11"/>
-      <c r="F59" s="11"/>
-      <c r="G59" s="12"/>
-      <c r="H59" s="12"/>
-      <c r="I59" s="13"/>
-      <c r="J59" s="11"/>
-      <c r="K59" s="14"/>
-      <c r="L59" s="15"/>
+      <c r="B59" s="46" t="str">
+        <f>IF(タスク表[[#This Row],[作業内容]]="","",ROW()-ROW(タスク表[#Headers]))</f>
+        <v/>
+      </c>
+      <c r="C59" s="44"/>
+      <c r="D59" s="47"/>
+      <c r="E59" s="48"/>
+      <c r="F59" s="48"/>
+      <c r="G59" s="49"/>
+      <c r="H59" s="49"/>
+      <c r="I59" s="50" t="str">
+        <f>IF(OR(タスク表[[#This Row],[見積コスト]]="",タスク表[[#This Row],[実コスト]]=""),"",タスク表[[#This Row],[実コスト]]-タスク表[[#This Row],[見積コスト]])</f>
+        <v/>
+      </c>
+      <c r="J59" s="48"/>
+      <c r="K59" s="51"/>
+      <c r="L59" s="52"/>
     </row>
     <row r="60" spans="2:12" x14ac:dyDescent="0.4">
-      <c r="B60" s="11"/>
-      <c r="D60" s="15"/>
-      <c r="E60" s="11"/>
-      <c r="F60" s="11"/>
-      <c r="G60" s="12"/>
-      <c r="H60" s="12"/>
-      <c r="I60" s="13"/>
-      <c r="J60" s="11"/>
-      <c r="K60" s="14"/>
-      <c r="L60" s="15"/>
+      <c r="B60" s="46" t="str">
+        <f>IF(タスク表[[#This Row],[作業内容]]="","",ROW()-ROW(タスク表[#Headers]))</f>
+        <v/>
+      </c>
+      <c r="C60" s="44"/>
+      <c r="D60" s="47"/>
+      <c r="E60" s="48"/>
+      <c r="F60" s="48"/>
+      <c r="G60" s="49"/>
+      <c r="H60" s="49"/>
+      <c r="I60" s="50" t="str">
+        <f>IF(OR(タスク表[[#This Row],[見積コスト]]="",タスク表[[#This Row],[実コスト]]=""),"",タスク表[[#This Row],[実コスト]]-タスク表[[#This Row],[見積コスト]])</f>
+        <v/>
+      </c>
+      <c r="J60" s="48"/>
+      <c r="K60" s="51"/>
+      <c r="L60" s="52"/>
     </row>
     <row r="61" spans="2:12" x14ac:dyDescent="0.4">
-      <c r="B61" s="11"/>
-      <c r="D61" s="15"/>
-      <c r="E61" s="11"/>
-      <c r="F61" s="11"/>
-      <c r="G61" s="12"/>
-      <c r="H61" s="12"/>
-      <c r="I61" s="13"/>
-      <c r="J61" s="11"/>
-      <c r="K61" s="14"/>
-      <c r="L61" s="15"/>
+      <c r="B61" s="46" t="str">
+        <f>IF(タスク表[[#This Row],[作業内容]]="","",ROW()-ROW(タスク表[#Headers]))</f>
+        <v/>
+      </c>
+      <c r="C61" s="44"/>
+      <c r="D61" s="47"/>
+      <c r="E61" s="48"/>
+      <c r="F61" s="48"/>
+      <c r="G61" s="49"/>
+      <c r="H61" s="49"/>
+      <c r="I61" s="50" t="str">
+        <f>IF(OR(タスク表[[#This Row],[見積コスト]]="",タスク表[[#This Row],[実コスト]]=""),"",タスク表[[#This Row],[実コスト]]-タスク表[[#This Row],[見積コスト]])</f>
+        <v/>
+      </c>
+      <c r="J61" s="48"/>
+      <c r="K61" s="51"/>
+      <c r="L61" s="52"/>
     </row>
     <row r="62" spans="2:12" x14ac:dyDescent="0.4">
-      <c r="B62" s="11"/>
-      <c r="D62" s="15"/>
-      <c r="E62" s="11"/>
-      <c r="F62" s="11"/>
-      <c r="G62" s="12"/>
-      <c r="H62" s="12"/>
-      <c r="I62" s="13"/>
-      <c r="J62" s="11"/>
-      <c r="K62" s="14"/>
-      <c r="L62" s="15"/>
+      <c r="B62" s="46" t="str">
+        <f>IF(タスク表[[#This Row],[作業内容]]="","",ROW()-ROW(タスク表[#Headers]))</f>
+        <v/>
+      </c>
+      <c r="C62" s="44"/>
+      <c r="D62" s="47"/>
+      <c r="E62" s="48"/>
+      <c r="F62" s="48"/>
+      <c r="G62" s="49"/>
+      <c r="H62" s="49"/>
+      <c r="I62" s="50" t="str">
+        <f>IF(OR(タスク表[[#This Row],[見積コスト]]="",タスク表[[#This Row],[実コスト]]=""),"",タスク表[[#This Row],[実コスト]]-タスク表[[#This Row],[見積コスト]])</f>
+        <v/>
+      </c>
+      <c r="J62" s="48"/>
+      <c r="K62" s="51"/>
+      <c r="L62" s="52"/>
     </row>
     <row r="63" spans="2:12" x14ac:dyDescent="0.4">
-      <c r="B63" s="11"/>
-      <c r="D63" s="15"/>
-      <c r="E63" s="11"/>
-      <c r="F63" s="11"/>
-      <c r="G63" s="12"/>
-      <c r="H63" s="12"/>
-      <c r="I63" s="13"/>
-      <c r="J63" s="11"/>
-      <c r="K63" s="14"/>
-      <c r="L63" s="15"/>
+      <c r="B63" s="46" t="str">
+        <f>IF(タスク表[[#This Row],[作業内容]]="","",ROW()-ROW(タスク表[#Headers]))</f>
+        <v/>
+      </c>
+      <c r="C63" s="44"/>
+      <c r="D63" s="47"/>
+      <c r="E63" s="48"/>
+      <c r="F63" s="48"/>
+      <c r="G63" s="49"/>
+      <c r="H63" s="49"/>
+      <c r="I63" s="50" t="str">
+        <f>IF(OR(タスク表[[#This Row],[見積コスト]]="",タスク表[[#This Row],[実コスト]]=""),"",タスク表[[#This Row],[実コスト]]-タスク表[[#This Row],[見積コスト]])</f>
+        <v/>
+      </c>
+      <c r="J63" s="48"/>
+      <c r="K63" s="51"/>
+      <c r="L63" s="52"/>
     </row>
     <row r="64" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B64" s="11"/>
@@ -17111,181 +17204,260 @@
       <c r="K1004" s="14"/>
       <c r="L1004" s="15"/>
     </row>
+    <row r="1005" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B1005" s="11"/>
+      <c r="D1005" s="15"/>
+      <c r="E1005" s="11"/>
+      <c r="F1005" s="11"/>
+      <c r="G1005" s="12"/>
+      <c r="H1005" s="12"/>
+      <c r="I1005" s="13"/>
+      <c r="J1005" s="11"/>
+      <c r="K1005" s="14"/>
+      <c r="L1005" s="15"/>
+    </row>
+    <row r="1006" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B1006" s="11"/>
+      <c r="D1006" s="15"/>
+      <c r="E1006" s="11"/>
+      <c r="F1006" s="11"/>
+      <c r="G1006" s="12"/>
+      <c r="H1006" s="12"/>
+      <c r="I1006" s="13"/>
+      <c r="J1006" s="11"/>
+      <c r="K1006" s="14"/>
+      <c r="L1006" s="15"/>
+    </row>
+    <row r="1007" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B1007" s="11"/>
+      <c r="D1007" s="15"/>
+      <c r="E1007" s="11"/>
+      <c r="F1007" s="11"/>
+      <c r="G1007" s="12"/>
+      <c r="H1007" s="12"/>
+      <c r="I1007" s="13"/>
+      <c r="J1007" s="11"/>
+      <c r="K1007" s="14"/>
+      <c r="L1007" s="15"/>
+    </row>
+    <row r="1008" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B1008" s="11"/>
+      <c r="D1008" s="15"/>
+      <c r="E1008" s="11"/>
+      <c r="F1008" s="11"/>
+      <c r="G1008" s="12"/>
+      <c r="H1008" s="12"/>
+      <c r="I1008" s="13"/>
+      <c r="J1008" s="11"/>
+      <c r="K1008" s="14"/>
+      <c r="L1008" s="15"/>
+    </row>
+    <row r="1009" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B1009" s="11"/>
+      <c r="D1009" s="15"/>
+      <c r="E1009" s="11"/>
+      <c r="F1009" s="11"/>
+      <c r="G1009" s="12"/>
+      <c r="H1009" s="12"/>
+      <c r="I1009" s="13"/>
+      <c r="J1009" s="11"/>
+      <c r="K1009" s="14"/>
+      <c r="L1009" s="15"/>
+    </row>
+    <row r="1010" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B1010" s="11"/>
+      <c r="D1010" s="15"/>
+      <c r="E1010" s="11"/>
+      <c r="F1010" s="11"/>
+      <c r="G1010" s="12"/>
+      <c r="H1010" s="12"/>
+      <c r="I1010" s="13"/>
+      <c r="J1010" s="11"/>
+      <c r="K1010" s="14"/>
+      <c r="L1010" s="15"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="6"/>
-  <conditionalFormatting sqref="B5:L7 B8:B10 E8:L10 B11:L20 E21:L22 C22:D22 C27:E28 B21:B33 F23:L33 B39:B44 F39:L44 B34:L38 B45:L1004 E29">
-    <cfRule type="expression" dxfId="49" priority="13" stopIfTrue="1">
+  <conditionalFormatting sqref="B5:L7 B8:B10 E8:L10 B11:L23 E24:L26 C26:D26 E35 B40:L44 B45:B50 F45:L50 B51:L1010 B24:B39 F27:L39 C34:E34 E33">
+    <cfRule type="expression" dxfId="52" priority="13" stopIfTrue="1">
       <formula>AND($J5&lt;&gt;"",$J5=除外ST)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="48" priority="14" stopIfTrue="1">
+    <cfRule type="expression" dxfId="51" priority="14" stopIfTrue="1">
       <formula>AND($J5&lt;&gt;"",$J5=完了ST)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="47" priority="15" stopIfTrue="1">
+    <cfRule type="expression" dxfId="50" priority="15" stopIfTrue="1">
       <formula>$J5="作業中"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C17:D18">
-    <cfRule type="expression" dxfId="46" priority="23" stopIfTrue="1">
+  <conditionalFormatting sqref="C20:D21">
+    <cfRule type="expression" dxfId="49" priority="23" stopIfTrue="1">
       <formula>AND($J8&lt;&gt;"",$J8=除外ST)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="45" priority="24" stopIfTrue="1">
+    <cfRule type="expression" dxfId="48" priority="24" stopIfTrue="1">
       <formula>AND($J8&lt;&gt;"",$J8=完了ST)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="44" priority="25" stopIfTrue="1">
+    <cfRule type="expression" dxfId="47" priority="25" stopIfTrue="1">
       <formula>$J8="作業中"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C27:D27">
-    <cfRule type="expression" dxfId="43" priority="29" stopIfTrue="1">
-      <formula>AND($J21&lt;&gt;"",$J21=除外ST)</formula>
+  <conditionalFormatting sqref="C24:D24">
+    <cfRule type="expression" dxfId="46" priority="29" stopIfTrue="1">
+      <formula>AND($J24&lt;&gt;"",$J24=除外ST)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="42" priority="30" stopIfTrue="1">
-      <formula>AND($J21&lt;&gt;"",$J21=完了ST)</formula>
+    <cfRule type="expression" dxfId="45" priority="30" stopIfTrue="1">
+      <formula>AND($J24&lt;&gt;"",$J24=完了ST)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="41" priority="31" stopIfTrue="1">
-      <formula>$J21="作業中"</formula>
+    <cfRule type="expression" dxfId="44" priority="31" stopIfTrue="1">
+      <formula>$J24="作業中"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E44:E1004 E5:E29 E31:E41">
-    <cfRule type="expression" dxfId="40" priority="16" stopIfTrue="1">
+  <conditionalFormatting sqref="C38:E38">
+    <cfRule type="expression" dxfId="43" priority="117" stopIfTrue="1">
+      <formula>AND($J31&lt;&gt;"",$J31=除外ST)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="42" priority="118" stopIfTrue="1">
+      <formula>AND($J31&lt;&gt;"",$J31=完了ST)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="41" priority="119" stopIfTrue="1">
+      <formula>$J31="作業中"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C39:E39 E35">
+    <cfRule type="expression" dxfId="40" priority="153" stopIfTrue="1">
+      <formula>AND($J31&lt;&gt;"",$J31=除外ST)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="39" priority="154" stopIfTrue="1">
+      <formula>AND($J31&lt;&gt;"",$J31=完了ST)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="38" priority="155" stopIfTrue="1">
+      <formula>$J31="作業中"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C45:E45">
+    <cfRule type="expression" dxfId="37" priority="111" stopIfTrue="1">
+      <formula>AND($J32&lt;&gt;"",$J32=除外ST)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="36" priority="112" stopIfTrue="1">
+      <formula>AND($J32&lt;&gt;"",$J32=完了ST)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="35" priority="113" stopIfTrue="1">
+      <formula>$J32="作業中"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C46:E47">
+    <cfRule type="expression" dxfId="34" priority="171" stopIfTrue="1">
+      <formula>AND($J36&lt;&gt;"",$J36=除外ST)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="33" priority="172" stopIfTrue="1">
+      <formula>AND($J36&lt;&gt;"",$J36=完了ST)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="32" priority="173" stopIfTrue="1">
+      <formula>$J36="作業中"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C50:E50">
+    <cfRule type="expression" dxfId="31" priority="35" stopIfTrue="1">
+      <formula>AND($J38&lt;&gt;"",$J38=除外ST)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="30" priority="36" stopIfTrue="1">
+      <formula>AND($J38&lt;&gt;"",$J38=完了ST)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="29" priority="37" stopIfTrue="1">
+      <formula>$J38="作業中"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E37:E47 E50:E1010 E5:E35">
+    <cfRule type="expression" dxfId="28" priority="16" stopIfTrue="1">
       <formula>E5="S"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="39" priority="17" stopIfTrue="1">
+    <cfRule type="expression" dxfId="27" priority="17" stopIfTrue="1">
       <formula>E5="A"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C44:E44">
-    <cfRule type="expression" dxfId="38" priority="35" stopIfTrue="1">
-      <formula>AND($J32&lt;&gt;"",$J32=除外ST)</formula>
+  <conditionalFormatting sqref="E27:E32">
+    <cfRule type="expression" dxfId="26" priority="7" stopIfTrue="1">
+      <formula>AND($J27&lt;&gt;"",$J27=除外ST)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="37" priority="36" stopIfTrue="1">
-      <formula>AND($J32&lt;&gt;"",$J32=完了ST)</formula>
+    <cfRule type="expression" dxfId="25" priority="8" stopIfTrue="1">
+      <formula>AND($J27&lt;&gt;"",$J27=完了ST)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="36" priority="37" stopIfTrue="1">
-      <formula>$J32="作業中"</formula>
+    <cfRule type="expression" dxfId="24" priority="9" stopIfTrue="1">
+      <formula>$J27="作業中"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="23" priority="10" stopIfTrue="1">
+      <formula>AND($J27&lt;&gt;"",$J27=除外ST)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="22" priority="11" stopIfTrue="1">
+      <formula>AND($J27&lt;&gt;"",$J27=完了ST)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="21" priority="12" stopIfTrue="1">
+      <formula>$J27="作業中"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I5:I1004">
-    <cfRule type="expression" dxfId="35" priority="18" stopIfTrue="1">
+  <conditionalFormatting sqref="E37:E38">
+    <cfRule type="expression" dxfId="20" priority="1" stopIfTrue="1">
+      <formula>AND($J37&lt;&gt;"",$J37=除外ST)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="19" priority="2" stopIfTrue="1">
+      <formula>AND($J37&lt;&gt;"",$J37=完了ST)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="18" priority="3" stopIfTrue="1">
+      <formula>$J37="作業中"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="17" priority="4" stopIfTrue="1">
+      <formula>AND($J33&lt;&gt;"",$J33=除外ST)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="16" priority="5" stopIfTrue="1">
+      <formula>AND($J33&lt;&gt;"",$J33=完了ST)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="15" priority="6" stopIfTrue="1">
+      <formula>$J33="作業中"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I5:I1010">
+    <cfRule type="expression" dxfId="14" priority="18" stopIfTrue="1">
       <formula>AND(ISNUMBER(I5),I5&gt;0)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="34" priority="19" stopIfTrue="1">
+    <cfRule type="expression" dxfId="13" priority="19" stopIfTrue="1">
       <formula>AND(ISNUMBER(I5),I5&lt;0)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E27:E29">
-    <cfRule type="expression" dxfId="33" priority="50" stopIfTrue="1">
-      <formula>AND($J23&lt;&gt;"",$J23=除外ST)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="32" priority="51" stopIfTrue="1">
-      <formula>AND($J23&lt;&gt;"",$J23=完了ST)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="31" priority="52" stopIfTrue="1">
-      <formula>$J23="作業中"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C39:E39">
-    <cfRule type="expression" dxfId="30" priority="111" stopIfTrue="1">
-      <formula>AND($J26&lt;&gt;"",$J26=除外ST)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="29" priority="112" stopIfTrue="1">
-      <formula>AND($J26&lt;&gt;"",$J26=完了ST)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="28" priority="113" stopIfTrue="1">
-      <formula>$J26="作業中"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C32:E32">
-    <cfRule type="expression" dxfId="27" priority="117" stopIfTrue="1">
-      <formula>AND($J25&lt;&gt;"",$J25=除外ST)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="26" priority="118" stopIfTrue="1">
-      <formula>AND($J25&lt;&gt;"",$J25=完了ST)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="25" priority="119" stopIfTrue="1">
-      <formula>$J25="作業中"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C33:E33">
-    <cfRule type="expression" dxfId="24" priority="153" stopIfTrue="1">
-      <formula>AND($J29&lt;&gt;"",$J29=除外ST)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="23" priority="154" stopIfTrue="1">
-      <formula>AND($J29&lt;&gt;"",$J29=完了ST)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="22" priority="155" stopIfTrue="1">
-      <formula>$J29="作業中"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C40:E41">
-    <cfRule type="expression" dxfId="21" priority="171" stopIfTrue="1">
-      <formula>AND($J30&lt;&gt;"",$J30=除外ST)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="20" priority="172" stopIfTrue="1">
-      <formula>AND($J30&lt;&gt;"",$J30=完了ST)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="19" priority="173" stopIfTrue="1">
-      <formula>$J30="作業中"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E23:E26">
-    <cfRule type="expression" dxfId="18" priority="10" stopIfTrue="1">
-      <formula>AND($J23&lt;&gt;"",$J23=除外ST)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="17" priority="11" stopIfTrue="1">
-      <formula>AND($J23&lt;&gt;"",$J23=完了ST)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="16" priority="12" stopIfTrue="1">
-      <formula>$J23="作業中"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E23:E26">
-    <cfRule type="expression" dxfId="15" priority="7" stopIfTrue="1">
-      <formula>AND($J23&lt;&gt;"",$J23=除外ST)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="14" priority="8" stopIfTrue="1">
-      <formula>AND($J23&lt;&gt;"",$J23=完了ST)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="13" priority="9" stopIfTrue="1">
-      <formula>$J23="作業中"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E31:E32">
-    <cfRule type="expression" dxfId="12" priority="1" stopIfTrue="1">
-      <formula>AND($J31&lt;&gt;"",$J31=除外ST)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="11" priority="2" stopIfTrue="1">
-      <formula>AND($J31&lt;&gt;"",$J31=完了ST)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="10" priority="3" stopIfTrue="1">
-      <formula>$J31="作業中"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E31:E32">
-    <cfRule type="expression" dxfId="9" priority="4" stopIfTrue="1">
+  <conditionalFormatting sqref="E33:E34">
+    <cfRule type="expression" dxfId="12" priority="174" stopIfTrue="1">
       <formula>AND($J27&lt;&gt;"",$J27=除外ST)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="8" priority="5" stopIfTrue="1">
+    <cfRule type="expression" dxfId="11" priority="175" stopIfTrue="1">
       <formula>AND($J27&lt;&gt;"",$J27=完了ST)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="7" priority="6" stopIfTrue="1">
+    <cfRule type="expression" dxfId="10" priority="176" stopIfTrue="1">
       <formula>$J27="作業中"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="C24:D24">
+    <cfRule type="expression" dxfId="9" priority="180" stopIfTrue="1">
+      <formula>AND($J33&lt;&gt;"",$J33=除外ST)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="8" priority="181" stopIfTrue="1">
+      <formula>AND($J33&lt;&gt;"",$J33=完了ST)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="7" priority="182" stopIfTrue="1">
+      <formula>$J33="作業中"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="5">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C5:C7 C11:C20 C22 C27:C28 C44:C1004 C32:C41" xr:uid="{E6BBE5BD-7004-4694-85A6-704154467F57}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C5:C7 C26 C50:C1010 C38:C47 C11:C24 C34" xr:uid="{E6BBE5BD-7004-4694-85A6-704154467F57}">
       <formula1>カテゴリ一覧</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E5:E29 E44:E1004 E31:E41" xr:uid="{029AB92C-5CA0-4F76-9790-7F4B331300FB}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E50:E1010 E37:E47 E31:E35 E5:E30" xr:uid="{029AB92C-5CA0-4F76-9790-7F4B331300FB}">
       <formula1>優先度一覧</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F5:F1004" xr:uid="{40647F47-509E-46A8-8187-C0A1ADC86BC3}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F31:F1010 F5:F30" xr:uid="{40647F47-509E-46A8-8187-C0A1ADC86BC3}">
       <formula1>バージョン一覧</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J5:J1004" xr:uid="{FD5F72C4-282D-476B-B239-E9C4C9E28E99}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J31:J1010 J5:J30" xr:uid="{FD5F72C4-282D-476B-B239-E9C4C9E28E99}">
       <formula1>ステータス一覧</formula1>
     </dataValidation>
-    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="0以上の数値を入力してください" sqref="G5:H1004" xr:uid="{3EFE3393-D09C-4B29-BFD5-14DF7F410677}">
+    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="0以上の数値を入力してください" sqref="G31:H1010 G5:H30" xr:uid="{3EFE3393-D09C-4B29-BFD5-14DF7F410677}">
       <formula1>0</formula1>
     </dataValidation>
   </dataValidations>
@@ -17320,17 +17492,17 @@
   <sheetData>
     <row r="1" spans="2:29" ht="21" x14ac:dyDescent="0.4">
       <c r="B1" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="2" spans="2:29" x14ac:dyDescent="0.4">
       <c r="B2" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="3" spans="2:29" x14ac:dyDescent="0.4">
       <c r="B3" s="55" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C3" s="56"/>
       <c r="D3" s="56"/>
@@ -17343,7 +17515,7 @@
       <c r="H3" s="58"/>
       <c r="I3" s="59"/>
       <c r="J3" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="5" spans="2:29" ht="16.5" x14ac:dyDescent="0.4">
@@ -17378,72 +17550,72 @@
       <c r="W5" s="54"/>
       <c r="X5" s="54"/>
       <c r="Z5" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="6" spans="2:29" x14ac:dyDescent="0.4">
       <c r="B6" s="31" t="s">
+        <v>114</v>
+      </c>
+      <c r="C6" s="32" t="s">
         <v>115</v>
       </c>
-      <c r="C6" s="32" t="s">
+      <c r="D6" s="32" t="s">
         <v>116</v>
       </c>
-      <c r="D6" s="32" t="s">
+      <c r="E6" s="32" t="s">
         <v>117</v>
       </c>
-      <c r="E6" s="32" t="s">
+      <c r="F6" s="32" t="s">
         <v>118</v>
       </c>
-      <c r="F6" s="32" t="s">
+      <c r="G6" s="32" t="s">
         <v>119</v>
       </c>
-      <c r="G6" s="32" t="s">
+      <c r="H6" s="33" t="s">
         <v>120</v>
       </c>
-      <c r="H6" s="33" t="s">
-        <v>121</v>
-      </c>
       <c r="J6" s="31" t="s">
+        <v>114</v>
+      </c>
+      <c r="K6" s="32" t="s">
         <v>115</v>
       </c>
-      <c r="K6" s="32" t="s">
+      <c r="L6" s="32" t="s">
         <v>116</v>
       </c>
-      <c r="L6" s="32" t="s">
+      <c r="M6" s="32" t="s">
         <v>117</v>
       </c>
-      <c r="M6" s="32" t="s">
+      <c r="N6" s="32" t="s">
         <v>118</v>
       </c>
-      <c r="N6" s="32" t="s">
+      <c r="O6" s="32" t="s">
         <v>119</v>
       </c>
-      <c r="O6" s="32" t="s">
+      <c r="P6" s="33" t="s">
         <v>120</v>
       </c>
-      <c r="P6" s="33" t="s">
-        <v>121</v>
-      </c>
       <c r="R6" s="31" t="s">
+        <v>114</v>
+      </c>
+      <c r="S6" s="32" t="s">
         <v>115</v>
       </c>
-      <c r="S6" s="32" t="s">
+      <c r="T6" s="32" t="s">
         <v>116</v>
       </c>
-      <c r="T6" s="32" t="s">
+      <c r="U6" s="32" t="s">
         <v>117</v>
       </c>
-      <c r="U6" s="32" t="s">
+      <c r="V6" s="32" t="s">
         <v>118</v>
       </c>
-      <c r="V6" s="32" t="s">
+      <c r="W6" s="32" t="s">
         <v>119</v>
       </c>
-      <c r="W6" s="32" t="s">
+      <c r="X6" s="33" t="s">
         <v>120</v>
-      </c>
-      <c r="X6" s="33" t="s">
-        <v>121</v>
       </c>
       <c r="Z6" s="10" t="s">
         <v>17</v>
@@ -17452,10 +17624,10 @@
         <v>18</v>
       </c>
       <c r="AB6" s="10" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="AC6" s="10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="7" spans="2:29" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
@@ -17549,15 +17721,15 @@
       </c>
       <c r="AA7" s="35">
         <f>IF(OR(Z7="",設定!$C13=""),"",設定!$C13)</f>
-        <v>46339</v>
+        <v>46326</v>
       </c>
       <c r="AB7" s="36">
         <f t="shared" ref="AB7:AB14" ca="1" si="0">IF(AA7="","",AA7-TODAY())</f>
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="AC7" s="36">
         <f ca="1">IF(AA7="","",MAX(0,NETWORKDAYS.INTL(TODAY(),AA7,週末区分,休日一覧)))</f>
-        <v>19</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="2:29" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
@@ -17651,15 +17823,15 @@
       </c>
       <c r="AA8" s="35">
         <f>IF(OR(Z8="",設定!$C14=""),"",設定!$C14)</f>
-        <v>46374</v>
+        <v>46356</v>
       </c>
       <c r="AB8" s="36">
         <f t="shared" ca="1" si="0"/>
-        <v>61</v>
+        <v>42</v>
       </c>
       <c r="AC8" s="36">
         <f ca="1">IF(AA8="","",MAX(0,NETWORKDAYS.INTL(TODAY(),AA8,週末区分,休日一覧)))</f>
-        <v>43</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9" spans="2:29" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
@@ -17753,15 +17925,15 @@
       </c>
       <c r="AA9" s="35">
         <f>IF(OR(Z9="",設定!$C15=""),"",設定!$C15)</f>
-        <v>46409</v>
+        <v>46372</v>
       </c>
       <c r="AB9" s="36">
         <f t="shared" ca="1" si="0"/>
-        <v>96</v>
+        <v>58</v>
       </c>
       <c r="AC9" s="36">
         <f ca="1">IF(AA9="","",MAX(0,NETWORKDAYS.INTL(TODAY(),AA9,週末区分,休日一覧)))</f>
-        <v>66</v>
+        <v>41</v>
       </c>
     </row>
     <row r="10" spans="2:29" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
@@ -17855,15 +18027,15 @@
       </c>
       <c r="AA10" s="35">
         <f>IF(OR(Z10="",設定!$C16=""),"",設定!$C16)</f>
-        <v>46430</v>
+        <v>46387</v>
       </c>
       <c r="AB10" s="36">
         <f t="shared" ca="1" si="0"/>
-        <v>117</v>
+        <v>73</v>
       </c>
       <c r="AC10" s="36">
         <f ca="1">IF(AA10="","",MAX(0,NETWORKDAYS.INTL(TODAY(),AA10,週末区分,休日一覧)))</f>
-        <v>80</v>
+        <v>52</v>
       </c>
     </row>
     <row r="11" spans="2:29" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
@@ -18140,67 +18312,67 @@
     </row>
     <row r="16" spans="2:29" x14ac:dyDescent="0.4">
       <c r="B16" s="31" t="s">
+        <v>114</v>
+      </c>
+      <c r="C16" s="32" t="s">
         <v>115</v>
       </c>
-      <c r="C16" s="32" t="s">
+      <c r="D16" s="32" t="s">
         <v>116</v>
       </c>
-      <c r="D16" s="32" t="s">
+      <c r="E16" s="32" t="s">
         <v>117</v>
       </c>
-      <c r="E16" s="32" t="s">
+      <c r="F16" s="32" t="s">
         <v>118</v>
       </c>
-      <c r="F16" s="32" t="s">
+      <c r="G16" s="32" t="s">
         <v>119</v>
       </c>
-      <c r="G16" s="32" t="s">
+      <c r="H16" s="33" t="s">
         <v>120</v>
       </c>
-      <c r="H16" s="33" t="s">
-        <v>121</v>
-      </c>
       <c r="J16" s="31" t="s">
+        <v>114</v>
+      </c>
+      <c r="K16" s="32" t="s">
         <v>115</v>
       </c>
-      <c r="K16" s="32" t="s">
+      <c r="L16" s="32" t="s">
         <v>116</v>
       </c>
-      <c r="L16" s="32" t="s">
+      <c r="M16" s="32" t="s">
         <v>117</v>
       </c>
-      <c r="M16" s="32" t="s">
+      <c r="N16" s="32" t="s">
         <v>118</v>
       </c>
-      <c r="N16" s="32" t="s">
+      <c r="O16" s="32" t="s">
         <v>119</v>
       </c>
-      <c r="O16" s="32" t="s">
+      <c r="P16" s="33" t="s">
         <v>120</v>
       </c>
-      <c r="P16" s="33" t="s">
-        <v>121</v>
-      </c>
       <c r="R16" s="31" t="s">
+        <v>114</v>
+      </c>
+      <c r="S16" s="32" t="s">
         <v>115</v>
       </c>
-      <c r="S16" s="32" t="s">
+      <c r="T16" s="32" t="s">
         <v>116</v>
       </c>
-      <c r="T16" s="32" t="s">
+      <c r="U16" s="32" t="s">
         <v>117</v>
       </c>
-      <c r="U16" s="32" t="s">
+      <c r="V16" s="32" t="s">
         <v>118</v>
       </c>
-      <c r="V16" s="32" t="s">
+      <c r="W16" s="32" t="s">
         <v>119</v>
       </c>
-      <c r="W16" s="32" t="s">
+      <c r="X16" s="33" t="s">
         <v>120</v>
-      </c>
-      <c r="X16" s="33" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="17" spans="2:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
@@ -18289,7 +18461,7 @@
         <v>46452</v>
       </c>
       <c r="Z17" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="18" spans="2:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
@@ -18378,7 +18550,7 @@
         <v>46459</v>
       </c>
       <c r="Z18" s="37" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="19" spans="2:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
@@ -18467,7 +18639,7 @@
         <v>46466</v>
       </c>
       <c r="Z19" s="38" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="20" spans="2:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
@@ -18556,7 +18728,7 @@
         <v>46473</v>
       </c>
       <c r="Z20" s="39" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="21" spans="2:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
@@ -18645,7 +18817,7 @@
         <v/>
       </c>
       <c r="Z21" s="40" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="22" spans="2:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
@@ -18734,12 +18906,12 @@
         <v/>
       </c>
       <c r="Z22" s="41" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="23" spans="2:26" x14ac:dyDescent="0.4">
       <c r="Z23" s="42" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
   </sheetData>
@@ -18883,16 +19055,16 @@
         <v>16</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K11" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="M11" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="12" spans="2:14" x14ac:dyDescent="0.4">
@@ -18909,16 +19081,16 @@
         <v>17</v>
       </c>
       <c r="H12" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="I12" s="10" t="s">
         <v>39</v>
-      </c>
-      <c r="I12" s="10" t="s">
-        <v>40</v>
       </c>
       <c r="K12" s="10" t="s">
         <v>17</v>
       </c>
       <c r="M12" s="10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="N12" s="10" t="s">
         <v>17</v>
@@ -18929,77 +19101,71 @@
         <v>20</v>
       </c>
       <c r="C13" s="7">
-        <v>46339</v>
-      </c>
-      <c r="D13" s="6" t="s">
-        <v>21</v>
-      </c>
+        <v>46326</v>
+      </c>
+      <c r="D13" s="6"/>
       <c r="F13" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H13" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="I13" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="I13" s="6" t="s">
-        <v>42</v>
-      </c>
       <c r="K13" s="6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M13" s="7">
         <v>46329</v>
       </c>
       <c r="N13" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="14" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B14" s="6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C14" s="7">
-        <v>46374</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>21</v>
-      </c>
+        <v>46356</v>
+      </c>
+      <c r="D14" s="6"/>
       <c r="F14" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H14" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="I14" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="I14" s="6" t="s">
-        <v>44</v>
-      </c>
       <c r="K14" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="M14" s="7">
         <v>46349</v>
       </c>
       <c r="N14" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B15" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C15" s="7">
-        <v>46409</v>
-      </c>
-      <c r="D15" s="6" t="s">
-        <v>21</v>
-      </c>
+        <v>46372</v>
+      </c>
+      <c r="D15" s="6"/>
       <c r="F15" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H15" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="I15" s="6" t="s">
         <v>45</v>
-      </c>
-      <c r="I15" s="6" t="s">
-        <v>46</v>
       </c>
       <c r="K15" s="6" t="s">
         <v>11</v>
@@ -19008,36 +19174,34 @@
         <v>46388</v>
       </c>
       <c r="N15" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="16" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B16" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C16" s="7">
-        <v>46430</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>21</v>
-      </c>
+        <v>46387</v>
+      </c>
+      <c r="D16" s="6"/>
       <c r="F16" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H16" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="I16" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="I16" s="6" t="s">
-        <v>48</v>
-      </c>
       <c r="K16" s="6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="M16" s="7">
         <v>46398</v>
       </c>
       <c r="N16" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.4">
@@ -19045,7 +19209,7 @@
       <c r="C17" s="7"/>
       <c r="D17" s="6"/>
       <c r="F17" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H17" s="8"/>
       <c r="I17" s="6"/>
@@ -19056,7 +19220,7 @@
         <v>46429</v>
       </c>
       <c r="N17" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.4">
@@ -19064,7 +19228,7 @@
       <c r="C18" s="7"/>
       <c r="D18" s="6"/>
       <c r="F18" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H18" s="8"/>
       <c r="I18" s="6"/>
@@ -19073,7 +19237,7 @@
         <v>46441</v>
       </c>
       <c r="N18" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.4">
@@ -19081,7 +19245,7 @@
       <c r="C19" s="7"/>
       <c r="D19" s="6"/>
       <c r="F19" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H19" s="8"/>
       <c r="I19" s="6"/>
@@ -19090,7 +19254,7 @@
         <v>46468</v>
       </c>
       <c r="N19" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.4">
@@ -19098,7 +19262,7 @@
       <c r="C20" s="7"/>
       <c r="D20" s="6"/>
       <c r="F20" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H20" s="8"/>
       <c r="I20" s="6"/>
@@ -19108,10 +19272,10 @@
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B21" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H21" s="8"/>
       <c r="I21" s="6"/>
@@ -19121,7 +19285,7 @@
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.4">
       <c r="F22" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H22" s="8"/>
       <c r="I22" s="6"/>
@@ -19131,7 +19295,7 @@
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.4">
       <c r="F23" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="M23" s="7"/>
       <c r="N23" s="6"/>
